--- a/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/1_four_bus_radial_1ph_grid_MP_pf_sc_results_0_branch.xlsx
+++ b/pandapower/test/shortcircuit/sce_tests/sc_result_comparison/wp_2.3/1_four_bus_radial_1ph_grid_MP_pf_sc_results_0_branch.xlsx
@@ -988,40 +988,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-5.088522306482316E-18</v>
+        <v>-8.11247845755563E-13</v>
       </c>
       <c r="O2">
-        <v>-4.732322522430773E-16</v>
+        <v>-2.330797607002082E-14</v>
       </c>
       <c r="P2">
-        <v>4.605109022681826E-16</v>
+        <v>3.708769450392485E-14</v>
       </c>
       <c r="Q2">
-        <v>2.544261153241111E-18</v>
+        <v>8.112427572462594E-13</v>
       </c>
       <c r="R2">
-        <v>1.526354593631646E-15</v>
+        <v>2.436225675059677E-14</v>
       </c>
       <c r="S2">
-        <v>5.900671922476028E-16</v>
+        <v>-3.603224138564162E-14</v>
       </c>
       <c r="T2">
-        <v>-2.544261153241234E-18</v>
+        <v>1.424531819696976E-14</v>
       </c>
       <c r="U2">
-        <v>5.763398608022439E-09</v>
+        <v>5.763091620015873E-09</v>
       </c>
       <c r="V2">
-        <v>-5.763398629651377E-09</v>
+        <v>-5.762809999567909E-09</v>
       </c>
       <c r="W2">
-        <v>5.088522306482376E-18</v>
+        <v>-1.448193448072472E-14</v>
       </c>
       <c r="X2">
-        <v>-5.76339789016039E-09</v>
+        <v>-5.763090790171571E-09</v>
       </c>
       <c r="Y2">
-        <v>5.763399346241313E-09</v>
+        <v>5.762810832937981E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1042,40 +1042,40 @@
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.100000023840337</v>
+        <v>1.100000023840339</v>
       </c>
       <c r="AG2">
-        <v>0.5500000119200388</v>
+        <v>0.5500000119200313</v>
       </c>
       <c r="AH2">
-        <v>0.5500000119202982</v>
+        <v>0.5500000119202888</v>
       </c>
       <c r="AI2">
-        <v>1.100000023840337</v>
+        <v>1.10000002385788</v>
       </c>
       <c r="AJ2">
-        <v>0.5499999440216159</v>
+        <v>0.549999944015071</v>
       </c>
       <c r="AK2">
-        <v>0.550000079818741</v>
+        <v>0.5500000798006062</v>
       </c>
       <c r="AL2">
-        <v>6.849422496719089E-13</v>
+        <v>1.94853721019302E-12</v>
       </c>
       <c r="AM2">
+        <v>179.9999999999892</v>
+      </c>
+      <c r="AN2">
         <v>179.9999999999895</v>
       </c>
-      <c r="AN2">
-        <v>179.9999999999891</v>
-      </c>
       <c r="AO2">
-        <v>6.930405785493513E-13</v>
+        <v>2.652051257066453E-10</v>
       </c>
       <c r="AP2">
-        <v>-179.9999895305697</v>
+        <v>-179.9999895311154</v>
       </c>
       <c r="AQ2">
-        <v>179.9999895305654</v>
+        <v>179.9999895315744</v>
       </c>
     </row>
     <row r="3" spans="1:43">
@@ -1119,40 +1119,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>-6.135951155608409E-21</v>
+        <v>1.543586225686732E-24</v>
       </c>
       <c r="O3">
-        <v>-5.342274675114934E-16</v>
+        <v>-3.338324193351642E-13</v>
       </c>
       <c r="P3">
-        <v>-1.729426153524918E-16</v>
+        <v>1.66389794050126E-13</v>
       </c>
       <c r="Q3">
-        <v>6.135951155608409E-21</v>
+        <v>-1.282586398760858E-24</v>
       </c>
       <c r="R3">
-        <v>6.512410573685855E-16</v>
+        <v>3.339494269908964E-13</v>
       </c>
       <c r="S3">
-        <v>2.89956204721247E-16</v>
+        <v>-1.662728171485907E-13</v>
       </c>
       <c r="T3">
-        <v>-5.366535363049228E-23</v>
+        <v>-3.334813978829455E-13</v>
       </c>
       <c r="U3">
-        <v>1.921132600370416E-09</v>
+        <v>1.921352836593411E-09</v>
       </c>
       <c r="V3">
-        <v>-1.921133069617069E-09</v>
+        <v>-1.920686348155737E-09</v>
       </c>
       <c r="W3">
-        <v>5.366535363049228E-23</v>
+        <v>3.334813978822767E-13</v>
       </c>
       <c r="X3">
-        <v>-1.921132521314707E-09</v>
+        <v>-1.921352757512827E-09</v>
       </c>
       <c r="Y3">
-        <v>1.921133148672777E-09</v>
+        <v>1.920686427191017E-09</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1173,40 +1173,40 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.100000023840337</v>
+        <v>1.10000002385788</v>
       </c>
       <c r="AG3">
-        <v>0.5499999440216159</v>
+        <v>0.549999944015071</v>
       </c>
       <c r="AH3">
-        <v>0.550000079818741</v>
+        <v>0.5500000798006062</v>
       </c>
       <c r="AI3">
-        <v>1.100000023840337</v>
+        <v>1.100000023855674</v>
       </c>
       <c r="AJ3">
-        <v>0.5499999213888129</v>
+        <v>0.5499999213835525</v>
       </c>
       <c r="AK3">
-        <v>0.5500001024515583</v>
+        <v>0.5500001024299328</v>
       </c>
       <c r="AL3">
-        <v>6.930405785493513E-13</v>
+        <v>2.652051257066453E-10</v>
       </c>
       <c r="AM3">
-        <v>-179.9999895305697</v>
+        <v>-179.9999895311154</v>
       </c>
       <c r="AN3">
-        <v>179.9999895305654</v>
+        <v>179.9999895315744</v>
       </c>
       <c r="AO3">
-        <v>6.930424367994429E-13</v>
+        <v>2.203624789164977E-10</v>
       </c>
       <c r="AP3">
-        <v>-179.9999860407604</v>
+        <v>-179.9999860414742</v>
       </c>
       <c r="AQ3">
-        <v>179.9999860407581</v>
+        <v>179.9999860418454</v>
       </c>
     </row>
     <row r="4" spans="1:43">
@@ -1250,40 +1250,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>-6.135951192632282E-21</v>
+        <v>-6.174344902746929E-24</v>
       </c>
       <c r="O4">
-        <v>-5.087848674882636E-16</v>
+        <v>3.331305073380795E-13</v>
       </c>
       <c r="P4">
-        <v>-1.882081953141666E-16</v>
+        <v>-3.338323949681293E-13</v>
       </c>
       <c r="Q4">
-        <v>6.135951192632282E-21</v>
+        <v>8.374486140837491E-24</v>
       </c>
       <c r="R4">
-        <v>5.789930242472707E-16</v>
+        <v>-3.330603331356996E-13</v>
       </c>
       <c r="S4">
-        <v>2.584163530950532E-16</v>
+        <v>3.339025872046534E-13</v>
       </c>
       <c r="T4">
-        <v>-5.366527032677889E-23</v>
+        <v>1.333925591531782E-12</v>
       </c>
       <c r="U4">
-        <v>1.921132646167115E-09</v>
+        <v>1.920185651966809E-09</v>
       </c>
       <c r="V4">
-        <v>-1.921133130679342E-09</v>
+        <v>-1.92085308878386E-09</v>
       </c>
       <c r="W4">
-        <v>5.366527032677889E-23</v>
+        <v>-1.333925591528926E-12</v>
       </c>
       <c r="X4">
-        <v>-1.921132598733688E-09</v>
+        <v>-1.920185604573719E-09</v>
       </c>
       <c r="Y4">
-        <v>1.921133178112768E-09</v>
+        <v>1.920853136185193E-09</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1304,40 +1304,40 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.100000023840337</v>
+        <v>1.10000002385788</v>
       </c>
       <c r="AG4">
-        <v>0.5499999440216159</v>
+        <v>0.549999944015071</v>
       </c>
       <c r="AH4">
-        <v>0.550000079818741</v>
+        <v>0.5500000798006062</v>
       </c>
       <c r="AI4">
-        <v>1.100000023840337</v>
+        <v>1.100000023855525</v>
       </c>
       <c r="AJ4">
-        <v>0.5499999304419333</v>
+        <v>0.549999930436753</v>
       </c>
       <c r="AK4">
-        <v>0.5500000933984315</v>
+        <v>0.5500000933765773</v>
       </c>
       <c r="AL4">
-        <v>6.930405785493513E-13</v>
+        <v>2.652051257066453E-10</v>
       </c>
       <c r="AM4">
-        <v>-179.9999895305697</v>
+        <v>-179.9999895311154</v>
       </c>
       <c r="AN4">
-        <v>179.9999895305654</v>
+        <v>179.9999895315744</v>
       </c>
       <c r="AO4">
-        <v>6.930416934994352E-13</v>
+        <v>3.597072539187162E-10</v>
       </c>
       <c r="AP4">
-        <v>-179.9999874366842</v>
+        <v>-179.9999874374561</v>
       </c>
       <c r="AQ4">
-        <v>179.999987436681</v>
+        <v>179.9999874381052</v>
       </c>
     </row>
   </sheetData>
@@ -1522,40 +1522,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>2.223461385568352E-21</v>
+        <v>3.79412933140974E-17</v>
       </c>
       <c r="O2">
-        <v>-1.763630980069599E-12</v>
+        <v>-1.763236370092092E-12</v>
       </c>
       <c r="P2">
-        <v>-4.921567962189332E-12</v>
+        <v>-4.921128583730339E-12</v>
       </c>
       <c r="Q2">
-        <v>-2.964615180757803E-21</v>
+        <v>-3.796352792795191E-17</v>
       </c>
       <c r="R2">
-        <v>1.763630980879332E-12</v>
+        <v>1.763236412104323E-12</v>
       </c>
       <c r="S2">
-        <v>4.921567958003147E-12</v>
+        <v>4.921128558841677E-12</v>
       </c>
       <c r="T2">
-        <v>2.371692144606242E-21</v>
+        <v>3.007471657810837E-16</v>
       </c>
       <c r="U2">
-        <v>4.665889178666842E-12</v>
+        <v>4.665715107910869E-12</v>
       </c>
       <c r="V2">
-        <v>8.038180720165916E-13</v>
+        <v>8.041752552257774E-13</v>
       </c>
       <c r="W2">
-        <v>-1.359405480727193E-38</v>
+        <v>-3.00709218706769E-16</v>
       </c>
       <c r="X2">
-        <v>-4.665889177493977E-12</v>
+        <v>-4.665715101790016E-12</v>
       </c>
       <c r="Y2">
-        <v>-8.038180737274803E-13</v>
+        <v>-8.041752969455418E-13</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1585,16 +1585,16 @@
         <v>1.049573667098045</v>
       </c>
       <c r="AI2">
-        <v>1.049999952316289</v>
+        <v>1.049999952316285</v>
       </c>
       <c r="AJ2">
-        <v>1.04984715703054</v>
+        <v>1.049847157030537</v>
       </c>
       <c r="AK2">
-        <v>1.049573667138054</v>
+        <v>1.04957366713805</v>
       </c>
       <c r="AL2">
-        <v>2.493182027243532E-16</v>
+        <v>2.365052242977894E-16</v>
       </c>
       <c r="AM2">
         <v>-120.0220469790133</v>
@@ -1603,10 +1603,10 @@
         <v>119.9962008556722</v>
       </c>
       <c r="AO2">
-        <v>2.627261615543246E-16</v>
+        <v>1.950262810913033E-13</v>
       </c>
       <c r="AP2">
-        <v>-120.0220469760931</v>
+        <v>-120.0220469760934</v>
       </c>
       <c r="AQ2">
         <v>119.9962008577318</v>
@@ -1653,40 +1653,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1.732136096799267E-23</v>
+        <v>-1.165734122916861E-16</v>
       </c>
       <c r="O3">
-        <v>-5.878770040471954E-13</v>
+        <v>-5.876886978860967E-13</v>
       </c>
       <c r="P3">
-        <v>-1.640522620453119E-12</v>
+        <v>-1.640424407435166E-12</v>
       </c>
       <c r="Q3">
-        <v>-1.732136096799267E-23</v>
+        <v>1.16573412291686E-16</v>
       </c>
       <c r="R3">
-        <v>5.878770040712513E-13</v>
+        <v>5.876886979101549E-13</v>
       </c>
       <c r="S3">
-        <v>1.640522620477175E-12</v>
+        <v>1.640424407459219E-12</v>
       </c>
       <c r="T3">
-        <v>-1.853613008875115E-26</v>
+        <v>1.554312163889137E-16</v>
       </c>
       <c r="U3">
-        <v>1.55529635629653E-12</v>
+        <v>1.555470974433415E-12</v>
       </c>
       <c r="V3">
-        <v>2.679393432006576E-13</v>
+        <v>2.679205245324649E-13</v>
       </c>
       <c r="W3">
-        <v>1.853613008875115E-26</v>
+        <v>-1.554312163889137E-16</v>
       </c>
       <c r="X3">
-        <v>-1.555296356280277E-12</v>
+        <v>-1.555470974417163E-12</v>
       </c>
       <c r="Y3">
-        <v>-2.679393431844052E-13</v>
+        <v>-2.679205245162128E-13</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,40 +1707,40 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.049999952316289</v>
+        <v>1.049999952316285</v>
       </c>
       <c r="AG3">
-        <v>1.04984715703054</v>
+        <v>1.049847157030537</v>
       </c>
       <c r="AH3">
-        <v>1.049573667138054</v>
+        <v>1.04957366713805</v>
       </c>
       <c r="AI3">
-        <v>1.049999952316289</v>
+        <v>1.049999952316284</v>
       </c>
       <c r="AJ3">
-        <v>1.049847157026311</v>
+        <v>1.049847157026307</v>
       </c>
       <c r="AK3">
-        <v>1.04957366715139</v>
+        <v>1.049573667151385</v>
       </c>
       <c r="AL3">
-        <v>2.627261615543246E-16</v>
+        <v>1.950262810913033E-13</v>
       </c>
       <c r="AM3">
-        <v>-120.0220469760931</v>
+        <v>-120.0220469760934</v>
       </c>
       <c r="AN3">
         <v>119.9962008577318</v>
       </c>
       <c r="AO3">
-        <v>2.627203196117043E-16</v>
+        <v>1.85563163132692E-13</v>
       </c>
       <c r="AP3">
-        <v>-120.0220469751197</v>
+        <v>-120.02204697512</v>
       </c>
       <c r="AQ3">
-        <v>119.9962008584183</v>
+        <v>119.9962008584184</v>
       </c>
     </row>
     <row r="4" spans="1:43">
@@ -1784,40 +1784,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>1.732136110604333E-23</v>
+        <v>-4.274358450695159E-16</v>
       </c>
       <c r="O4">
-        <v>-5.878770062351546E-13</v>
+        <v>-5.867647164597305E-13</v>
       </c>
       <c r="P4">
-        <v>-1.640522671633288E-12</v>
+        <v>-1.640343985096874E-12</v>
       </c>
       <c r="Q4">
-        <v>-1.732136110604333E-23</v>
+        <v>4.27435845069516E-16</v>
       </c>
       <c r="R4">
-        <v>5.878770062495881E-13</v>
+        <v>5.867647164741647E-13</v>
       </c>
       <c r="S4">
-        <v>1.640522671647721E-12</v>
+        <v>1.640343985111297E-12</v>
       </c>
       <c r="T4">
-        <v>-1.853647521538151E-26</v>
+        <v>6.217248655556549E-16</v>
       </c>
       <c r="U4">
-        <v>1.555296390426524E-12</v>
+        <v>1.555206274769376E-12</v>
       </c>
       <c r="V4">
-        <v>2.679393465048291E-13</v>
+        <v>2.671596637851233E-13</v>
       </c>
       <c r="W4">
-        <v>1.853647521538151E-26</v>
+        <v>-6.217248655556536E-16</v>
       </c>
       <c r="X4">
-        <v>-1.555296390416772E-12</v>
+        <v>-1.555206274759637E-12</v>
       </c>
       <c r="Y4">
-        <v>-2.679393464950776E-13</v>
+        <v>-2.671596637753682E-13</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1838,37 +1838,37 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.049999952316289</v>
+        <v>1.049999952316285</v>
       </c>
       <c r="AG4">
-        <v>1.04984715703054</v>
+        <v>1.049847157030537</v>
       </c>
       <c r="AH4">
-        <v>1.049573667138054</v>
+        <v>1.04957366713805</v>
       </c>
       <c r="AI4">
-        <v>1.049999952316289</v>
+        <v>1.049999952316283</v>
       </c>
       <c r="AJ4">
-        <v>1.049847157028003</v>
+        <v>1.049847157028</v>
       </c>
       <c r="AK4">
-        <v>1.049573667146056</v>
+        <v>1.049573667146049</v>
       </c>
       <c r="AL4">
-        <v>2.627261615543246E-16</v>
+        <v>1.950262810913033E-13</v>
       </c>
       <c r="AM4">
-        <v>-120.0220469760931</v>
+        <v>-120.0220469760934</v>
       </c>
       <c r="AN4">
         <v>119.9962008577318</v>
       </c>
       <c r="AO4">
-        <v>2.627226563886625E-16</v>
+        <v>2.661017745272361E-13</v>
       </c>
       <c r="AP4">
-        <v>-120.022046975509</v>
+        <v>-120.0220469755094</v>
       </c>
       <c r="AQ4">
         <v>119.9962008581437</v>
@@ -2056,40 +2056,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>2.795208786523708E-21</v>
+        <v>-2.60163436648186E-16</v>
       </c>
       <c r="O2">
-        <v>-2.027695456031609E-12</v>
+        <v>-2.027377766721892E-12</v>
       </c>
       <c r="P2">
-        <v>-5.658463172962532E-12</v>
+        <v>-5.657893412211234E-12</v>
       </c>
       <c r="Q2">
-        <v>-2.795208786523708E-21</v>
+        <v>2.601823819521861E-16</v>
       </c>
       <c r="R2">
-        <v>2.027695455073701E-12</v>
+        <v>2.027377594500781E-12</v>
       </c>
       <c r="S2">
-        <v>5.658463177835561E-12</v>
+        <v>5.657893549422469E-12</v>
       </c>
       <c r="T2">
-        <v>-4.969260064931035E-21</v>
+        <v>-1.119971833434157E-16</v>
       </c>
       <c r="U2">
-        <v>5.364567043634896E-12</v>
+        <v>5.364632655004435E-12</v>
       </c>
       <c r="V2">
-        <v>9.241070533809363E-13</v>
+        <v>9.243350811857785E-13</v>
       </c>
       <c r="W2">
-        <v>4.969260064931035E-21</v>
+        <v>1.118232592411441E-16</v>
       </c>
       <c r="X2">
-        <v>-5.364567040602531E-12</v>
+        <v>-5.364632575954975E-12</v>
       </c>
       <c r="Y2">
-        <v>-9.241070512592127E-13</v>
+        <v>-9.243349804463979E-13</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -2119,16 +2119,16 @@
         <v>1.099532180585668</v>
       </c>
       <c r="AI2">
-        <v>1.100000023841857</v>
+        <v>1.100000023841868</v>
       </c>
       <c r="AJ2">
-        <v>1.099832330786825</v>
+        <v>1.099832330786819</v>
       </c>
       <c r="AK2">
-        <v>1.099532180629578</v>
+        <v>1.099532180629567</v>
       </c>
       <c r="AL2">
-        <v>2.638570207191328E-16</v>
+        <v>6.509648016880854E-16</v>
       </c>
       <c r="AM2">
         <v>-120.023096465693</v>
@@ -2137,13 +2137,13 @@
         <v>119.9960202858331</v>
       </c>
       <c r="AO2">
-        <v>2.717461580925804E-16</v>
+        <v>-1.448560192813638E-14</v>
       </c>
       <c r="AP2">
-        <v>-120.0230964626337</v>
+        <v>-120.0230964626334</v>
       </c>
       <c r="AQ2">
-        <v>119.9960202879907</v>
+        <v>119.9960202879903</v>
       </c>
     </row>
     <row r="3" spans="1:43">
@@ -2187,40 +2187,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>-2.177670899091417E-24</v>
+        <v>3.460195168412812E-16</v>
       </c>
       <c r="O3">
-        <v>-6.758985031434405E-13</v>
+        <v>-6.758262530163239E-13</v>
       </c>
       <c r="P3">
-        <v>-1.886154365398227E-12</v>
+        <v>-1.886221283602431E-12</v>
       </c>
       <c r="Q3">
-        <v>2.177670899091417E-24</v>
+        <v>-3.460195168412806E-16</v>
       </c>
       <c r="R3">
-        <v>6.758985031724149E-13</v>
+        <v>6.758262530452935E-13</v>
       </c>
       <c r="S3">
-        <v>1.886154365427202E-12</v>
+        <v>1.886221283631406E-12</v>
       </c>
       <c r="T3">
-        <v>-2.104256681482605E-26</v>
+        <v>-1.628327138076619E-16</v>
       </c>
       <c r="U3">
-        <v>1.788188983835574E-12</v>
+        <v>1.787980715352572E-12</v>
       </c>
       <c r="V3">
-        <v>3.08035659792932E-13</v>
+        <v>3.081594927659914E-13</v>
       </c>
       <c r="W3">
-        <v>2.104256681482605E-26</v>
+        <v>1.628327138076618E-16</v>
       </c>
       <c r="X3">
-        <v>-1.788188983815999E-12</v>
+        <v>-1.787980715332996E-12</v>
       </c>
       <c r="Y3">
-        <v>-3.080356597733563E-13</v>
+        <v>-3.081594927464171E-13</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -2241,40 +2241,40 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.100000023841857</v>
+        <v>1.100000023841868</v>
       </c>
       <c r="AG3">
-        <v>1.099832330786825</v>
+        <v>1.099832330786819</v>
       </c>
       <c r="AH3">
-        <v>1.099532180629578</v>
+        <v>1.099532180629567</v>
       </c>
       <c r="AI3">
-        <v>1.100000023841857</v>
+        <v>1.100000023841867</v>
       </c>
       <c r="AJ3">
-        <v>1.099832330782184</v>
+        <v>1.099832330782176</v>
       </c>
       <c r="AK3">
-        <v>1.099532180644215</v>
+        <v>1.099532180644202</v>
       </c>
       <c r="AL3">
-        <v>2.717461580925804E-16</v>
+        <v>-1.448560192813638E-14</v>
       </c>
       <c r="AM3">
-        <v>-120.0230964626337</v>
+        <v>-120.0230964626334</v>
       </c>
       <c r="AN3">
-        <v>119.9960202879907</v>
+        <v>119.9960202879903</v>
       </c>
       <c r="AO3">
-        <v>2.717468166854522E-16</v>
+        <v>-4.220128573570005E-14</v>
       </c>
       <c r="AP3">
-        <v>-120.0230964616139</v>
+        <v>-120.0230964616136</v>
       </c>
       <c r="AQ3">
-        <v>119.9960202887099</v>
+        <v>119.9960202887095</v>
       </c>
     </row>
     <row r="4" spans="1:43">
@@ -2318,40 +2318,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>-2.177670899091417E-24</v>
+        <v>1.646704098026956E-31</v>
       </c>
       <c r="O4">
-        <v>-6.758984869845343E-13</v>
+        <v>-6.756140118952604E-13</v>
       </c>
       <c r="P4">
-        <v>-1.886154393780353E-12</v>
+        <v>-1.885423487507991E-12</v>
       </c>
       <c r="Q4">
-        <v>2.177670899091417E-24</v>
+        <v>6.817639963450281E-31</v>
       </c>
       <c r="R4">
-        <v>6.758984870019189E-13</v>
+        <v>6.756140119126427E-13</v>
       </c>
       <c r="S4">
-        <v>1.886154393797738E-12</v>
+        <v>1.885423487525365E-12</v>
       </c>
       <c r="T4">
-        <v>-2.104253065870045E-26</v>
+        <v>6.51330855230647E-16</v>
       </c>
       <c r="U4">
-        <v>1.788189011797584E-12</v>
+        <v>1.788022597152259E-12</v>
       </c>
       <c r="V4">
-        <v>3.080356692181484E-13</v>
+        <v>3.080797120599512E-13</v>
       </c>
       <c r="W4">
-        <v>2.104253065870045E-26</v>
+        <v>-6.513308552306461E-16</v>
       </c>
       <c r="X4">
-        <v>-1.788189011785839E-12</v>
+        <v>-1.788022597140518E-12</v>
       </c>
       <c r="Y4">
-        <v>-3.080356692064029E-13</v>
+        <v>-3.080797120482129E-13</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2372,40 +2372,40 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.100000023841857</v>
+        <v>1.100000023841868</v>
       </c>
       <c r="AG4">
-        <v>1.099832330786825</v>
+        <v>1.099832330786819</v>
       </c>
       <c r="AH4">
-        <v>1.099532180629578</v>
+        <v>1.099532180629567</v>
       </c>
       <c r="AI4">
-        <v>1.100000023841857</v>
+        <v>1.100000023841867</v>
       </c>
       <c r="AJ4">
-        <v>1.099832330784041</v>
+        <v>1.099832330784034</v>
       </c>
       <c r="AK4">
-        <v>1.09953218063836</v>
+        <v>1.099532180638346</v>
       </c>
       <c r="AL4">
-        <v>2.717461580925804E-16</v>
+        <v>-1.448560192813638E-14</v>
       </c>
       <c r="AM4">
-        <v>-120.0230964626337</v>
+        <v>-120.0230964626334</v>
       </c>
       <c r="AN4">
-        <v>119.9960202879907</v>
+        <v>119.9960202879903</v>
       </c>
       <c r="AO4">
-        <v>2.717465532483137E-16</v>
+        <v>5.997289902795791E-14</v>
       </c>
       <c r="AP4">
-        <v>-120.0230964620218</v>
+        <v>-120.0230964620216</v>
       </c>
       <c r="AQ4">
-        <v>119.9960202884222</v>
+        <v>119.9960202884218</v>
       </c>
     </row>
   </sheetData>
@@ -2590,40 +2590,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.64798728148616E-18</v>
+        <v>-2.093174565706698E-13</v>
       </c>
       <c r="O2">
-        <v>-3.5623503829239E-16</v>
+        <v>-5.072257179777714E-14</v>
       </c>
       <c r="P2">
-        <v>3.658575370956073E-16</v>
+        <v>-3.232724766340615E-13</v>
       </c>
       <c r="Q2">
-        <v>-2.19731637531486E-18</v>
+        <v>2.09524553649389E-13</v>
       </c>
       <c r="R2">
-        <v>1.864924743581726E-15</v>
+        <v>5.212723364402447E-14</v>
       </c>
       <c r="S2">
-        <v>1.142282851345845E-15</v>
+        <v>3.246761786536843E-13</v>
       </c>
       <c r="T2">
-        <v>-5.493290938286962E-18</v>
+        <v>-5.16785739652113E-13</v>
       </c>
       <c r="U2">
-        <v>4.298732479816834E-09</v>
+        <v>4.298695494038311E-09</v>
       </c>
       <c r="V2">
-        <v>-4.298732483672345E-09</v>
+        <v>-4.298775386274617E-09</v>
       </c>
       <c r="W2">
-        <v>5.493290938286957E-18</v>
+        <v>5.169406504521063E-13</v>
       </c>
       <c r="X2">
-        <v>-4.298731948581695E-09</v>
+        <v>-4.298695038142936E-09</v>
       </c>
       <c r="Y2">
-        <v>4.298733016555468E-09</v>
+        <v>4.298775840137501E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -2644,40 +2644,40 @@
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.9499999880719476</v>
+        <v>0.9499999880719677</v>
       </c>
       <c r="AG2">
-        <v>0.4749999940354099</v>
+        <v>0.4749999940354138</v>
       </c>
       <c r="AH2">
-        <v>0.4749999940365377</v>
+        <v>0.4749999940365425</v>
       </c>
       <c r="AI2">
-        <v>0.949999988071948</v>
+        <v>0.9499999880715366</v>
       </c>
       <c r="AJ2">
-        <v>0.4749999353958987</v>
+        <v>0.4749999354063731</v>
       </c>
       <c r="AK2">
-        <v>0.4750000526761066</v>
+        <v>0.4750000526972563</v>
       </c>
       <c r="AL2">
-        <v>6.849393129573195E-13</v>
+        <v>1.039699615593286E-12</v>
       </c>
       <c r="AM2">
-        <v>179.9999999999277</v>
+        <v>179.9999999999295</v>
       </c>
       <c r="AN2">
-        <v>-179.9999999999346</v>
+        <v>-179.999999999933</v>
       </c>
       <c r="AO2">
-        <v>6.981652515714128E-13</v>
+        <v>-1.156182649515411E-09</v>
       </c>
       <c r="AP2">
-        <v>-179.9999798987623</v>
+        <v>-179.9999798975721</v>
       </c>
       <c r="AQ2">
-        <v>179.9999798987602</v>
+        <v>179.9999799003721</v>
       </c>
     </row>
     <row r="3" spans="1:43">
@@ -2721,40 +2721,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>-2.481215133777116E-20</v>
+        <v>1.440033259638503E-13</v>
       </c>
       <c r="O3">
-        <v>-6.400440871196675E-16</v>
+        <v>-1.085052460108473E-13</v>
       </c>
       <c r="P3">
-        <v>-3.653797167060019E-16</v>
+        <v>-1.085052027771773E-13</v>
       </c>
       <c r="Q3">
-        <v>2.481215133777116E-20</v>
+        <v>-1.440033259635461E-13</v>
       </c>
       <c r="R3">
-        <v>8.076152296604724E-16</v>
+        <v>1.08672829070394E-13</v>
       </c>
       <c r="S3">
-        <v>5.329508592468066E-16</v>
+        <v>1.086727985965139E-13</v>
       </c>
       <c r="T3">
-        <v>-4.032370046028807E-23</v>
+        <v>-4.320099779206096E-13</v>
       </c>
       <c r="U3">
-        <v>1.432910602651148E-09</v>
+        <v>1.432976919842239E-09</v>
       </c>
       <c r="V3">
-        <v>-1.432910956445089E-09</v>
+        <v>-1.432977273684668E-09</v>
       </c>
       <c r="W3">
-        <v>4.032370046028807E-23</v>
+        <v>4.32009977921642E-13</v>
       </c>
       <c r="X3">
-        <v>-1.432910543686062E-09</v>
+        <v>-1.432976860860621E-09</v>
       </c>
       <c r="Y3">
-        <v>1.432911015410175E-09</v>
+        <v>1.432977332646582E-09</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -2775,40 +2775,40 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.949999988071948</v>
+        <v>0.9499999880715366</v>
       </c>
       <c r="AG3">
-        <v>0.4749999353958987</v>
+        <v>0.4749999354063731</v>
       </c>
       <c r="AH3">
-        <v>0.4750000526761066</v>
+        <v>0.4750000526972563</v>
       </c>
       <c r="AI3">
-        <v>0.949999988071948</v>
+        <v>0.949999988073379</v>
       </c>
       <c r="AJ3">
-        <v>0.4749999158494094</v>
+        <v>0.4749999158594899</v>
       </c>
       <c r="AK3">
-        <v>0.4750000722226414</v>
+        <v>0.4750000722460274</v>
       </c>
       <c r="AL3">
-        <v>6.981652515714128E-13</v>
+        <v>-1.156182649515411E-09</v>
       </c>
       <c r="AM3">
-        <v>-179.9999798987623</v>
+        <v>-179.9999798975721</v>
       </c>
       <c r="AN3">
-        <v>179.9999798987602</v>
+        <v>179.9999799003721</v>
       </c>
       <c r="AO3">
-        <v>6.981754110932108E-13</v>
+        <v>-1.233568687635038E-09</v>
       </c>
       <c r="AP3">
-        <v>-179.9999731983295</v>
+        <v>-179.9999731967955</v>
       </c>
       <c r="AQ3">
-        <v>179.9999731983313</v>
+        <v>179.9999731994446</v>
       </c>
     </row>
     <row r="4" spans="1:43">
@@ -2852,40 +2852,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>-2.481215204122472E-20</v>
+        <v>-2.880066519335124E-13</v>
       </c>
       <c r="O4">
-        <v>-6.257615470902583E-16</v>
+        <v>7.149904080904525E-14</v>
       </c>
       <c r="P4">
-        <v>-3.7966228955569E-16</v>
+        <v>-5.028465107680773E-16</v>
       </c>
       <c r="Q4">
-        <v>2.481215204122472E-20</v>
+        <v>2.880066519339435E-13</v>
       </c>
       <c r="R4">
-        <v>7.263042384421354E-16</v>
+        <v>-7.139851544389762E-14</v>
       </c>
       <c r="S4">
-        <v>4.802049809075671E-16</v>
+        <v>6.034301331437854E-16</v>
       </c>
       <c r="T4">
-        <v>-4.032349262173752E-23</v>
+        <v>5.760133038960835E-13</v>
       </c>
       <c r="U4">
-        <v>1.432910644400159E-09</v>
+        <v>1.432544909980799E-09</v>
       </c>
       <c r="V4">
-        <v>-1.432910998194101E-09</v>
+        <v>-1.433409283753826E-09</v>
       </c>
       <c r="W4">
-        <v>4.032349262173752E-23</v>
+        <v>-5.760133038966467E-13</v>
       </c>
       <c r="X4">
-        <v>-1.432910609021106E-09</v>
+        <v>-1.432544874613751E-09</v>
       </c>
       <c r="Y4">
-        <v>1.432911033573154E-09</v>
+        <v>1.433409319150362E-09</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2906,40 +2906,40 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.949999988071948</v>
+        <v>0.9499999880715366</v>
       </c>
       <c r="AG4">
-        <v>0.4749999353958987</v>
+        <v>0.4749999354063731</v>
       </c>
       <c r="AH4">
-        <v>0.4750000526761066</v>
+        <v>0.4750000526972563</v>
       </c>
       <c r="AI4">
-        <v>0.949999988071948</v>
+        <v>0.9499999880725641</v>
       </c>
       <c r="AJ4">
-        <v>0.4749999236680036</v>
+        <v>0.4749999236777863</v>
       </c>
       <c r="AK4">
-        <v>0.4750000644040273</v>
+        <v>0.4750000644268962</v>
       </c>
       <c r="AL4">
-        <v>6.981652515714128E-13</v>
+        <v>-1.156182649515411E-09</v>
       </c>
       <c r="AM4">
-        <v>-179.9999798987623</v>
+        <v>-179.9999798975721</v>
       </c>
       <c r="AN4">
-        <v>179.9999798987602</v>
+        <v>179.9999799003721</v>
       </c>
       <c r="AO4">
-        <v>6.981713472848077E-13</v>
+        <v>-1.144287156533274E-09</v>
       </c>
       <c r="AP4">
-        <v>-179.9999758785026</v>
+        <v>-179.9999758770503</v>
       </c>
       <c r="AQ4">
-        <v>179.9999758785027</v>
+        <v>179.9999758798761</v>
       </c>
     </row>
   </sheetData>
@@ -3124,40 +3124,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-1.040834058007535E-18</v>
+        <v>-6.595505217079281E-14</v>
       </c>
       <c r="O2">
-        <v>-3.192707195898938E-16</v>
+        <v>1.914861498571608E-13</v>
       </c>
       <c r="P2">
-        <v>3.263061403785614E-16</v>
+        <v>-3.509801684083149E-13</v>
       </c>
       <c r="Q2">
-        <v>5.204170290037488E-19</v>
+        <v>6.596494009489146E-14</v>
       </c>
       <c r="R2">
-        <v>1.673877949785958E-15</v>
+        <v>-1.901371401670253E-13</v>
       </c>
       <c r="S2">
-        <v>1.027260261240627E-15</v>
+        <v>3.523305574980039E-13</v>
       </c>
       <c r="T2">
-        <v>-3.12250217402273E-18</v>
+        <v>-1.829734232274435E-13</v>
       </c>
       <c r="U2">
-        <v>3.858142067575433E-09</v>
+        <v>3.857946179483253E-09</v>
       </c>
       <c r="V2">
-        <v>-3.85814206602065E-09</v>
+        <v>-3.85807002573221E-09</v>
       </c>
       <c r="W2">
-        <v>3.122502174022724E-18</v>
+        <v>1.830775066323622E-13</v>
       </c>
       <c r="X2">
-        <v>-3.858141585556669E-09</v>
+        <v>-3.857945757929632E-09</v>
       </c>
       <c r="Y2">
-        <v>3.858142542314823E-09</v>
+        <v>3.858070450015303E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -3178,40 +3178,40 @@
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.8999999761531055</v>
+        <v>0.8999999761531126</v>
       </c>
       <c r="AG2">
-        <v>0.4499999880761755</v>
+        <v>0.4499999880761801</v>
       </c>
       <c r="AH2">
-        <v>0.4499999880769299</v>
+        <v>0.4499999880769358</v>
       </c>
       <c r="AI2">
-        <v>0.8999999761531058</v>
+        <v>0.8999999761501329</v>
       </c>
       <c r="AJ2">
-        <v>0.4499999325229551</v>
+        <v>0.4499999325235781</v>
       </c>
       <c r="AK2">
-        <v>0.450000043630205</v>
+        <v>0.4500000436491957</v>
       </c>
       <c r="AL2">
-        <v>6.863149386262686E-13</v>
+        <v>7.995276734266983E-13</v>
       </c>
       <c r="AM2">
-        <v>179.9999999999166</v>
+        <v>179.9999999999173</v>
       </c>
       <c r="AN2">
-        <v>-179.9999999999235</v>
+        <v>-179.9999999999227</v>
       </c>
       <c r="AO2">
-        <v>6.908379230916166E-13</v>
+        <v>-2.389142860797283E-10</v>
       </c>
       <c r="AP2">
-        <v>-179.9999798987734</v>
+        <v>-179.9999799000816</v>
       </c>
       <c r="AQ2">
-        <v>179.9999798987714</v>
+        <v>179.9999798998547</v>
       </c>
     </row>
     <row r="3" spans="1:43">
@@ -3255,40 +3255,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>-1.661965703260801E-20</v>
+        <v>3.410605041262259E-13</v>
       </c>
       <c r="O3">
-        <v>-5.719238229028769E-16</v>
+        <v>-1.027693524818972E-13</v>
       </c>
       <c r="P3">
-        <v>-3.283688087651545E-16</v>
+        <v>-3.455715405566361E-14</v>
       </c>
       <c r="Q3">
-        <v>1.661965703260801E-20</v>
+        <v>-3.410605041260555E-13</v>
       </c>
       <c r="R3">
-        <v>7.223200789303654E-16</v>
+        <v>1.029197650120809E-13</v>
       </c>
       <c r="S3">
-        <v>4.787650644635414E-16</v>
+        <v>3.470753216323553E-14</v>
       </c>
       <c r="T3">
-        <v>-3.581087122054945E-23</v>
+        <v>-1.364242016521401E-13</v>
       </c>
       <c r="U3">
-        <v>1.286047150776637E-09</v>
+        <v>1.286207214347583E-09</v>
       </c>
       <c r="V3">
-        <v>-1.286047466226573E-09</v>
+        <v>-1.285866471448804E-09</v>
       </c>
       <c r="W3">
-        <v>3.581087122054945E-23</v>
+        <v>1.364242016520488E-13</v>
       </c>
       <c r="X3">
-        <v>-1.286047097855066E-09</v>
+        <v>-1.286207161406107E-09</v>
       </c>
       <c r="Y3">
-        <v>1.286047519148144E-09</v>
+        <v>1.285866524358944E-09</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -3309,40 +3309,40 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.8999999761531058</v>
+        <v>0.8999999761501329</v>
       </c>
       <c r="AG3">
-        <v>0.4499999325229551</v>
+        <v>0.4499999325235781</v>
       </c>
       <c r="AH3">
-        <v>0.450000043630205</v>
+        <v>0.4500000436491957</v>
       </c>
       <c r="AI3">
-        <v>0.8999999761531058</v>
+        <v>0.899999976149662</v>
       </c>
       <c r="AJ3">
-        <v>0.4499999140052287</v>
+        <v>0.4499999140053736</v>
       </c>
       <c r="AK3">
-        <v>0.4500000621479745</v>
+        <v>0.4500000621669723</v>
       </c>
       <c r="AL3">
-        <v>6.908379230916166E-13</v>
+        <v>-2.389142860797283E-10</v>
       </c>
       <c r="AM3">
-        <v>-179.9999798987734</v>
+        <v>-179.9999799000816</v>
       </c>
       <c r="AN3">
-        <v>179.9999798987714</v>
+        <v>179.9999798998547</v>
       </c>
       <c r="AO3">
-        <v>6.908454937905569E-13</v>
+        <v>-2.355628544635772E-10</v>
       </c>
       <c r="AP3">
-        <v>-179.9999731983406</v>
+        <v>-179.9999731995704</v>
       </c>
       <c r="AQ3">
-        <v>179.9999731983425</v>
+        <v>179.9999731993541</v>
       </c>
     </row>
     <row r="4" spans="1:43">
@@ -3386,40 +3386,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>-1.661965745669962E-20</v>
+        <v>1.364242016484425E-13</v>
       </c>
       <c r="O4">
-        <v>-5.635971646124647E-16</v>
+        <v>-1.368753986842593E-13</v>
       </c>
       <c r="P4">
-        <v>-3.408588314185557E-16</v>
+        <v>-6.866328046957677E-14</v>
       </c>
       <c r="Q4">
-        <v>1.661965745669962E-20</v>
+        <v>-1.364242016487033E-13</v>
       </c>
       <c r="R4">
-        <v>6.53834923348175E-16</v>
+        <v>1.369656501915321E-13</v>
       </c>
       <c r="S4">
-        <v>4.310965899135352E-16</v>
+        <v>6.875352692275971E-14</v>
       </c>
       <c r="T4">
-        <v>-3.581075005151762E-23</v>
+        <v>-5.456968066034406E-13</v>
       </c>
       <c r="U4">
-        <v>1.286047188246662E-09</v>
+        <v>1.286207214335618E-09</v>
       </c>
       <c r="V4">
-        <v>-1.286047501614931E-09</v>
+        <v>-1.286071107764587E-09</v>
       </c>
       <c r="W4">
-        <v>3.581075005151762E-23</v>
+        <v>5.456968066040026E-13</v>
       </c>
       <c r="X4">
-        <v>-1.286047156493717E-09</v>
+        <v>-1.286207182567284E-09</v>
       </c>
       <c r="Y4">
-        <v>1.286047533367876E-09</v>
+        <v>1.286071139517975E-09</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -3440,40 +3440,40 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.8999999761531058</v>
+        <v>0.8999999761501329</v>
       </c>
       <c r="AG4">
-        <v>0.4499999325229551</v>
+        <v>0.4499999325235781</v>
       </c>
       <c r="AH4">
-        <v>0.450000043630205</v>
+        <v>0.4500000436491957</v>
       </c>
       <c r="AI4">
-        <v>0.8999999761531058</v>
+        <v>0.8999999761511064</v>
       </c>
       <c r="AJ4">
-        <v>0.4499999214123178</v>
+        <v>0.4499999214122856</v>
       </c>
       <c r="AK4">
-        <v>0.4500000547408666</v>
+        <v>0.450000054761486</v>
       </c>
       <c r="AL4">
-        <v>6.908379230916166E-13</v>
+        <v>-2.389142860797283E-10</v>
       </c>
       <c r="AM4">
-        <v>-179.9999798987734</v>
+        <v>-179.9999799000816</v>
       </c>
       <c r="AN4">
-        <v>179.9999798987714</v>
+        <v>179.9999798998547</v>
       </c>
       <c r="AO4">
-        <v>6.908424655112165E-13</v>
+        <v>-2.270187942885306E-10</v>
       </c>
       <c r="AP4">
-        <v>-179.9999758785137</v>
+        <v>-179.9999758795597</v>
       </c>
       <c r="AQ4">
-        <v>179.9999758785139</v>
+        <v>179.9999758793588</v>
       </c>
     </row>
   </sheetData>
@@ -3658,40 +3658,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-8.046812897941617E-22</v>
+        <v>-6.397672239927802E-17</v>
       </c>
       <c r="O2">
-        <v>-1.632596297176762E-12</v>
+        <v>-1.632661170121914E-12</v>
       </c>
       <c r="P2">
-        <v>-4.555904069893242E-12</v>
+        <v>-4.556013548594678E-12</v>
       </c>
       <c r="Q2">
-        <v>5.364541931961079E-22</v>
+        <v>6.402232100569914E-17</v>
       </c>
       <c r="R2">
-        <v>1.632596297890905E-12</v>
+        <v>1.632661306307792E-12</v>
       </c>
       <c r="S2">
-        <v>4.555904072722128E-12</v>
+        <v>4.556013363046914E-12</v>
       </c>
       <c r="T2">
-        <v>-3.982938124135857E-39</v>
+        <v>1.036107628738963E-17</v>
       </c>
       <c r="U2">
-        <v>4.319365415847804E-12</v>
+        <v>4.319120216859393E-12</v>
       </c>
       <c r="V2">
-        <v>7.439521622936176E-13</v>
+        <v>7.442119028409013E-13</v>
       </c>
       <c r="W2">
-        <v>2.769445745554612E-39</v>
+        <v>-1.018190058686215E-17</v>
       </c>
       <c r="X2">
-        <v>-4.319365413068145E-12</v>
+        <v>-4.31912034626939E-12</v>
       </c>
       <c r="Y2">
-        <v>-7.439521619969862E-13</v>
+        <v>-7.442119580393095E-13</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -3721,16 +3721,16 @@
         <v>0.9495638133650118</v>
       </c>
       <c r="AI2">
-        <v>0.9499999880790663</v>
+        <v>0.9499999880790583</v>
       </c>
       <c r="AJ2">
-        <v>0.9498436431019424</v>
+        <v>0.9498436431019519</v>
       </c>
       <c r="AK2">
-        <v>0.9495638134482837</v>
+        <v>0.9495638134482867</v>
       </c>
       <c r="AL2">
-        <v>2.835974285336046E-16</v>
+        <v>4.299027284504202E-16</v>
       </c>
       <c r="AM2">
         <v>-120.0249329865872</v>
@@ -3739,13 +3739,13 @@
         <v>119.9957043633572</v>
       </c>
       <c r="AO2">
-        <v>2.957895656763519E-16</v>
+        <v>-1.016764147924837E-13</v>
       </c>
       <c r="AP2">
-        <v>-120.0249329808643</v>
+        <v>-120.024932980865</v>
       </c>
       <c r="AQ2">
-        <v>119.9957043661035</v>
+        <v>119.9957043661044</v>
       </c>
     </row>
     <row r="3" spans="1:43">
@@ -3789,40 +3789,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>-1.655531423278421E-23</v>
+        <v>2.10942372031799E-16</v>
       </c>
       <c r="O3">
-        <v>-5.441987645220876E-13</v>
+        <v>-5.442626517679671E-13</v>
       </c>
       <c r="P3">
-        <v>-1.518634642824216E-12</v>
+        <v>-1.518850182419726E-12</v>
       </c>
       <c r="Q3">
-        <v>1.655531423278421E-23</v>
+        <v>-2.109423720317987E-16</v>
       </c>
       <c r="R3">
-        <v>5.441987645704418E-13</v>
+        <v>5.442626518163215E-13</v>
       </c>
       <c r="S3">
-        <v>1.518634642872571E-12</v>
+        <v>1.518850182468089E-12</v>
       </c>
       <c r="T3">
-        <v>-1.708394790148113E-26</v>
+        <v>-3.743358463448307E-31</v>
       </c>
       <c r="U3">
-        <v>1.439788412060066E-12</v>
+        <v>1.439717871428829E-12</v>
       </c>
       <c r="V3">
-        <v>2.479840293351087E-13</v>
+        <v>2.480362364637127E-13</v>
       </c>
       <c r="W3">
-        <v>1.708394790148113E-26</v>
+        <v>4.465081313067287E-31</v>
       </c>
       <c r="X3">
-        <v>-1.439788412043051E-12</v>
+        <v>-1.439717871411813E-12</v>
       </c>
       <c r="Y3">
-        <v>-2.479840293180937E-13</v>
+        <v>-2.48036236446698E-13</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -3843,40 +3843,40 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.9499999880790663</v>
+        <v>0.9499999880790583</v>
       </c>
       <c r="AG3">
-        <v>0.9498436431019424</v>
+        <v>0.9498436431019519</v>
       </c>
       <c r="AH3">
-        <v>0.9495638134482837</v>
+        <v>0.9495638134482867</v>
       </c>
       <c r="AI3">
-        <v>0.9499999880790663</v>
+        <v>0.9499999880790572</v>
       </c>
       <c r="AJ3">
-        <v>0.9498436431026707</v>
+        <v>0.949843643102681</v>
       </c>
       <c r="AK3">
-        <v>0.9495638134760409</v>
+        <v>0.9495638134760451</v>
       </c>
       <c r="AL3">
-        <v>2.957895656763519E-16</v>
+        <v>-1.016764147924837E-13</v>
       </c>
       <c r="AM3">
-        <v>-120.0249329808643</v>
+        <v>-120.024932980865</v>
       </c>
       <c r="AN3">
-        <v>119.9957043661035</v>
+        <v>119.9957043661044</v>
       </c>
       <c r="AO3">
-        <v>2.957963558552057E-16</v>
+        <v>-1.212797182269817E-13</v>
       </c>
       <c r="AP3">
-        <v>-120.0249329789567</v>
+        <v>-120.0249329789573</v>
       </c>
       <c r="AQ3">
-        <v>119.9957043670189</v>
+        <v>119.9957043670198</v>
       </c>
     </row>
     <row r="4" spans="1:43">
@@ -3920,40 +3920,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>-1.65553147948476E-23</v>
+        <v>-3.515706200529883E-17</v>
       </c>
       <c r="O4">
-        <v>-5.441987642684503E-13</v>
+        <v>-5.439502074556133E-13</v>
       </c>
       <c r="P4">
-        <v>-1.518634681236922E-12</v>
+        <v>-1.519163929108881E-12</v>
       </c>
       <c r="Q4">
-        <v>1.65553147948476E-23</v>
+        <v>3.515706200529914E-17</v>
       </c>
       <c r="R4">
-        <v>5.441987642974629E-13</v>
+        <v>5.439502074846185E-13</v>
       </c>
       <c r="S4">
-        <v>1.518634681265935E-12</v>
+        <v>1.519163929137904E-12</v>
       </c>
       <c r="T4">
-        <v>-1.708385422424981E-26</v>
+        <v>5.625129920847973E-16</v>
       </c>
       <c r="U4">
-        <v>1.439788463951289E-12</v>
+        <v>1.43941550208547E-12</v>
       </c>
       <c r="V4">
-        <v>2.479840529771854E-13</v>
+        <v>2.480174280237441E-13</v>
       </c>
       <c r="W4">
-        <v>1.708385422424981E-26</v>
+        <v>-5.625129920847978E-16</v>
       </c>
       <c r="X4">
-        <v>-1.43978846394108E-12</v>
+        <v>-1.439415502075267E-12</v>
       </c>
       <c r="Y4">
-        <v>-2.479840529669763E-13</v>
+        <v>-2.480174280135305E-13</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -3974,40 +3974,40 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.9499999880790663</v>
+        <v>0.9499999880790583</v>
       </c>
       <c r="AG4">
-        <v>0.9498436431019424</v>
+        <v>0.9498436431019519</v>
       </c>
       <c r="AH4">
-        <v>0.9495638134482837</v>
+        <v>0.9495638134482867</v>
       </c>
       <c r="AI4">
-        <v>0.9499999880790663</v>
+        <v>0.9499999880790592</v>
       </c>
       <c r="AJ4">
-        <v>0.9498436431023793</v>
+        <v>0.9498436431023898</v>
       </c>
       <c r="AK4">
-        <v>0.9495638134649381</v>
+        <v>0.9495638134649412</v>
       </c>
       <c r="AL4">
-        <v>2.957895656763519E-16</v>
+        <v>-1.016764147924837E-13</v>
       </c>
       <c r="AM4">
-        <v>-120.0249329808643</v>
+        <v>-120.024932980865</v>
       </c>
       <c r="AN4">
-        <v>119.9957043661035</v>
+        <v>119.9957043661044</v>
       </c>
       <c r="AO4">
-        <v>2.957936397838754E-16</v>
+        <v>-7.330696188076414E-14</v>
       </c>
       <c r="AP4">
-        <v>-120.0249329797197</v>
+        <v>-120.0249329797204</v>
       </c>
       <c r="AQ4">
-        <v>119.9957043666528</v>
+        <v>119.9957043666537</v>
       </c>
     </row>
   </sheetData>
@@ -4192,40 +4192,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>7.623296323340277E-22</v>
+        <v>-9.503607772479901E-17</v>
       </c>
       <c r="O2">
-        <v>-1.388207921681025E-12</v>
+        <v>-1.387939412424147E-12</v>
       </c>
       <c r="P2">
-        <v>-3.873916742452908E-12</v>
+        <v>-3.873900348675338E-12</v>
       </c>
       <c r="Q2">
-        <v>-1.016439509778704E-21</v>
+        <v>9.4954000234385E-17</v>
       </c>
       <c r="R2">
-        <v>1.388207924485634E-12</v>
+        <v>1.387939527054994E-12</v>
       </c>
       <c r="S2">
-        <v>3.873916742295541E-12</v>
+        <v>3.873900320283455E-12</v>
       </c>
       <c r="T2">
-        <v>-2.032879019557407E-21</v>
+        <v>1.166110227593618E-16</v>
       </c>
       <c r="U2">
-        <v>3.672730775079093E-12</v>
+        <v>3.672594386085305E-12</v>
       </c>
       <c r="V2">
-        <v>6.326431834161806E-13</v>
+        <v>6.329270383171852E-13</v>
       </c>
       <c r="W2">
-        <v>2.032879019557407E-21</v>
+        <v>-1.165281829393136E-16</v>
       </c>
       <c r="X2">
-        <v>-3.672730775787036E-12</v>
+        <v>-3.672594357808761E-12</v>
       </c>
       <c r="Y2">
-        <v>-6.326431824129066E-13</v>
+        <v>-6.329271509817989E-13</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -4255,16 +4255,16 @@
         <v>0.8996084987865827</v>
       </c>
       <c r="AI2">
-        <v>0.8999999761581381</v>
+        <v>0.8999999761581348</v>
       </c>
       <c r="AJ2">
-        <v>0.899859654781918</v>
+        <v>0.8998596547819119</v>
       </c>
       <c r="AK2">
-        <v>0.8996084988613209</v>
+        <v>0.8996084988613245</v>
       </c>
       <c r="AL2">
-        <v>2.715765678349059E-16</v>
+        <v>5.250323187535518E-16</v>
       </c>
       <c r="AM2">
         <v>-120.0236211964411</v>
@@ -4273,13 +4273,13 @@
         <v>119.9959300125619</v>
       </c>
       <c r="AO2">
-        <v>2.785046687906037E-16</v>
+        <v>4.78480848704322E-13</v>
       </c>
       <c r="AP2">
-        <v>-120.0236211910194</v>
+        <v>-120.0236211910201</v>
       </c>
       <c r="AQ2">
-        <v>119.9959300151637</v>
+        <v>119.9959300151642</v>
       </c>
     </row>
     <row r="3" spans="1:43">
@@ -4323,40 +4323,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>-1.311428722481762E-23</v>
+        <v>-3.330668985642843E-17</v>
       </c>
       <c r="O3">
-        <v>-4.627359722779878E-13</v>
+        <v>-4.628734123138742E-13</v>
       </c>
       <c r="P3">
-        <v>-1.291305540617543E-12</v>
+        <v>-1.291114648064885E-12</v>
       </c>
       <c r="Q3">
-        <v>1.311428722481762E-23</v>
+        <v>3.330668985642839E-17</v>
       </c>
       <c r="R3">
-        <v>4.627359723169397E-13</v>
+        <v>4.628734123528347E-13</v>
       </c>
       <c r="S3">
-        <v>1.291305540656495E-12</v>
+        <v>1.291114648103832E-12</v>
       </c>
       <c r="T3">
-        <v>-1.44369529047624E-26</v>
+        <v>-2.781463724810194E-31</v>
       </c>
       <c r="U3">
-        <v>1.224243541841E-12</v>
+        <v>1.224458693775623E-12</v>
       </c>
       <c r="V3">
-        <v>2.108810440935117E-13</v>
+        <v>2.108962382494101E-13</v>
       </c>
       <c r="W3">
-        <v>1.44369529047624E-26</v>
+        <v>3.029923594547509E-31</v>
       </c>
       <c r="X3">
-        <v>-1.224243541827294E-12</v>
+        <v>-1.224458693761912E-12</v>
       </c>
       <c r="Y3">
-        <v>-2.108810440798053E-13</v>
+        <v>-2.108962382357079E-13</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -4377,40 +4377,40 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.8999999761581381</v>
+        <v>0.8999999761581348</v>
       </c>
       <c r="AG3">
-        <v>0.899859654781918</v>
+        <v>0.8998596547819119</v>
       </c>
       <c r="AH3">
-        <v>0.8996084988613209</v>
+        <v>0.8996084988613245</v>
       </c>
       <c r="AI3">
-        <v>0.8999999761581381</v>
+        <v>0.8999999761581334</v>
       </c>
       <c r="AJ3">
-        <v>0.8998596547825717</v>
+        <v>0.899859654782566</v>
       </c>
       <c r="AK3">
-        <v>0.8996084988862336</v>
+        <v>0.8996084988862372</v>
       </c>
       <c r="AL3">
-        <v>2.785046687906037E-16</v>
+        <v>4.78480848704322E-13</v>
       </c>
       <c r="AM3">
-        <v>-120.0236211910194</v>
+        <v>-120.0236211910201</v>
       </c>
       <c r="AN3">
-        <v>119.9959300151637</v>
+        <v>119.9959300151642</v>
       </c>
       <c r="AO3">
-        <v>2.785106607016237E-16</v>
+        <v>5.212221177276993E-13</v>
       </c>
       <c r="AP3">
-        <v>-120.0236211892121</v>
+        <v>-120.0236211892127</v>
       </c>
       <c r="AQ3">
-        <v>119.995930016031</v>
+        <v>119.9959300160315</v>
       </c>
     </row>
     <row r="4" spans="1:43">
@@ -4454,40 +4454,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>-1.311428766855187E-23</v>
+        <v>3.330668985642732E-17</v>
       </c>
       <c r="O4">
-        <v>-4.627359735643333E-13</v>
+        <v>-4.62801042761211E-13</v>
       </c>
       <c r="P4">
-        <v>-1.291305578733435E-12</v>
+        <v>-1.291684163614508E-12</v>
       </c>
       <c r="Q4">
-        <v>1.311428766855187E-23</v>
+        <v>-3.330668985642729E-17</v>
       </c>
       <c r="R4">
-        <v>4.627359735877046E-13</v>
+        <v>4.628010427845785E-13</v>
       </c>
       <c r="S4">
-        <v>1.291305578756806E-12</v>
+        <v>1.291684163637885E-12</v>
       </c>
       <c r="T4">
-        <v>-1.443683457562975E-26</v>
+        <v>1.33226759425714E-16</v>
       </c>
       <c r="U4">
-        <v>1.22424358836179E-12</v>
+        <v>1.224051478465681E-12</v>
       </c>
       <c r="V4">
-        <v>2.108810572846396E-13</v>
+        <v>2.108173483902819E-13</v>
       </c>
       <c r="W4">
-        <v>1.443683457562975E-26</v>
+        <v>-1.332267594257142E-16</v>
       </c>
       <c r="X4">
-        <v>-1.224243588353566E-12</v>
+        <v>-1.224051478457457E-12</v>
       </c>
       <c r="Y4">
-        <v>-2.108810572764158E-13</v>
+        <v>-2.108173483820534E-13</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -4508,40 +4508,40 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.8999999761581381</v>
+        <v>0.8999999761581348</v>
       </c>
       <c r="AG4">
-        <v>0.899859654781918</v>
+        <v>0.8998596547819119</v>
       </c>
       <c r="AH4">
-        <v>0.8996084988613209</v>
+        <v>0.8996084988613245</v>
       </c>
       <c r="AI4">
-        <v>0.8999999761581381</v>
+        <v>0.8999999761581355</v>
       </c>
       <c r="AJ4">
-        <v>0.8998596547823102</v>
+        <v>0.8998596547823049</v>
       </c>
       <c r="AK4">
-        <v>0.8996084988762685</v>
+        <v>0.8996084988762724</v>
       </c>
       <c r="AL4">
-        <v>2.785046687906037E-16</v>
+        <v>4.78480848704322E-13</v>
       </c>
       <c r="AM4">
-        <v>-120.0236211910194</v>
+        <v>-120.0236211910201</v>
       </c>
       <c r="AN4">
-        <v>119.9959300151637</v>
+        <v>119.9959300151642</v>
       </c>
       <c r="AO4">
-        <v>2.78508263937402E-16</v>
+        <v>5.053581779289299E-13</v>
       </c>
       <c r="AP4">
-        <v>-120.023621189935</v>
+        <v>-120.0236211899357</v>
       </c>
       <c r="AQ4">
-        <v>119.9959300156841</v>
+        <v>119.9959300156846</v>
       </c>
     </row>
   </sheetData>
@@ -4693,13 +4693,13 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>4.668202856459293E-05</v>
+        <v>4.668202556953209E-05</v>
       </c>
       <c r="C2">
-        <v>4.668198697115369E-05</v>
+        <v>4.66819889408912E-05</v>
       </c>
       <c r="D2">
-        <v>4.668198697115398E-05</v>
+        <v>4.668199433406139E-05</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -4711,13 +4711,13 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>1.078075286387995E-05</v>
+        <v>1.078075217220026E-05</v>
       </c>
       <c r="I2">
-        <v>1.078074325828647E-05</v>
+        <v>1.078074371317787E-05</v>
       </c>
       <c r="J2">
-        <v>1.078074325828653E-05</v>
+        <v>1.078074495867719E-05</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -4729,49 +4729,49 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>3.24214179123027E-17</v>
+        <v>3.286206158497823E-17</v>
       </c>
       <c r="O2">
-        <v>9.804891632219654E-06</v>
+        <v>9.804891532009263E-06</v>
       </c>
       <c r="P2">
-        <v>-9.801541438346653E-06</v>
+        <v>-9.801543301252365E-06</v>
       </c>
       <c r="Q2">
-        <v>-1.610664795704137E-12</v>
+        <v>-1.610710825613703E-12</v>
       </c>
       <c r="R2">
-        <v>1.263484781822502E-12</v>
+        <v>1.36450497437855E-12</v>
       </c>
       <c r="S2">
-        <v>-2.880029598895975E-12</v>
+        <v>-1.017280181115579E-12</v>
       </c>
       <c r="T2">
-        <v>-1.794036406641227E-17</v>
+        <v>-1.756872195100537E-17</v>
       </c>
       <c r="U2">
-        <v>-5.656991364496376E-06</v>
+        <v>-5.656992493946725E-06</v>
       </c>
       <c r="V2">
-        <v>-5.662795332437378E-06</v>
+        <v>-5.662795676986525E-06</v>
       </c>
       <c r="W2">
-        <v>2.392729301165479E-12</v>
+        <v>2.39248776282074E-12</v>
       </c>
       <c r="X2">
-        <v>-2.594915532326029E-12</v>
+        <v>-1.465953470886837E-12</v>
       </c>
       <c r="Y2">
-        <v>2.026473529682125E-13</v>
+        <v>5.469834515202112E-13</v>
       </c>
       <c r="Z2">
-        <v>-90.07834493200572</v>
+        <v>-90.07834121635071</v>
       </c>
       <c r="AA2">
-        <v>-90.01696090547081</v>
+        <v>-90.01695570026567</v>
       </c>
       <c r="AB2">
-        <v>-90.01696090544348</v>
+        <v>-90.01695769846786</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -4786,19 +4786,19 @@
         <v>0</v>
       </c>
       <c r="AH2">
-        <v>1.050000091913128</v>
+        <v>1.050000091913162</v>
       </c>
       <c r="AI2">
-        <v>1.050000150613765</v>
+        <v>1.050000150613781</v>
       </c>
       <c r="AJ2">
-        <v>0.0002496929323590718</v>
+        <v>0.000249692941218148</v>
       </c>
       <c r="AK2">
-        <v>1.049890524026351</v>
+        <v>1.049890524050607</v>
       </c>
       <c r="AL2">
-        <v>1.050249245583347</v>
+        <v>1.050249245617572</v>
       </c>
       <c r="AM2">
         <v>0</v>
@@ -4807,16 +4807,16 @@
         <v>-120.0000168926288</v>
       </c>
       <c r="AO2">
-        <v>120.0000150432931</v>
+        <v>120.0000150432961</v>
       </c>
       <c r="AP2">
-        <v>123.935149789476</v>
+        <v>123.9351577144078</v>
       </c>
       <c r="AQ2">
-        <v>-120.0122607512</v>
+        <v>-120.0122607531929</v>
       </c>
       <c r="AR2">
-        <v>120.0009571465917</v>
+        <v>120.0009571485533</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -4860,40 +4860,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>5.368882704777873E-13</v>
+        <v>5.369100773532747E-13</v>
       </c>
       <c r="O3">
-        <v>-4.211624457410767E-13</v>
+        <v>-3.774897014441403E-13</v>
       </c>
       <c r="P3">
-        <v>9.600074421510766E-13</v>
+        <v>9.801036531844791E-13</v>
       </c>
       <c r="Q3">
-        <v>-5.367460757091319E-13</v>
+        <v>-5.368152897533938E-13</v>
       </c>
       <c r="R3">
-        <v>4.211624457491297E-13</v>
+        <v>3.774896971402653E-13</v>
       </c>
       <c r="S3">
-        <v>-9.600074421430237E-13</v>
+        <v>-9.80103644632892E-13</v>
       </c>
       <c r="T3">
-        <v>-7.975764188850102E-13</v>
+        <v>-7.976105387933883E-13</v>
       </c>
       <c r="U3">
-        <v>8.649662225654034E-13</v>
+        <v>1.471315351517488E-12</v>
       </c>
       <c r="V3">
-        <v>-6.754741461157706E-14</v>
+        <v>5.364883993144775E-13</v>
       </c>
       <c r="W3">
-        <v>7.976724872833206E-13</v>
+        <v>7.976746122408424E-13</v>
       </c>
       <c r="X3">
-        <v>-8.649662225599628E-13</v>
+        <v>-1.47131537256756E-12</v>
       </c>
       <c r="Y3">
-        <v>6.754741461701775E-14</v>
+        <v>-5.364884126125196E-13</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -4914,40 +4914,40 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>0.0002496929323590718</v>
+        <v>0.000249692941218148</v>
       </c>
       <c r="AH3">
-        <v>1.049890524026351</v>
+        <v>1.049890524050607</v>
       </c>
       <c r="AI3">
-        <v>1.050249245583347</v>
+        <v>1.050249245617572</v>
       </c>
       <c r="AJ3">
-        <v>0.0002496930117500629</v>
+        <v>0.0002496930005813501</v>
       </c>
       <c r="AK3">
-        <v>1.049890524024861</v>
+        <v>1.049890537404389</v>
       </c>
       <c r="AL3">
-        <v>1.050249245574997</v>
+        <v>1.050249244568355</v>
       </c>
       <c r="AM3">
-        <v>123.935149789476</v>
+        <v>123.9351577144078</v>
       </c>
       <c r="AN3">
-        <v>-120.0122607512</v>
+        <v>-120.0122607531929</v>
       </c>
       <c r="AO3">
-        <v>120.0009571465917</v>
+        <v>120.0009571485533</v>
       </c>
       <c r="AP3">
-        <v>123.924923248027</v>
+        <v>123.9283398205222</v>
       </c>
       <c r="AQ3">
-        <v>-120.012260750627</v>
+        <v>-120.0122611077683</v>
       </c>
       <c r="AR3">
-        <v>120.000957146235</v>
+        <v>120.0009579572739</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -4991,40 +4991,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>5.368882647634949E-13</v>
+        <v>5.370222280211683E-13</v>
       </c>
       <c r="O4">
-        <v>-4.211624467934052E-13</v>
+        <v>-5.102297231459777E-13</v>
       </c>
       <c r="P4">
-        <v>9.600074574857024E-13</v>
+        <v>1.824503535854225E-12</v>
       </c>
       <c r="Q4">
-        <v>-5.368029479011657E-13</v>
+        <v>-5.369653735677651E-13</v>
       </c>
       <c r="R4">
-        <v>4.211624467982369E-13</v>
+        <v>5.102297228704195E-13</v>
       </c>
       <c r="S4">
-        <v>-9.600074574808706E-13</v>
+        <v>-1.824503541192246E-12</v>
       </c>
       <c r="T4">
-        <v>-7.975764310831121E-13</v>
+        <v>-7.974833427898033E-13</v>
       </c>
       <c r="U4">
-        <v>8.649662491904142E-13</v>
+        <v>1.122668027032411E-12</v>
       </c>
       <c r="V4">
-        <v>-6.754742219341023E-14</v>
+        <v>-7.59652602454106E-13</v>
       </c>
       <c r="W4">
-        <v>7.976340721229673E-13</v>
+        <v>7.975217798514182E-13</v>
       </c>
       <c r="X4">
-        <v>-8.6496624918715E-13</v>
+        <v>-1.12266803749779E-12</v>
       </c>
       <c r="Y4">
-        <v>6.754742219667458E-14</v>
+        <v>7.596525865601924E-13</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -5045,40 +5045,40 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>0.0002496929323590718</v>
+        <v>0.000249692941218148</v>
       </c>
       <c r="AH4">
-        <v>1.049890524026351</v>
+        <v>1.049890524050607</v>
       </c>
       <c r="AI4">
-        <v>1.050249245583347</v>
+        <v>1.050249245617572</v>
       </c>
       <c r="AJ4">
-        <v>0.0002496929790394573</v>
+        <v>0.0002496929744879526</v>
       </c>
       <c r="AK4">
-        <v>1.049890524025457</v>
+        <v>1.049890532065048</v>
       </c>
       <c r="AL4">
-        <v>1.050249245578337</v>
+        <v>1.050249244989821</v>
       </c>
       <c r="AM4">
-        <v>123.935149789476</v>
+        <v>123.9351577144078</v>
       </c>
       <c r="AN4">
-        <v>-120.0122607512</v>
+        <v>-120.0122607531929</v>
       </c>
       <c r="AO4">
-        <v>120.0009571465917</v>
+        <v>120.0009571485533</v>
       </c>
       <c r="AP4">
-        <v>123.9290138637829</v>
+        <v>123.9310679221861</v>
       </c>
       <c r="AQ4">
-        <v>-120.0122607508562</v>
+        <v>-120.0122609660332</v>
       </c>
       <c r="AR4">
-        <v>120.0009571463777</v>
+        <v>120.0009576334187</v>
       </c>
     </row>
   </sheetData>
@@ -5230,13 +5230,13 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>4.890498708558385E-05</v>
+        <v>4.890498219944334E-05</v>
       </c>
       <c r="C2">
-        <v>4.89049435114013E-05</v>
+        <v>4.890494579526724E-05</v>
       </c>
       <c r="D2">
-        <v>4.890494351141195E-05</v>
+        <v>4.890495111268913E-05</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -5248,13 +5248,13 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>1.129412315172635E-05</v>
+        <v>1.129412202332052E-05</v>
       </c>
       <c r="I2">
-        <v>1.129411308869979E-05</v>
+        <v>1.129411361613605E-05</v>
       </c>
       <c r="J2">
-        <v>1.129411308870225E-05</v>
+        <v>1.129411484414204E-05</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -5266,49 +5266,49 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>2.076366284187988E-17</v>
+        <v>2.135287909528525E-17</v>
       </c>
       <c r="O2">
-        <v>1.076092592341311E-05</v>
+        <v>1.076092622115764E-05</v>
       </c>
       <c r="P2">
-        <v>-1.075724906572977E-05</v>
+        <v>-1.075725076622441E-05</v>
       </c>
       <c r="Q2">
-        <v>-1.767714059137121E-12</v>
+        <v>-1.767779866149755E-12</v>
       </c>
       <c r="R2">
-        <v>1.386603959051428E-12</v>
+        <v>1.089486354258826E-12</v>
       </c>
       <c r="S2">
-        <v>-3.160953366207822E-12</v>
+        <v>-1.460524997665102E-12</v>
       </c>
       <c r="T2">
-        <v>-4.347694785115411E-17</v>
+        <v>-4.309746214944724E-17</v>
       </c>
       <c r="U2">
-        <v>-6.208581272084943E-06</v>
+        <v>-6.20858191697897E-06</v>
       </c>
       <c r="V2">
-        <v>-6.214951227345683E-06</v>
+        <v>-6.21495214400529E-06</v>
       </c>
       <c r="W2">
-        <v>2.626034424928642E-12</v>
+        <v>2.625603323999935E-12</v>
       </c>
       <c r="X2">
-        <v>-2.848095457086843E-12</v>
+        <v>-2.203463185600851E-12</v>
       </c>
       <c r="Y2">
-        <v>2.22561152882024E-13</v>
+        <v>1.139196425779224E-12</v>
       </c>
       <c r="Z2">
-        <v>-90.07834510634639</v>
+        <v>-90.07833889006311</v>
       </c>
       <c r="AA2">
-        <v>-90.01696108250498</v>
+        <v>-90.01695919258627</v>
       </c>
       <c r="AB2">
-        <v>-90.01696108250157</v>
+        <v>-90.01696081976522</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -5323,37 +5323,37 @@
         <v>0</v>
       </c>
       <c r="AH2">
-        <v>1.100000177048324</v>
+        <v>1.100000177048342</v>
       </c>
       <c r="AI2">
-        <v>1.100000241472614</v>
+        <v>1.100000241472646</v>
       </c>
       <c r="AJ2">
-        <v>0.0002615830998269562</v>
+        <v>0.0002615831000558032</v>
       </c>
       <c r="AK2">
-        <v>1.099885391634488</v>
+        <v>1.099885391647033</v>
       </c>
       <c r="AL2">
-        <v>1.1002611981332</v>
+        <v>1.100261198165473</v>
       </c>
       <c r="AM2">
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>-120.0000176970404</v>
+        <v>-120.000017697041</v>
       </c>
       <c r="AO2">
-        <v>120.000015759641</v>
+        <v>120.0000157596435</v>
       </c>
       <c r="AP2">
-        <v>123.9351498358517</v>
+        <v>123.9351571320616</v>
       </c>
       <c r="AQ2">
-        <v>-120.0122615559749</v>
+        <v>-120.0122615574227</v>
       </c>
       <c r="AR2">
-        <v>120.0009578627482</v>
+        <v>120.0009578638979</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -5397,40 +5397,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>5.892380224056025E-13</v>
+        <v>5.893920642716105E-13</v>
       </c>
       <c r="O3">
-        <v>-4.622001605687392E-13</v>
+        <v>-4.571292236221197E-13</v>
       </c>
       <c r="P3">
-        <v>1.05365369010372E-12</v>
+        <v>8.98811152693879E-13</v>
       </c>
       <c r="Q3">
-        <v>-5.890819628208454E-13</v>
+        <v>-5.892880570876155E-13</v>
       </c>
       <c r="R3">
-        <v>4.62200160577578E-13</v>
+        <v>4.571292238593897E-13</v>
       </c>
       <c r="S3">
-        <v>-1.053653690094881E-12</v>
+        <v>-8.988111530341065E-13</v>
       </c>
       <c r="T3">
-        <v>-8.753447913207387E-13</v>
+        <v>-8.752521840709896E-13</v>
       </c>
       <c r="U3">
-        <v>9.493677831905437E-13</v>
+        <v>9.012764986085056E-13</v>
       </c>
       <c r="V3">
-        <v>-7.418915443213963E-14</v>
+        <v>-8.766921201200159E-14</v>
       </c>
       <c r="W3">
-        <v>8.754502269464638E-13</v>
+        <v>8.753225131441131E-13</v>
       </c>
       <c r="X3">
-        <v>-9.49367783184572E-13</v>
+        <v>-9.012765129032806E-13</v>
       </c>
       <c r="Y3">
-        <v>7.418915443811124E-14</v>
+        <v>8.766919924198959E-14</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -5451,40 +5451,40 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>0.0002615830998269562</v>
+        <v>0.0002615831000558032</v>
       </c>
       <c r="AH3">
-        <v>1.099885391634488</v>
+        <v>1.099885391647033</v>
       </c>
       <c r="AI3">
-        <v>1.1002611981332</v>
+        <v>1.100261198165473</v>
       </c>
       <c r="AJ3">
-        <v>0.0002615831829985295</v>
+        <v>0.0002615831617362572</v>
       </c>
       <c r="AK3">
-        <v>1.099885391632925</v>
+        <v>1.099885405639189</v>
       </c>
       <c r="AL3">
-        <v>1.100261198124453</v>
+        <v>1.100261197067655</v>
       </c>
       <c r="AM3">
-        <v>123.9351498358517</v>
+        <v>123.9351571320616</v>
       </c>
       <c r="AN3">
-        <v>-120.0122615559749</v>
+        <v>-120.0122615574227</v>
       </c>
       <c r="AO3">
-        <v>120.0009578627482</v>
+        <v>120.0009578638979</v>
       </c>
       <c r="AP3">
-        <v>123.9249232948346</v>
+        <v>123.9283397882917</v>
       </c>
       <c r="AQ3">
-        <v>-120.0122615554018</v>
+        <v>-120.0122619120316</v>
       </c>
       <c r="AR3">
-        <v>120.0009578623914</v>
+        <v>120.0009586723612</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -5528,40 +5528,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>5.892380124033823E-13</v>
+        <v>5.891734112347256E-13</v>
       </c>
       <c r="O4">
-        <v>-4.622001518702175E-13</v>
+        <v>2.571436936052959E-13</v>
       </c>
       <c r="P4">
-        <v>1.053653719082024E-12</v>
+        <v>1.283078697136875E-12</v>
       </c>
       <c r="Q4">
-        <v>-5.891443766512268E-13</v>
+        <v>-5.891110066753583E-13</v>
       </c>
       <c r="R4">
-        <v>4.622001518755208E-13</v>
+        <v>-2.571437003912154E-13</v>
       </c>
       <c r="S4">
-        <v>-1.053653719076721E-12</v>
+        <v>-1.283078707223374E-12</v>
       </c>
       <c r="T4">
-        <v>-8.753448068017992E-13</v>
+        <v>-8.753328238539989E-13</v>
       </c>
       <c r="U4">
-        <v>9.493677982493821E-13</v>
+        <v>1.298329818510279E-12</v>
       </c>
       <c r="V4">
-        <v>-7.418915491913704E-14</v>
+        <v>-1.282531069910583E-12</v>
       </c>
       <c r="W4">
-        <v>8.754080681777886E-13</v>
+        <v>8.753749936597421E-13</v>
       </c>
       <c r="X4">
-        <v>-9.493677982457989E-13</v>
+        <v>-1.298329827465978E-12</v>
       </c>
       <c r="Y4">
-        <v>7.418915492272001E-14</v>
+        <v>1.282531058285943E-12</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -5582,40 +5582,40 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>0.0002615830998269562</v>
+        <v>0.0002615831000558032</v>
       </c>
       <c r="AH4">
-        <v>1.099885391634488</v>
+        <v>1.099885391647033</v>
       </c>
       <c r="AI4">
-        <v>1.1002611981332</v>
+        <v>1.100261198165473</v>
       </c>
       <c r="AJ4">
-        <v>0.0002615831487302761</v>
+        <v>0.000261583134910041</v>
       </c>
       <c r="AK4">
-        <v>1.09988539163355</v>
+        <v>1.099885400043115</v>
       </c>
       <c r="AL4">
-        <v>1.100261198127952</v>
+        <v>1.100261197507829</v>
       </c>
       <c r="AM4">
-        <v>123.9351498358517</v>
+        <v>123.9351571320616</v>
       </c>
       <c r="AN4">
-        <v>-120.0122615559749</v>
+        <v>-120.0122615574227</v>
       </c>
       <c r="AO4">
-        <v>120.0009578627482</v>
+        <v>120.0009578638979</v>
       </c>
       <c r="AP4">
-        <v>123.9290139104254</v>
+        <v>123.9310673399011</v>
       </c>
       <c r="AQ4">
-        <v>-120.0122615556311</v>
+        <v>-120.0122617702629</v>
       </c>
       <c r="AR4">
-        <v>120.0009578625341</v>
+        <v>120.0009583487632</v>
       </c>
     </row>
   </sheetData>
@@ -5803,40 +5803,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.699585652327409E-09</v>
+        <v>1.699585853519369E-09</v>
       </c>
       <c r="O2">
-        <v>9.520637003500426E-10</v>
+        <v>9.520639400358307E-10</v>
       </c>
       <c r="P2">
-        <v>-2.653878382870921E-09</v>
+        <v>-2.65387874596528E-09</v>
       </c>
       <c r="Q2">
-        <v>2.229875818810663E-12</v>
+        <v>2.2296745165191E-12</v>
       </c>
       <c r="R2">
-        <v>-1.578139348696765E-16</v>
+        <v>-3.973226974467399E-16</v>
       </c>
       <c r="S2">
-        <v>-4.989517067939976E-16</v>
+        <v>-1.359225826464741E-16</v>
       </c>
       <c r="T2">
-        <v>2.083076794396576E-09</v>
+        <v>2.083076756362282E-09</v>
       </c>
       <c r="U2">
-        <v>-2.514760563981422E-09</v>
+        <v>-2.514760778137558E-09</v>
       </c>
       <c r="V2">
-        <v>4.328689311409998E-10</v>
+        <v>4.328686652360272E-10</v>
       </c>
       <c r="W2">
-        <v>-1.8237093785709E-12</v>
+        <v>-1.823671205655193E-12</v>
       </c>
       <c r="X2">
-        <v>-6.672542881461968E-16</v>
+        <v>-4.530701392298908E-16</v>
       </c>
       <c r="Y2">
-        <v>4.702964145597831E-16</v>
+        <v>7.360349179036026E-16</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -5866,16 +5866,16 @@
         <v>1.049999952311284</v>
       </c>
       <c r="AJ2">
-        <v>1.049806842073367</v>
+        <v>1.04980684207336</v>
       </c>
       <c r="AK2">
-        <v>1.049999965979676</v>
+        <v>1.049999965979674</v>
       </c>
       <c r="AL2">
-        <v>1.04999999551561</v>
+        <v>1.049999995515623</v>
       </c>
       <c r="AM2">
-        <v>-0.008618545935952278</v>
+        <v>-0.008618545935952612</v>
       </c>
       <c r="AN2">
         <v>-120.0000000019556</v>
@@ -5884,13 +5884,13 @@
         <v>120.0000000043885</v>
       </c>
       <c r="AP2">
-        <v>-0.008617611622191802</v>
+        <v>-0.008617611621991213</v>
       </c>
       <c r="AQ2">
-        <v>-120.0000031524007</v>
+        <v>-120.0000031524013</v>
       </c>
       <c r="AR2">
-        <v>120.0000022218855</v>
+        <v>120.0000022218857</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -5934,40 +5934,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>-7.432919357631377E-13</v>
+        <v>-7.433725853457665E-13</v>
       </c>
       <c r="O3">
-        <v>5.260405717911544E-17</v>
+        <v>1.487439733350487E-16</v>
       </c>
       <c r="P3">
-        <v>1.663174038602972E-16</v>
+        <v>7.205825376972394E-17</v>
       </c>
       <c r="Q3">
-        <v>7.432919357711612E-13</v>
+        <v>7.433725853511148E-13</v>
       </c>
       <c r="R3">
-        <v>-5.260405717911499E-17</v>
+        <v>-1.487439733353334E-16</v>
       </c>
       <c r="S3">
-        <v>-1.663174038602968E-16</v>
+        <v>-7.205825376966217E-17</v>
       </c>
       <c r="T3">
-        <v>6.079031085936443E-13</v>
+        <v>6.078820544856425E-13</v>
       </c>
       <c r="U3">
-        <v>2.224177461848796E-16</v>
+        <v>2.604781167398264E-16</v>
       </c>
       <c r="V3">
-        <v>-1.567653128622389E-16</v>
+        <v>-4.269107877867973E-17</v>
       </c>
       <c r="W3">
-        <v>-6.079031085882233E-13</v>
+        <v>-6.078820544820276E-13</v>
       </c>
       <c r="X3">
-        <v>-2.224177461848793E-16</v>
+        <v>-2.604781167407933E-16</v>
       </c>
       <c r="Y3">
-        <v>1.567653128622392E-16</v>
+        <v>4.269107877840507E-17</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -5988,40 +5988,40 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>1.049806842073367</v>
+        <v>1.04980684207336</v>
       </c>
       <c r="AH3">
-        <v>1.049999965979676</v>
+        <v>1.049999965979674</v>
       </c>
       <c r="AI3">
-        <v>1.04999999551561</v>
+        <v>1.049999995515623</v>
       </c>
       <c r="AJ3">
-        <v>1.049806842076406</v>
+        <v>1.049806842075384</v>
       </c>
       <c r="AK3">
-        <v>1.049999965979674</v>
+        <v>1.049999965983107</v>
       </c>
       <c r="AL3">
-        <v>1.049999995515609</v>
+        <v>1.049999995513201</v>
       </c>
       <c r="AM3">
-        <v>-0.008617611622191802</v>
+        <v>-0.008617611621991213</v>
       </c>
       <c r="AN3">
-        <v>-120.0000031524007</v>
+        <v>-120.0000031524013</v>
       </c>
       <c r="AO3">
-        <v>120.0000022218855</v>
+        <v>120.0000022218857</v>
       </c>
       <c r="AP3">
-        <v>-0.008617611068708075</v>
+        <v>-0.008617611253009208</v>
       </c>
       <c r="AQ3">
-        <v>-120.0000031524006</v>
+        <v>-120.000003152357</v>
       </c>
       <c r="AR3">
-        <v>120.0000022218854</v>
+        <v>120.0000022220258</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -6065,40 +6065,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>-7.432919405031529E-13</v>
+        <v>-7.432793127354576E-13</v>
       </c>
       <c r="O4">
-        <v>5.260405984152306E-17</v>
+        <v>6.830169722645827E-18</v>
       </c>
       <c r="P4">
-        <v>1.663174058868899E-16</v>
+        <v>3.775717391501121E-17</v>
       </c>
       <c r="Q4">
-        <v>7.432919405079671E-13</v>
+        <v>7.432793127386663E-13</v>
       </c>
       <c r="R4">
-        <v>-5.260405984152278E-17</v>
+        <v>-6.83016972268716E-18</v>
       </c>
       <c r="S4">
-        <v>-1.663174058868896E-16</v>
+        <v>-3.775717391506567E-17</v>
       </c>
       <c r="T4">
-        <v>6.07903125193149E-13</v>
+        <v>6.080505324220238E-13</v>
       </c>
       <c r="U4">
-        <v>2.224177473221462E-16</v>
+        <v>-6.011744749784085E-17</v>
       </c>
       <c r="V4">
-        <v>-1.567653163724E-16</v>
+        <v>-7.275906993949121E-17</v>
       </c>
       <c r="W4">
-        <v>-6.079031251898964E-13</v>
+        <v>-6.080505324198552E-13</v>
       </c>
       <c r="X4">
-        <v>-2.224177473221459E-16</v>
+        <v>6.01174474979556E-17</v>
       </c>
       <c r="Y4">
-        <v>1.567653163724002E-16</v>
+        <v>7.275906993933518E-17</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -6119,40 +6119,40 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>1.049806842073367</v>
+        <v>1.04980684207336</v>
       </c>
       <c r="AH4">
-        <v>1.049999965979676</v>
+        <v>1.049999965979674</v>
       </c>
       <c r="AI4">
-        <v>1.04999999551561</v>
+        <v>1.049999995515623</v>
       </c>
       <c r="AJ4">
-        <v>1.049806842075191</v>
+        <v>1.049806842074573</v>
       </c>
       <c r="AK4">
-        <v>1.049999965979675</v>
+        <v>1.049999965981734</v>
       </c>
       <c r="AL4">
-        <v>1.049999995515609</v>
+        <v>1.04999999551417</v>
       </c>
       <c r="AM4">
-        <v>-0.008617611622191802</v>
+        <v>-0.008617611621991213</v>
       </c>
       <c r="AN4">
-        <v>-120.0000031524007</v>
+        <v>-120.0000031524013</v>
       </c>
       <c r="AO4">
-        <v>120.0000022218855</v>
+        <v>120.0000022218857</v>
       </c>
       <c r="AP4">
-        <v>-0.00861761129010156</v>
+        <v>-0.00861761140062761</v>
       </c>
       <c r="AQ4">
-        <v>-120.0000031524007</v>
+        <v>-120.0000031523747</v>
       </c>
       <c r="AR4">
-        <v>120.0000022218854</v>
+        <v>120.0000022219697</v>
       </c>
     </row>
   </sheetData>
@@ -6562,40 +6562,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.954095052004217E-09</v>
+        <v>1.954095294314158E-09</v>
       </c>
       <c r="O2">
-        <v>1.094663560602519E-09</v>
+        <v>1.09466402518739E-09</v>
       </c>
       <c r="P2">
-        <v>-3.051321424956531E-09</v>
+        <v>-3.051321822847033E-09</v>
       </c>
       <c r="Q2">
-        <v>2.563794993821223E-12</v>
+        <v>2.563552547296655E-12</v>
       </c>
       <c r="R2">
-        <v>-1.814866436112473E-16</v>
+        <v>-6.458598242258721E-16</v>
       </c>
       <c r="S2">
-        <v>-5.736744803004126E-16</v>
+        <v>-1.758553445657309E-16</v>
       </c>
       <c r="T2">
-        <v>2.395013213670932E-09</v>
+        <v>2.395013037979648E-09</v>
       </c>
       <c r="U2">
-        <v>-2.891358190993868E-09</v>
+        <v>-2.891358511081948E-09</v>
       </c>
       <c r="V2">
-        <v>4.976726430080633E-10</v>
+        <v>4.976723592165934E-10</v>
       </c>
       <c r="W2">
-        <v>-2.096805983168397E-12</v>
+        <v>-2.096630127656906E-12</v>
       </c>
       <c r="X2">
-        <v>-7.67203519424596E-16</v>
+        <v>-4.470769664323776E-16</v>
       </c>
       <c r="Y2">
-        <v>5.407735707413108E-16</v>
+        <v>8.243603386353276E-16</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -6625,16 +6625,16 @@
         <v>1.100000023836109</v>
       </c>
       <c r="AJ2">
-        <v>1.099788085472779</v>
+        <v>1.099788085472771</v>
       </c>
       <c r="AK2">
-        <v>1.100000038840699</v>
+        <v>1.100000038840695</v>
       </c>
       <c r="AL2">
-        <v>1.100000071253012</v>
+        <v>1.100000071253026</v>
       </c>
       <c r="AM2">
-        <v>-0.009028873954486989</v>
+        <v>-0.009028873954487393</v>
       </c>
       <c r="AN2">
         <v>-120.0000000021468</v>
@@ -6643,13 +6643,13 @@
         <v>120.0000000048169</v>
       </c>
       <c r="AP2">
-        <v>-0.009027895149532556</v>
+        <v>-0.009027895149364131</v>
       </c>
       <c r="AQ2">
-        <v>-120.0000033025899</v>
+        <v>-120.0000033025907</v>
       </c>
       <c r="AR2">
-        <v>120.000002327871</v>
+        <v>120.0000023278712</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -6693,40 +6693,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>-8.545983311105893E-13</v>
+        <v>-8.54519798139436E-13</v>
       </c>
       <c r="O3">
-        <v>6.049532637579036E-17</v>
+        <v>-2.323830609350641E-18</v>
       </c>
       <c r="P3">
-        <v>1.912250001098514E-16</v>
+        <v>5.228782780542146E-17</v>
       </c>
       <c r="Q3">
-        <v>8.545983311202539E-13</v>
+        <v>8.545197981458778E-13</v>
       </c>
       <c r="R3">
-        <v>-6.04953263757898E-17</v>
+        <v>2.323830609411795E-18</v>
       </c>
       <c r="S3">
-        <v>-1.912250001098509E-16</v>
+        <v>-5.228782780521444E-17</v>
       </c>
       <c r="T3">
-        <v>6.989353082067806E-13</v>
+        <v>6.989605596518023E-13</v>
       </c>
       <c r="U3">
-        <v>2.557345852656677E-16</v>
+        <v>6.558439684129128E-17</v>
       </c>
       <c r="V3">
-        <v>-1.802577701424733E-16</v>
+        <v>3.151961206712659E-17</v>
       </c>
       <c r="W3">
-        <v>-6.989353082002513E-13</v>
+        <v>-6.989605596474495E-13</v>
       </c>
       <c r="X3">
-        <v>-2.557345852656674E-16</v>
+        <v>-6.558439684151405E-17</v>
       </c>
       <c r="Y3">
-        <v>1.802577701424737E-16</v>
+        <v>-3.151961206718439E-17</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -6747,40 +6747,40 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>1.099788085472779</v>
+        <v>1.099788085472771</v>
       </c>
       <c r="AH3">
-        <v>1.100000038840699</v>
+        <v>1.100000038840695</v>
       </c>
       <c r="AI3">
-        <v>1.100000071253012</v>
+        <v>1.100000071253026</v>
       </c>
       <c r="AJ3">
-        <v>1.099788085476114</v>
+        <v>1.099788085474993</v>
       </c>
       <c r="AK3">
-        <v>1.100000038840697</v>
+        <v>1.100000038844463</v>
       </c>
       <c r="AL3">
-        <v>1.100000071253011</v>
+        <v>1.100000071250369</v>
       </c>
       <c r="AM3">
-        <v>-0.009027895149532556</v>
+        <v>-0.009027895149364131</v>
       </c>
       <c r="AN3">
-        <v>-120.0000033025899</v>
+        <v>-120.0000033025907</v>
       </c>
       <c r="AO3">
-        <v>120.000002327871</v>
+        <v>120.0000023278712</v>
       </c>
       <c r="AP3">
-        <v>-0.009027894569692449</v>
+        <v>-0.009027894762837179</v>
       </c>
       <c r="AQ3">
-        <v>-120.0000033025898</v>
+        <v>-120.0000033025442</v>
       </c>
       <c r="AR3">
-        <v>120.0000023278709</v>
+        <v>120.0000023280179</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -6824,40 +6824,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>-8.545983261391554E-13</v>
+        <v>-8.542696257912519E-13</v>
       </c>
       <c r="O4">
-        <v>6.049532946827909E-17</v>
+        <v>1.987686440631517E-17</v>
       </c>
       <c r="P4">
-        <v>1.912250039714773E-16</v>
+        <v>1.289695813511418E-16</v>
       </c>
       <c r="Q4">
-        <v>8.545983261449542E-13</v>
+        <v>8.542696257951156E-13</v>
       </c>
       <c r="R4">
-        <v>-6.049532946827876E-17</v>
+        <v>-1.987686440626811E-17</v>
       </c>
       <c r="S4">
-        <v>-1.91225003971477E-16</v>
+        <v>-1.289695813509587E-16</v>
       </c>
       <c r="T4">
-        <v>6.989353280792081E-13</v>
+        <v>6.989506233740573E-13</v>
       </c>
       <c r="U4">
-        <v>2.557345869824202E-16</v>
+        <v>1.805637218562534E-16</v>
       </c>
       <c r="V4">
-        <v>-1.802577756178066E-16</v>
+        <v>-2.428673069826951E-18</v>
       </c>
       <c r="W4">
-        <v>-6.989353280752906E-13</v>
+        <v>-6.989506233714462E-13</v>
       </c>
       <c r="X4">
-        <v>-2.5573458698242E-16</v>
+        <v>-1.805637218566342E-16</v>
       </c>
       <c r="Y4">
-        <v>1.802577756178069E-16</v>
+        <v>2.428673069625331E-18</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -6878,40 +6878,40 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>1.099788085472779</v>
+        <v>1.099788085472771</v>
       </c>
       <c r="AH4">
-        <v>1.100000038840699</v>
+        <v>1.100000038840695</v>
       </c>
       <c r="AI4">
-        <v>1.100000071253012</v>
+        <v>1.100000071253026</v>
       </c>
       <c r="AJ4">
-        <v>1.09978808547478</v>
+        <v>1.099788085474103</v>
       </c>
       <c r="AK4">
-        <v>1.100000038840698</v>
+        <v>1.100000038842956</v>
       </c>
       <c r="AL4">
-        <v>1.100000071253012</v>
+        <v>1.100000071251432</v>
       </c>
       <c r="AM4">
-        <v>-0.009027895149532556</v>
+        <v>-0.009027895149364131</v>
       </c>
       <c r="AN4">
-        <v>-120.0000033025899</v>
+        <v>-120.0000033025907</v>
       </c>
       <c r="AO4">
-        <v>120.000002327871</v>
+        <v>120.0000023278712</v>
       </c>
       <c r="AP4">
-        <v>-0.009027894801628487</v>
+        <v>-0.009027894917459405</v>
       </c>
       <c r="AQ4">
-        <v>-120.0000033025898</v>
+        <v>-120.0000033025628</v>
       </c>
       <c r="AR4">
-        <v>120.0000023278709</v>
+        <v>120.0000023279592</v>
       </c>
     </row>
   </sheetData>
@@ -7063,13 +7063,13 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>4.223610704496081E-05</v>
+        <v>4.223610552345609E-05</v>
       </c>
       <c r="C2">
-        <v>4.223605710366345E-05</v>
+        <v>4.223605903063634E-05</v>
       </c>
       <c r="D2">
-        <v>4.223605710366324E-05</v>
+        <v>4.223605640210277E-05</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -7081,13 +7081,13 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>9.75401125411808E-06</v>
+        <v>9.754010902741612E-06</v>
       </c>
       <c r="I2">
-        <v>9.75399972066932E-06</v>
+        <v>9.754000165684652E-06</v>
       </c>
       <c r="J2">
-        <v>9.753999720669271E-06</v>
+        <v>9.75399955865082E-06</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -7099,49 +7099,49 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-1.244690764709367E-17</v>
+        <v>-1.240143722389865E-17</v>
       </c>
       <c r="O2">
-        <v>8.027481102941373E-06</v>
+        <v>8.027481329503798E-06</v>
       </c>
       <c r="P2">
-        <v>-8.022218044710302E-06</v>
+        <v>-8.022217958415126E-06</v>
       </c>
       <c r="Q2">
-        <v>-1.314478183905239E-12</v>
+        <v>-1.314495256889344E-12</v>
       </c>
       <c r="R2">
-        <v>2.594539019015576E-12</v>
+        <v>2.368465201343234E-12</v>
       </c>
       <c r="S2">
-        <v>-3.916244220603461E-12</v>
+        <v>-4.003064462358238E-12</v>
       </c>
       <c r="T2">
-        <v>-1.679474716038409E-17</v>
+        <v>-1.674918850627522E-17</v>
       </c>
       <c r="U2">
-        <v>-4.628593907940073E-06</v>
+        <v>-4.628594361369372E-06</v>
       </c>
       <c r="V2">
-        <v>-4.637710960488362E-06</v>
+        <v>-4.637710802227443E-06</v>
       </c>
       <c r="W2">
-        <v>3.759345724051429E-12</v>
+        <v>3.758988303230155E-12</v>
       </c>
       <c r="X2">
-        <v>-3.021362258131679E-12</v>
+        <v>-2.568369180394152E-12</v>
       </c>
       <c r="Y2">
-        <v>-7.376378611683031E-13</v>
+        <v>-8.960183764248484E-13</v>
       </c>
       <c r="Z2">
-        <v>-90.0939309717175</v>
+        <v>-90.09392586038892</v>
       </c>
       <c r="AA2">
-        <v>-90.03254693882892</v>
+        <v>-90.03254520974704</v>
       </c>
       <c r="AB2">
-        <v>-90.03254693882783</v>
+        <v>-90.0325463586982</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -7156,37 +7156,37 @@
         <v>0</v>
       </c>
       <c r="AH2">
-        <v>0.9500001308346691</v>
+        <v>0.950000130834685</v>
       </c>
       <c r="AI2">
-        <v>0.9500001910625286</v>
+        <v>0.9500001910625224</v>
       </c>
       <c r="AJ2">
-        <v>0.0003810528012204703</v>
+        <v>0.0003810527929867142</v>
       </c>
       <c r="AK2">
-        <v>0.9497515977749511</v>
+        <v>0.949751597793258</v>
       </c>
       <c r="AL2">
-        <v>0.9503745977192835</v>
+        <v>0.9503745977197934</v>
       </c>
       <c r="AM2">
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>-120.0000191070894</v>
+        <v>-120.00001910709</v>
       </c>
       <c r="AO2">
-        <v>120.0000170099076</v>
+        <v>120.0000170099075</v>
       </c>
       <c r="AP2">
-        <v>109.2507962213217</v>
+        <v>109.2508024850522</v>
       </c>
       <c r="AQ2">
-        <v>-120.017442097928</v>
+        <v>-120.0174420994616</v>
       </c>
       <c r="AR2">
-        <v>119.9957444346445</v>
+        <v>119.9957444362708</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -7230,40 +7230,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>4.381593914326211E-13</v>
+        <v>4.382105231284473E-13</v>
       </c>
       <c r="O3">
-        <v>-8.648466623000476E-13</v>
+        <v>-1.01027778771743E-12</v>
       </c>
       <c r="P3">
-        <v>1.305413818825361E-12</v>
+        <v>1.638877251016555E-12</v>
       </c>
       <c r="Q3">
-        <v>-4.379359040216745E-13</v>
+        <v>-4.380615759189524E-13</v>
       </c>
       <c r="R3">
-        <v>8.648466623360222E-13</v>
+        <v>1.010277791707677E-12</v>
       </c>
       <c r="S3">
-        <v>-1.305413818789386E-12</v>
+        <v>-1.638877253013227E-12</v>
       </c>
       <c r="T3">
-        <v>-1.253115192929901E-12</v>
+        <v>-1.25307081493238E-12</v>
       </c>
       <c r="U3">
-        <v>1.00711973295051E-12</v>
+        <v>9.219101728323903E-13</v>
       </c>
       <c r="V3">
-        <v>2.458807400702835E-13</v>
+        <v>2.217213804781814E-13</v>
       </c>
       <c r="W3">
-        <v>1.253193833883099E-12</v>
+        <v>1.253123301956838E-12</v>
       </c>
       <c r="X3">
-        <v>-1.007119732937851E-12</v>
+        <v>-9.21910205230142E-13</v>
       </c>
       <c r="Y3">
-        <v>-2.458807400576248E-13</v>
+        <v>-2.217214198661852E-13</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -7284,40 +7284,40 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>0.0003810528012204703</v>
+        <v>0.0003810527929867142</v>
       </c>
       <c r="AH3">
-        <v>0.9497515977749511</v>
+        <v>0.949751597793258</v>
       </c>
       <c r="AI3">
-        <v>0.9503745977192835</v>
+        <v>0.9503745977197934</v>
       </c>
       <c r="AJ3">
-        <v>0.0003810529420124964</v>
+        <v>0.0003810529037410396</v>
       </c>
       <c r="AK3">
-        <v>0.9497515977848481</v>
+        <v>0.9497516150048757</v>
       </c>
       <c r="AL3">
-        <v>0.950374597692314</v>
+        <v>0.9503746018914051</v>
       </c>
       <c r="AM3">
-        <v>109.2507962213217</v>
+        <v>109.2508024850522</v>
       </c>
       <c r="AN3">
-        <v>-120.017442097928</v>
+        <v>-120.0174420994616</v>
       </c>
       <c r="AO3">
-        <v>119.9957444346445</v>
+        <v>119.9957444362708</v>
       </c>
       <c r="AP3">
-        <v>109.2405706995654</v>
+        <v>109.243986298883</v>
       </c>
       <c r="AQ3">
-        <v>-120.0174420963941</v>
+        <v>-120.0174429893256</v>
       </c>
       <c r="AR3">
-        <v>119.9957444343951</v>
+        <v>119.995745779266</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -7361,40 +7361,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>4.381593950656262E-13</v>
+        <v>4.382210535757597E-13</v>
       </c>
       <c r="O4">
-        <v>-8.648466815361523E-13</v>
+        <v>-1.030168079758898E-12</v>
       </c>
       <c r="P4">
-        <v>1.305413861699345E-12</v>
+        <v>1.590136192751073E-12</v>
       </c>
       <c r="Q4">
-        <v>-4.38025302611239E-13</v>
+        <v>-4.381316783880854E-13</v>
       </c>
       <c r="R4">
-        <v>8.64846681557737E-13</v>
+        <v>1.030168085242765E-12</v>
       </c>
       <c r="S4">
-        <v>-1.30541386167776E-12</v>
+        <v>-1.590136204119559E-12</v>
       </c>
       <c r="T4">
-        <v>-1.253115232737884E-12</v>
+        <v>-1.253174534380451E-12</v>
       </c>
       <c r="U4">
-        <v>1.007119772556269E-12</v>
+        <v>6.136149826553821E-13</v>
       </c>
       <c r="V4">
-        <v>2.458807387935554E-13</v>
+        <v>-5.10756812657952E-13</v>
       </c>
       <c r="W4">
-        <v>1.253162417312642E-12</v>
+        <v>1.253206018896087E-12</v>
       </c>
       <c r="X4">
-        <v>-1.007119772548674E-12</v>
+        <v>-6.136149989328577E-13</v>
       </c>
       <c r="Y4">
-        <v>-2.458807387859601E-13</v>
+        <v>5.107567916490304E-13</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -7415,40 +7415,40 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>0.0003810528012204703</v>
+        <v>0.0003810527929867142</v>
       </c>
       <c r="AH4">
-        <v>0.9497515977749511</v>
+        <v>0.949751597793258</v>
       </c>
       <c r="AI4">
-        <v>0.9503745977192835</v>
+        <v>0.9503745977197934</v>
       </c>
       <c r="AJ4">
-        <v>0.0003810528842395722</v>
+        <v>0.0003810528565488157</v>
       </c>
       <c r="AK4">
-        <v>0.9497515977808894</v>
+        <v>0.9497516081229054</v>
       </c>
       <c r="AL4">
-        <v>0.9503745977031017</v>
+        <v>0.950374600222977</v>
       </c>
       <c r="AM4">
-        <v>109.2507962213217</v>
+        <v>109.2508024850522</v>
       </c>
       <c r="AN4">
-        <v>-120.017442097928</v>
+        <v>-120.0174420994616</v>
       </c>
       <c r="AO4">
-        <v>119.9957444346445</v>
+        <v>119.9957444362708</v>
       </c>
       <c r="AP4">
-        <v>109.2446609071788</v>
+        <v>109.246712915473</v>
       </c>
       <c r="AQ4">
-        <v>-120.0174420970076</v>
+        <v>-120.0174426335993</v>
       </c>
       <c r="AR4">
-        <v>119.9957444344949</v>
+        <v>119.9957452417372</v>
       </c>
     </row>
   </sheetData>
@@ -7600,13 +7600,13 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>4.001315195164984E-05</v>
+        <v>4.001315075938171E-05</v>
       </c>
       <c r="C2">
-        <v>4.001310463908002E-05</v>
+        <v>4.001310570594514E-05</v>
       </c>
       <c r="D2">
-        <v>4.001310463908459E-05</v>
+        <v>4.001310379973555E-05</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -7618,13 +7618,13 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>9.240641757860462E-06</v>
+        <v>9.240641482517931E-06</v>
       </c>
       <c r="I2">
-        <v>9.240630831490333E-06</v>
+        <v>9.240631077872283E-06</v>
       </c>
       <c r="J2">
-        <v>9.240630831491388E-06</v>
+        <v>9.240630637652028E-06</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -7636,49 +7636,49 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>2.962921341953684E-17</v>
+        <v>2.931396177327888E-17</v>
       </c>
       <c r="O2">
-        <v>7.204719404792083E-06</v>
+        <v>7.204719715158045E-06</v>
       </c>
       <c r="P2">
-        <v>-7.1999957742921E-06</v>
+        <v>-7.199995492895954E-06</v>
       </c>
       <c r="Q2">
-        <v>-1.179753187106189E-12</v>
+        <v>-1.179869893334723E-12</v>
       </c>
       <c r="R2">
-        <v>2.328689004290752E-12</v>
+        <v>2.018140070678842E-12</v>
       </c>
       <c r="S2">
-        <v>-3.514754251483346E-12</v>
+        <v>-3.795999779191013E-12</v>
       </c>
       <c r="T2">
-        <v>4.334862543420485E-18</v>
+        <v>4.280998436905769E-18</v>
       </c>
       <c r="U2">
-        <v>-4.154194680014471E-06</v>
+        <v>-4.15419458566341E-06</v>
       </c>
       <c r="V2">
-        <v>-4.162377241399156E-06</v>
+        <v>-4.162377379584729E-06</v>
       </c>
       <c r="W2">
-        <v>3.374038552434024E-12</v>
+        <v>3.374071803005128E-12</v>
       </c>
       <c r="X2">
-        <v>-2.711534789585124E-12</v>
+        <v>-2.805615698096423E-12</v>
       </c>
       <c r="Y2">
-        <v>-6.621770665586882E-13</v>
+        <v>-5.237908951063343E-13</v>
       </c>
       <c r="Z2">
-        <v>-90.09393075309094</v>
+        <v>-90.09393195770849</v>
       </c>
       <c r="AA2">
-        <v>-90.03254671658866</v>
+        <v>-90.03254834776456</v>
       </c>
       <c r="AB2">
-        <v>-90.03254671658433</v>
+        <v>-90.03254851105122</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -7693,37 +7693,37 @@
         <v>0</v>
       </c>
       <c r="AH2">
-        <v>0.9000001042838466</v>
+        <v>0.9000001042838419</v>
       </c>
       <c r="AI2">
-        <v>0.9000001583387633</v>
+        <v>0.9000001583387675</v>
       </c>
       <c r="AJ2">
-        <v>0.0003609973669044587</v>
+        <v>0.0003609973572337977</v>
       </c>
       <c r="AK2">
-        <v>0.899764651920039</v>
+        <v>0.8997646519047784</v>
       </c>
       <c r="AL2">
-        <v>0.9003548593647794</v>
+        <v>0.900354859353045</v>
       </c>
       <c r="AM2">
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>-120.0000181014523</v>
+        <v>-120.000018101453</v>
       </c>
       <c r="AO2">
-        <v>120.0000161146487</v>
+        <v>120.000016114648</v>
       </c>
       <c r="AP2">
-        <v>109.2507963587852</v>
+        <v>109.2507934401323</v>
       </c>
       <c r="AQ2">
-        <v>-120.017441091556</v>
+        <v>-120.017441090761</v>
       </c>
       <c r="AR2">
-        <v>119.9957435399412</v>
+        <v>119.995743538771</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -7767,40 +7767,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>3.932510601574227E-13</v>
+        <v>3.93315371083036E-13</v>
       </c>
       <c r="O3">
-        <v>-7.762293156509529E-13</v>
+        <v>-8.427282224169299E-13</v>
       </c>
       <c r="P3">
-        <v>1.171584454140269E-12</v>
+        <v>1.247099154943455E-12</v>
       </c>
       <c r="Q3">
-        <v>-3.930504786636249E-13</v>
+        <v>-3.931816534913853E-13</v>
       </c>
       <c r="R3">
-        <v>7.762293156832389E-13</v>
+        <v>8.427282219792862E-13</v>
       </c>
       <c r="S3">
-        <v>-1.171584454107983E-12</v>
+        <v>-1.24709915671328E-12</v>
       </c>
       <c r="T3">
-        <v>-1.124679474187025E-12</v>
+        <v>-1.124831291042999E-12</v>
       </c>
       <c r="U3">
-        <v>9.038447510746954E-13</v>
+        <v>1.011584544539079E-12</v>
       </c>
       <c r="V3">
-        <v>2.207260544416578E-13</v>
+        <v>1.581486283825443E-13</v>
       </c>
       <c r="W3">
-        <v>1.124750054985273E-12</v>
+        <v>1.124878402738123E-12</v>
       </c>
       <c r="X3">
-        <v>-9.038447510633343E-13</v>
+        <v>-1.011584575957888E-12</v>
       </c>
       <c r="Y3">
-        <v>-2.20726054430297E-13</v>
+        <v>-1.58148658315674E-13</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -7821,40 +7821,40 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>0.0003609973669044587</v>
+        <v>0.0003609973572337977</v>
       </c>
       <c r="AH3">
-        <v>0.899764651920039</v>
+        <v>0.8997646519047784</v>
       </c>
       <c r="AI3">
-        <v>0.9003548593647794</v>
+        <v>0.900354859353045</v>
       </c>
       <c r="AJ3">
-        <v>0.0003609975002862038</v>
+        <v>0.0003609974613614956</v>
       </c>
       <c r="AK3">
-        <v>0.8997646519294159</v>
+        <v>0.8997646682100982</v>
       </c>
       <c r="AL3">
-        <v>0.9003548593392297</v>
+        <v>0.9003548633076867</v>
       </c>
       <c r="AM3">
-        <v>109.2507963587852</v>
+        <v>109.2507934401323</v>
       </c>
       <c r="AN3">
-        <v>-120.017441091556</v>
+        <v>-120.017441090761</v>
       </c>
       <c r="AO3">
-        <v>119.9957435399412</v>
+        <v>119.995743538771</v>
       </c>
       <c r="AP3">
-        <v>109.2405708364905</v>
+        <v>109.243976602617</v>
       </c>
       <c r="AQ3">
-        <v>-120.0174410900221</v>
+        <v>-120.0174419805335</v>
       </c>
       <c r="AR3">
-        <v>119.9957435396919</v>
+        <v>119.9957448820821</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -7898,40 +7898,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>3.932510606085779E-13</v>
+        <v>3.930973631724473E-13</v>
       </c>
       <c r="O4">
-        <v>-7.762293353996955E-13</v>
+        <v>-9.171749752035317E-13</v>
       </c>
       <c r="P4">
-        <v>1.171584493741017E-12</v>
+        <v>1.084631150484571E-12</v>
       </c>
       <c r="Q4">
-        <v>-3.93130711706196E-13</v>
+        <v>-3.930171620186248E-13</v>
       </c>
       <c r="R4">
-        <v>7.762293354190674E-13</v>
+        <v>9.171749876720912E-13</v>
       </c>
       <c r="S4">
-        <v>-1.171584493721646E-12</v>
+        <v>-1.084631157284197E-12</v>
       </c>
       <c r="T4">
-        <v>-1.124679505868853E-12</v>
+        <v>-1.124540438374931E-12</v>
       </c>
       <c r="U4">
-        <v>9.038447859563078E-13</v>
+        <v>-2.674422730645233E-13</v>
       </c>
       <c r="V4">
-        <v>2.2072605499342E-13</v>
+        <v>-2.80467642742768E-13</v>
       </c>
       <c r="W4">
-        <v>1.124721854350049E-12</v>
+        <v>1.124568681006329E-12</v>
       </c>
       <c r="X4">
-        <v>-9.038447859494911E-13</v>
+        <v>2.674422674229382E-13</v>
       </c>
       <c r="Y4">
-        <v>-2.207260549866034E-13</v>
+        <v>2.804676282336994E-13</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -7952,40 +7952,40 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>0.0003609973669044587</v>
+        <v>0.0003609973572337977</v>
       </c>
       <c r="AH4">
-        <v>0.899764651920039</v>
+        <v>0.8997646519047784</v>
       </c>
       <c r="AI4">
-        <v>0.9003548593647794</v>
+        <v>0.900354859353045</v>
       </c>
       <c r="AJ4">
-        <v>0.0003609974455540776</v>
+        <v>0.0003609974174545793</v>
       </c>
       <c r="AK4">
-        <v>0.899764651925665</v>
+        <v>0.89976466169076</v>
       </c>
       <c r="AL4">
-        <v>0.9003548593494496</v>
+        <v>0.9003548617244822</v>
       </c>
       <c r="AM4">
-        <v>109.2507963587852</v>
+        <v>109.2507934401323</v>
       </c>
       <c r="AN4">
-        <v>-120.017441091556</v>
+        <v>-120.017441090761</v>
       </c>
       <c r="AO4">
-        <v>119.9957435399412</v>
+        <v>119.995743538771</v>
       </c>
       <c r="AP4">
-        <v>109.2446610443411</v>
+        <v>109.2467038702595</v>
       </c>
       <c r="AQ4">
-        <v>-120.0174410906356</v>
+        <v>-120.0174416248987</v>
       </c>
       <c r="AR4">
-        <v>119.9957435397916</v>
+        <v>119.9957443442375</v>
       </c>
     </row>
   </sheetData>
@@ -8173,40 +8173,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.57286019710568E-09</v>
+        <v>1.572860333670908E-09</v>
       </c>
       <c r="O2">
-        <v>8.820693779418422E-10</v>
+        <v>8.820692712677718E-10</v>
       </c>
       <c r="P2">
-        <v>-2.456992886748341E-09</v>
+        <v>-2.4569928902364E-09</v>
       </c>
       <c r="Q2">
-        <v>2.064604861879486E-12</v>
+        <v>2.0644684217188E-12</v>
       </c>
       <c r="R2">
-        <v>2.598884033586923E-17</v>
+        <v>1.326794915765953E-16</v>
       </c>
       <c r="S2">
-        <v>-9.395029430255281E-16</v>
+        <v>-9.361585198295381E-16</v>
       </c>
       <c r="T2">
-        <v>1.928828222941497E-09</v>
+        <v>1.928828034380772E-09</v>
       </c>
       <c r="U2">
-        <v>-2.32782801652537E-09</v>
+        <v>-2.327828148598527E-09</v>
       </c>
       <c r="V2">
-        <v>4.000195186779838E-10</v>
+        <v>4.000195370329086E-10</v>
       </c>
       <c r="W2">
-        <v>-1.687917159612849E-12</v>
+        <v>-1.687728507352532E-12</v>
       </c>
       <c r="X2">
-        <v>-1.069839212774191E-15</v>
+        <v>-9.37921916570763E-16</v>
       </c>
       <c r="Y2">
-        <v>5.124130634466132E-16</v>
+        <v>4.941221125334121E-16</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -8236,16 +8236,16 @@
         <v>0.9499999880733127</v>
       </c>
       <c r="AJ2">
-        <v>0.9498023633840782</v>
+        <v>0.9498023633840721</v>
       </c>
       <c r="AK2">
-        <v>0.9499999855921459</v>
+        <v>0.9499999855921569</v>
       </c>
       <c r="AL2">
-        <v>0.9500000779836723</v>
+        <v>0.9500000779836689</v>
       </c>
       <c r="AM2">
-        <v>-0.009746930722313861</v>
+        <v>-0.009746930722314211</v>
       </c>
       <c r="AN2">
         <v>-120.0000000025041</v>
@@ -8254,13 +8254,13 @@
         <v>120.0000000056145</v>
       </c>
       <c r="AP2">
-        <v>-0.009743707869720132</v>
+        <v>-0.009743707870388401</v>
       </c>
       <c r="AQ2">
-        <v>-120.0000061744936</v>
+        <v>-120.0000061744938</v>
       </c>
       <c r="AR2">
-        <v>120.0000029573488</v>
+        <v>120.0000029573493</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -8304,40 +8304,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>-6.882015995974497E-13</v>
+        <v>-6.882277731830304E-13</v>
       </c>
       <c r="O3">
-        <v>-8.662777809035983E-18</v>
+        <v>-8.884695667945313E-17</v>
       </c>
       <c r="P3">
-        <v>3.131677070613612E-16</v>
+        <v>3.622738133621652E-16</v>
       </c>
       <c r="Q3">
-        <v>6.882015996135787E-13</v>
+        <v>6.88227773193781E-13</v>
       </c>
       <c r="R3">
-        <v>8.662777809038579E-18</v>
+        <v>8.884695667997421E-17</v>
       </c>
       <c r="S3">
-        <v>-3.131677070613587E-16</v>
+        <v>-3.622738133617265E-16</v>
       </c>
       <c r="T3">
-        <v>5.626390282477687E-13</v>
+        <v>5.626638680431504E-13</v>
       </c>
       <c r="U3">
-        <v>3.566133967676941E-16</v>
+        <v>3.229988245538052E-16</v>
       </c>
       <c r="V3">
-        <v>-1.708044796943405E-16</v>
+        <v>-1.200681561828223E-16</v>
       </c>
       <c r="W3">
-        <v>-5.626390282420932E-13</v>
+        <v>-5.626638680393626E-13</v>
       </c>
       <c r="X3">
-        <v>-3.566133967676932E-16</v>
+        <v>-3.229988245558882E-16</v>
       </c>
       <c r="Y3">
-        <v>1.708044796943414E-16</v>
+        <v>1.200681561804158E-16</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -8358,40 +8358,40 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>0.9498023633840782</v>
+        <v>0.9498023633840721</v>
       </c>
       <c r="AH3">
-        <v>0.9499999855921459</v>
+        <v>0.9499999855921569</v>
       </c>
       <c r="AI3">
-        <v>0.9500000779836723</v>
+        <v>0.9500000779836689</v>
       </c>
       <c r="AJ3">
-        <v>0.9498023633935823</v>
+        <v>0.949802363390403</v>
       </c>
       <c r="AK3">
-        <v>0.9499999855921438</v>
+        <v>0.9499999855982446</v>
       </c>
       <c r="AL3">
-        <v>0.9500000779836673</v>
+        <v>0.9500000779807475</v>
       </c>
       <c r="AM3">
-        <v>-0.009743707869720132</v>
+        <v>-0.009743707870388401</v>
       </c>
       <c r="AN3">
-        <v>-120.0000061744936</v>
+        <v>-120.0000061744938</v>
       </c>
       <c r="AO3">
-        <v>120.0000029573488</v>
+        <v>120.0000029573493</v>
       </c>
       <c r="AP3">
-        <v>-0.00974370692849303</v>
+        <v>-0.009743707242809648</v>
       </c>
       <c r="AQ3">
-        <v>-120.0000061744932</v>
+        <v>-120.0000061745023</v>
       </c>
       <c r="AR3">
-        <v>120.0000029573485</v>
+        <v>120.0000029576715</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -8435,40 +8435,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>-6.882016167563081E-13</v>
+        <v>-6.883862019383665E-13</v>
       </c>
       <c r="O4">
-        <v>-8.662774052874159E-18</v>
+        <v>-1.428315169196457E-16</v>
       </c>
       <c r="P4">
-        <v>3.131677147603981E-16</v>
+        <v>3.835345804283944E-16</v>
       </c>
       <c r="Q4">
-        <v>6.882016167659856E-13</v>
+        <v>6.883862019448164E-13</v>
       </c>
       <c r="R4">
-        <v>8.662774052875737E-18</v>
+        <v>1.428315169201758E-16</v>
       </c>
       <c r="S4">
-        <v>-3.131677147603965E-16</v>
+        <v>-3.835345804286437E-16</v>
       </c>
       <c r="T4">
-        <v>5.626390523861039E-13</v>
+        <v>5.625779943539685E-13</v>
       </c>
       <c r="U4">
-        <v>3.56613408512365E-16</v>
+        <v>2.122596496073303E-16</v>
       </c>
       <c r="V4">
-        <v>-1.708044867428892E-16</v>
+        <v>-2.836162365569078E-16</v>
       </c>
       <c r="W4">
-        <v>-5.626390523826986E-13</v>
+        <v>-5.625779943516955E-13</v>
       </c>
       <c r="X4">
-        <v>-3.566134085123645E-16</v>
+        <v>-2.122596496081596E-16</v>
       </c>
       <c r="Y4">
-        <v>1.708044867428898E-16</v>
+        <v>2.836162365550912E-16</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -8489,40 +8489,40 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>0.9498023633840782</v>
+        <v>0.9498023633840721</v>
       </c>
       <c r="AH4">
-        <v>0.9499999855921459</v>
+        <v>0.9499999855921569</v>
       </c>
       <c r="AI4">
-        <v>0.9500000779836723</v>
+        <v>0.9500000779836689</v>
       </c>
       <c r="AJ4">
-        <v>0.9498023633897805</v>
+        <v>0.9498023633878712</v>
       </c>
       <c r="AK4">
-        <v>0.9499999855921447</v>
+        <v>0.9499999855958103</v>
       </c>
       <c r="AL4">
-        <v>0.9500000779836694</v>
+        <v>0.9500000779819171</v>
       </c>
       <c r="AM4">
-        <v>-0.009743707869720132</v>
+        <v>-0.009743707870388401</v>
       </c>
       <c r="AN4">
-        <v>-120.0000061744936</v>
+        <v>-120.0000061744938</v>
       </c>
       <c r="AO4">
-        <v>120.0000029573488</v>
+        <v>120.0000029573493</v>
       </c>
       <c r="AP4">
-        <v>-0.009743707304983851</v>
+        <v>-0.009743707493908871</v>
       </c>
       <c r="AQ4">
-        <v>-120.0000061744934</v>
+        <v>-120.000006174499</v>
       </c>
       <c r="AR4">
-        <v>120.0000029573486</v>
+        <v>120.0000029575425</v>
       </c>
     </row>
   </sheetData>
@@ -8710,40 +8710,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>1.337384566713627E-09</v>
+        <v>1.33738446810267E-09</v>
       </c>
       <c r="O2">
-        <v>7.499872965807424E-10</v>
+        <v>7.499872732053008E-10</v>
       </c>
       <c r="P2">
-        <v>-2.089126290105466E-09</v>
+        <v>-2.089126228883938E-09</v>
       </c>
       <c r="Q2">
-        <v>1.755509340662304E-12</v>
+        <v>1.755608002567204E-12</v>
       </c>
       <c r="R2">
-        <v>2.212827167499376E-17</v>
+        <v>4.53872581323656E-17</v>
       </c>
       <c r="S2">
-        <v>-7.988390390509877E-16</v>
+        <v>-8.599958007393831E-16</v>
       </c>
       <c r="T2">
-        <v>1.640059982177426E-09</v>
+        <v>1.640059814051786E-09</v>
       </c>
       <c r="U2">
-        <v>-1.97930988451134E-09</v>
+        <v>-1.979309866624345E-09</v>
       </c>
       <c r="V2">
-        <v>3.401468906053267E-10</v>
+        <v>3.401468094514263E-10</v>
       </c>
       <c r="W2">
-        <v>-1.435216210221266E-12</v>
+        <v>-1.435048190456866E-12</v>
       </c>
       <c r="X2">
-        <v>-9.096436836335502E-16</v>
+        <v>-9.275229131314325E-16</v>
       </c>
       <c r="Y2">
-        <v>4.356587123217982E-16</v>
+        <v>5.169106560241317E-16</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -8773,16 +8773,16 @@
         <v>0.8999999761532447</v>
       </c>
       <c r="AJ2">
-        <v>0.8998226053398991</v>
+        <v>0.899822605339908</v>
       </c>
       <c r="AK2">
-        <v>0.8999999739229601</v>
+        <v>0.8999999739229599</v>
       </c>
       <c r="AL2">
-        <v>0.9000000568488989</v>
+        <v>0.9000000568488929</v>
       </c>
       <c r="AM2">
-        <v>-0.009234035272194732</v>
+        <v>-0.009234035272194539</v>
       </c>
       <c r="AN2">
         <v>-120.0000000022469</v>
@@ -8791,13 +8791,13 @@
         <v>120.0000000050386</v>
       </c>
       <c r="AP2">
-        <v>-0.009230982043640826</v>
+        <v>-0.009230982043994746</v>
       </c>
       <c r="AQ2">
-        <v>-120.0000058494599</v>
+        <v>-120.0000058494594</v>
       </c>
       <c r="AR2">
-        <v>120.000002801495</v>
+        <v>120.0000028014946</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -8841,40 +8841,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>-5.851697644649517E-13</v>
+        <v>-5.852334092653674E-13</v>
       </c>
       <c r="O3">
-        <v>-7.37609189992654E-18</v>
+        <v>1.591289328099434E-17</v>
       </c>
       <c r="P3">
-        <v>2.662795033446456E-16</v>
+        <v>3.044822294634595E-16</v>
       </c>
       <c r="Q3">
-        <v>5.851697644779441E-13</v>
+        <v>5.852334092740283E-13</v>
       </c>
       <c r="R3">
-        <v>7.376091899928643E-18</v>
+        <v>-1.591289328113722E-17</v>
       </c>
       <c r="S3">
-        <v>-2.662795033446435E-16</v>
+        <v>-3.044822294632747E-16</v>
       </c>
       <c r="T3">
-        <v>4.784053834806217E-13</v>
+        <v>4.784320324127744E-13</v>
       </c>
       <c r="U3">
-        <v>3.032144465563687E-16</v>
+        <v>3.268992493565479E-16</v>
       </c>
       <c r="V3">
-        <v>-1.45219314976666E-16</v>
+        <v>-1.317966357428434E-16</v>
       </c>
       <c r="W3">
-        <v>-4.784053834760498E-13</v>
+        <v>-4.784320324097229E-13</v>
       </c>
       <c r="X3">
-        <v>-3.03214446556368E-16</v>
+        <v>-3.2689924935853E-16</v>
       </c>
       <c r="Y3">
-        <v>1.452193149766668E-16</v>
+        <v>1.317966357408368E-16</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -8895,40 +8895,40 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>0.8998226053398991</v>
+        <v>0.899822605339908</v>
       </c>
       <c r="AH3">
-        <v>0.8999999739229601</v>
+        <v>0.8999999739229599</v>
       </c>
       <c r="AI3">
-        <v>0.9000000568488989</v>
+        <v>0.9000000568488929</v>
       </c>
       <c r="AJ3">
-        <v>0.8998226053484289</v>
+        <v>0.899822605345591</v>
       </c>
       <c r="AK3">
-        <v>0.8999999739229581</v>
+        <v>0.8999999739284232</v>
       </c>
       <c r="AL3">
-        <v>0.9000000568488946</v>
+        <v>0.9000000568462708</v>
       </c>
       <c r="AM3">
-        <v>-0.009230982043640826</v>
+        <v>-0.009230982043994746</v>
       </c>
       <c r="AN3">
-        <v>-120.0000058494599</v>
+        <v>-120.0000058494594</v>
       </c>
       <c r="AO3">
-        <v>120.000002801495</v>
+        <v>120.0000028014946</v>
       </c>
       <c r="AP3">
-        <v>-0.009230981151952011</v>
+        <v>-0.009230981449429866</v>
       </c>
       <c r="AQ3">
-        <v>-120.0000058494595</v>
+        <v>-120.0000058494675</v>
       </c>
       <c r="AR3">
-        <v>120.0000028014947</v>
+        <v>120.0000028017999</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -8972,40 +8972,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>-5.851697786890256E-13</v>
+        <v>-5.851076498455831E-13</v>
       </c>
       <c r="O4">
-        <v>-7.376089896875712E-18</v>
+        <v>-2.472266514271948E-17</v>
       </c>
       <c r="P4">
-        <v>2.662795084228986E-16</v>
+        <v>1.170466967897226E-16</v>
       </c>
       <c r="Q4">
-        <v>5.851697786968212E-13</v>
+        <v>5.851076498507784E-13</v>
       </c>
       <c r="R4">
-        <v>7.376089896876977E-18</v>
+        <v>2.472266514278718E-17</v>
       </c>
       <c r="S4">
-        <v>-2.662795084228974E-16</v>
+        <v>-1.170466967903118E-16</v>
       </c>
       <c r="T4">
-        <v>4.784054038076974E-13</v>
+        <v>4.784182888573284E-13</v>
       </c>
       <c r="U4">
-        <v>3.032144539962199E-16</v>
+        <v>2.609724841789072E-16</v>
       </c>
       <c r="V4">
-        <v>-1.45219321787224E-16</v>
+        <v>-2.48397397327903E-16</v>
       </c>
       <c r="W4">
-        <v>-4.784054038049543E-13</v>
+        <v>-4.784182888554989E-13</v>
       </c>
       <c r="X4">
-        <v>-3.032144539962195E-16</v>
+        <v>-2.609724841798602E-16</v>
       </c>
       <c r="Y4">
-        <v>1.452193217872244E-16</v>
+        <v>2.48397397327095E-16</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -9026,40 +9026,40 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>0.8998226053398991</v>
+        <v>0.899822605339908</v>
       </c>
       <c r="AH4">
-        <v>0.8999999739229601</v>
+        <v>0.8999999739229599</v>
       </c>
       <c r="AI4">
-        <v>0.9000000568488989</v>
+        <v>0.9000000568488929</v>
       </c>
       <c r="AJ4">
-        <v>0.899822605345017</v>
+        <v>0.8998226053433176</v>
       </c>
       <c r="AK4">
-        <v>0.8999999739229588</v>
+        <v>0.899999973926239</v>
       </c>
       <c r="AL4">
-        <v>0.9000000568488963</v>
+        <v>0.9000000568473205</v>
       </c>
       <c r="AM4">
-        <v>-0.009230982043640826</v>
+        <v>-0.009230982043994746</v>
       </c>
       <c r="AN4">
-        <v>-120.0000058494599</v>
+        <v>-120.0000058494594</v>
       </c>
       <c r="AO4">
-        <v>120.000002801495</v>
+        <v>120.0000028014946</v>
       </c>
       <c r="AP4">
-        <v>-0.009230981508627516</v>
+        <v>-0.009230981687329928</v>
       </c>
       <c r="AQ4">
-        <v>-120.0000058494596</v>
+        <v>-120.0000058494644</v>
       </c>
       <c r="AR4">
-        <v>120.0000028014948</v>
+        <v>120.0000028016777</v>
       </c>
     </row>
   </sheetData>
@@ -9211,13 +9211,13 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>4.668197194885915E-05</v>
+        <v>4.66819643296966E-05</v>
       </c>
       <c r="C2">
-        <v>4.672529852501745E-05</v>
+        <v>4.672529244857401E-05</v>
       </c>
       <c r="D2">
-        <v>4.663867357042594E-05</v>
+        <v>4.663867694075198E-05</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -9229,13 +9229,13 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>1.078073978903609E-05</v>
+        <v>1.078073802946585E-05</v>
       </c>
       <c r="I2">
-        <v>1.079074563334842E-05</v>
+        <v>1.079074423005389E-05</v>
       </c>
       <c r="J2">
-        <v>1.077074045670954E-05</v>
+        <v>1.077074123505301E-05</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -9247,49 +9247,49 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>3.350191719571972E-09</v>
+        <v>3.348546834842865E-09</v>
       </c>
       <c r="O2">
-        <v>1.230986413905135E-17</v>
+        <v>1.232787242440564E-17</v>
       </c>
       <c r="P2">
-        <v>1.039137265775512E-17</v>
+        <v>1.035992420888159E-17</v>
       </c>
       <c r="Q2">
-        <v>-1.615851702396343E-12</v>
+        <v>2.800854337748585E-14</v>
       </c>
       <c r="R2">
-        <v>1.266379101315748E-12</v>
+        <v>1.266159225284705E-12</v>
       </c>
       <c r="S2">
-        <v>-2.876449865996319E-12</v>
+        <v>-2.876193041254016E-12</v>
       </c>
       <c r="T2">
-        <v>-1.131977941151797E-05</v>
+        <v>-1.131977756445478E-05</v>
       </c>
       <c r="U2">
-        <v>1.841651286024959E-17</v>
+        <v>1.836980231023077E-17</v>
       </c>
       <c r="V2">
-        <v>-2.003044585936415E-17</v>
+        <v>-1.960118449188398E-17</v>
       </c>
       <c r="W2">
-        <v>-2.392251564570578E-12</v>
+        <v>-4.240121892497338E-12</v>
       </c>
       <c r="X2">
-        <v>2.592186758710665E-12</v>
+        <v>2.591884565824931E-12</v>
       </c>
       <c r="Y2">
-        <v>-1.985939010329601E-13</v>
+        <v>-1.986274555535751E-13</v>
       </c>
       <c r="Z2">
-        <v>89.9830409438563</v>
+        <v>89.98304926678107</v>
       </c>
       <c r="AA2">
-        <v>89.95239308289068</v>
+        <v>89.9523958018829</v>
       </c>
       <c r="AB2">
-        <v>89.95230466839467</v>
+        <v>89.95230831594047</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -9301,7 +9301,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>1.050000290220336</v>
+        <v>1.050000290220286</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -9310,16 +9310,16 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>1.050139813505782</v>
+        <v>1.050139813520438</v>
       </c>
       <c r="AK2">
-        <v>0.0002498085071879114</v>
+        <v>0.0002498084633057758</v>
       </c>
       <c r="AL2">
-        <v>0.000249576963600323</v>
+        <v>0.000249576944946398</v>
       </c>
       <c r="AM2">
-        <v>-1.849333418587094E-06</v>
+        <v>-1.849330438355434E-06</v>
       </c>
       <c r="AN2">
         <v>0</v>
@@ -9328,13 +9328,13 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-0.01130059042159403</v>
+        <v>-0.01130058671894961</v>
       </c>
       <c r="AQ2">
-        <v>-56.04946840618023</v>
+        <v>-56.04945971402487</v>
       </c>
       <c r="AR2">
-        <v>-56.04955391074928</v>
+        <v>-56.04954475371046</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -9378,40 +9378,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>5.38615879980024E-13</v>
+        <v>9.552221619649455E-13</v>
       </c>
       <c r="O3">
-        <v>-4.221263489806517E-13</v>
+        <v>-4.22301193162765E-13</v>
       </c>
       <c r="P3">
-        <v>9.588165991342414E-13</v>
+        <v>9.587504209188922E-13</v>
       </c>
       <c r="Q3">
-        <v>-5.386158799719711E-13</v>
+        <v>-9.552221681144279E-13</v>
       </c>
       <c r="R3">
-        <v>4.222684763009461E-13</v>
+        <v>4.223919367462657E-13</v>
       </c>
       <c r="S3">
-        <v>-9.586743746913165E-13</v>
+        <v>-9.586042191678619E-13</v>
       </c>
       <c r="T3">
-        <v>7.974185294325228E-13</v>
+        <v>6.365426759241326E-13</v>
       </c>
       <c r="U3">
-        <v>-8.64062244648204E-13</v>
+        <v>-8.641465251777914E-13</v>
       </c>
       <c r="V3">
-        <v>6.619797203045549E-14</v>
+        <v>6.623249014458208E-14</v>
       </c>
       <c r="W3">
-        <v>-7.974185294270824E-13</v>
+        <v>-6.36542690949546E-13</v>
       </c>
       <c r="X3">
-        <v>8.641582674782146E-13</v>
+        <v>8.642676034135225E-13</v>
       </c>
       <c r="Y3">
-        <v>-6.610188358383156E-14</v>
+        <v>-6.619349765703354E-14</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -9432,40 +9432,40 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>1.050139813505782</v>
+        <v>1.050139813520438</v>
       </c>
       <c r="AH3">
-        <v>0.0002498085071879114</v>
+        <v>0.0002498084633057758</v>
       </c>
       <c r="AI3">
-        <v>0.000249576963600323</v>
+        <v>0.000249576944946398</v>
       </c>
       <c r="AJ3">
-        <v>1.050139813495943</v>
+        <v>1.050139825824685</v>
       </c>
       <c r="AK3">
-        <v>0.0002498471264653432</v>
+        <v>0.0002498470654215067</v>
       </c>
       <c r="AL3">
-        <v>0.0002495384010157196</v>
+        <v>0.0002495383694660382</v>
       </c>
       <c r="AM3">
-        <v>-0.01130059042159403</v>
+        <v>-0.01130058671894961</v>
       </c>
       <c r="AN3">
-        <v>-56.04946840618023</v>
+        <v>-56.04945971402487</v>
       </c>
       <c r="AO3">
-        <v>-56.04955391074928</v>
+        <v>-56.04954475371046</v>
       </c>
       <c r="AP3">
-        <v>-0.01130059020557701</v>
+        <v>-0.01130013282666222</v>
       </c>
       <c r="AQ3">
-        <v>-56.05456486094521</v>
+        <v>-56.0511493184167</v>
       </c>
       <c r="AR3">
-        <v>-56.05468540846118</v>
+        <v>-56.05126346373248</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -9509,40 +9509,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>5.386158918409999E-13</v>
+        <v>-6.362287158635585E-13</v>
       </c>
       <c r="O4">
-        <v>-4.221263697753666E-13</v>
+        <v>-4.218409110523776E-13</v>
       </c>
       <c r="P4">
-        <v>9.58816624091269E-13</v>
+        <v>9.586857972120393E-13</v>
       </c>
       <c r="Q4">
-        <v>-5.38615891836168E-13</v>
+        <v>6.362287324464266E-13</v>
       </c>
       <c r="R4">
-        <v>4.222116461706835E-13</v>
+        <v>4.218952932532584E-13</v>
       </c>
       <c r="S4">
-        <v>-9.58731289421313E-13</v>
+        <v>-9.585981013193564E-13</v>
       </c>
       <c r="T4">
-        <v>7.974185341741997E-13</v>
+        <v>2.547049791866139E-12</v>
       </c>
       <c r="U4">
-        <v>-8.640622530759474E-13</v>
+        <v>-8.637453411705615E-13</v>
       </c>
       <c r="V4">
-        <v>6.619797630661603E-14</v>
+        <v>6.659944005585981E-14</v>
       </c>
       <c r="W4">
-        <v>-7.974185341709353E-13</v>
+        <v>-2.547049806745445E-12</v>
       </c>
       <c r="X4">
-        <v>8.641198667762372E-13</v>
+        <v>8.638179605087116E-13</v>
       </c>
       <c r="Y4">
-        <v>-6.614032323546073E-14</v>
+        <v>-6.657599759535104E-14</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -9563,40 +9563,40 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>1.050139813505782</v>
+        <v>1.050139813520438</v>
       </c>
       <c r="AH4">
-        <v>0.0002498085071879114</v>
+        <v>0.0002498084633057758</v>
       </c>
       <c r="AI4">
-        <v>0.000249576963600323</v>
+        <v>0.000249576944946398</v>
       </c>
       <c r="AJ4">
-        <v>1.050139813499879</v>
+        <v>1.050139820902359</v>
       </c>
       <c r="AK4">
-        <v>0.0002498316785178714</v>
+        <v>0.0002498316232705855</v>
       </c>
       <c r="AL4">
-        <v>0.0002495538258087707</v>
+        <v>0.0002495538026319482</v>
       </c>
       <c r="AM4">
-        <v>-0.01130059042159403</v>
+        <v>-0.01130058671894961</v>
       </c>
       <c r="AN4">
-        <v>-56.04946840618023</v>
+        <v>-56.04945971402487</v>
       </c>
       <c r="AO4">
-        <v>-56.04955391074928</v>
+        <v>-56.04954475371046</v>
       </c>
       <c r="AP4">
-        <v>-0.01130059029198382</v>
+        <v>-0.01130031429330083</v>
       </c>
       <c r="AQ4">
-        <v>-56.05252646808786</v>
+        <v>-56.0504727423649</v>
       </c>
       <c r="AR4">
-        <v>-56.05263261914583</v>
+        <v>-56.05057680660726</v>
       </c>
     </row>
   </sheetData>
@@ -9748,13 +9748,13 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>4.890492702392472E-05</v>
+        <v>4.890492423726896E-05</v>
       </c>
       <c r="C2">
-        <v>4.895031677353423E-05</v>
+        <v>4.895031038743554E-05</v>
       </c>
       <c r="D2">
-        <v>4.885956681510263E-05</v>
+        <v>4.885956846051135E-05</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -9766,13 +9766,13 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>1.129410928108012E-05</v>
+        <v>1.129410863752953E-05</v>
       </c>
       <c r="I2">
-        <v>1.130459159489852E-05</v>
+        <v>1.130459012009217E-05</v>
       </c>
       <c r="J2">
-        <v>1.128363378941445E-05</v>
+        <v>1.128363416940532E-05</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -9784,49 +9784,49 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>3.67685519495808E-09</v>
+        <v>3.674720651491653E-09</v>
       </c>
       <c r="O2">
-        <v>3.820402875227395E-17</v>
+        <v>3.835324977018296E-17</v>
       </c>
       <c r="P2">
-        <v>1.264798341994832E-18</v>
+        <v>1.323195993039212E-18</v>
       </c>
       <c r="Q2">
-        <v>-1.773607944590161E-12</v>
+        <v>3.60238016506685E-13</v>
       </c>
       <c r="R2">
-        <v>1.389858434138071E-12</v>
+        <v>1.389605929069058E-12</v>
       </c>
       <c r="S2">
-        <v>-3.156920526440625E-12</v>
+        <v>-3.156714350298849E-12</v>
       </c>
       <c r="T2">
-        <v>-1.242352412268172E-05</v>
+        <v>-1.242352341540717E-05</v>
       </c>
       <c r="U2">
-        <v>2.273581926461343E-17</v>
+        <v>2.288905627597206E-17</v>
       </c>
       <c r="V2">
-        <v>-4.458881229046556E-17</v>
+        <v>-4.401501242625015E-17</v>
       </c>
       <c r="W2">
-        <v>-2.625529941992664E-12</v>
+        <v>-3.333766962555456E-12</v>
       </c>
       <c r="X2">
-        <v>2.84494007096116E-12</v>
+        <v>2.844622860921018E-12</v>
       </c>
       <c r="Y2">
-        <v>-2.179579780685569E-13</v>
+        <v>-2.18086391085315E-13</v>
       </c>
       <c r="Z2">
-        <v>89.98304085494074</v>
+        <v>89.98305069823287</v>
       </c>
       <c r="AA2">
-        <v>89.95239299552334</v>
+        <v>89.95239536246569</v>
       </c>
       <c r="AB2">
-        <v>89.95230458079857</v>
+        <v>89.95230887975193</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -9838,7 +9838,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>1.100000394683004</v>
+        <v>1.10000039468299</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -9847,16 +9847,16 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>1.100146561946468</v>
+        <v>1.100146561980871</v>
       </c>
       <c r="AK2">
-        <v>0.0002617041700154426</v>
+        <v>0.0002617041327635535</v>
       </c>
       <c r="AL2">
-        <v>0.0002614616043274386</v>
+        <v>0.0002614615885258088</v>
       </c>
       <c r="AM2">
-        <v>-1.937396942924354E-06</v>
+        <v>-1.937393514027851E-06</v>
       </c>
       <c r="AN2">
         <v>0</v>
@@ -9865,13 +9865,13 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-0.01130067848518257</v>
+        <v>-0.01130067553898963</v>
       </c>
       <c r="AQ2">
-        <v>-56.0494682669585</v>
+        <v>-56.04945884122931</v>
       </c>
       <c r="AR2">
-        <v>-56.04955374465615</v>
+        <v>-56.04954335138832</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -9915,40 +9915,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>5.912020388810133E-13</v>
+        <v>1.167537706030175E-12</v>
       </c>
       <c r="O3">
-        <v>-4.632861231066975E-13</v>
+        <v>-4.633176915113235E-13</v>
       </c>
       <c r="P3">
-        <v>1.052306819524692E-12</v>
+        <v>1.052251519322535E-12</v>
       </c>
       <c r="Q3">
-        <v>-5.912020388721744E-13</v>
+        <v>-1.167537711785353E-12</v>
       </c>
       <c r="R3">
-        <v>4.634421086667246E-13</v>
+        <v>4.63417254692651E-13</v>
       </c>
       <c r="S3">
-        <v>-1.052150727370922E-12</v>
+        <v>-1.05209105787637E-12</v>
       </c>
       <c r="T3">
-        <v>8.751783107183451E-13</v>
+        <v>1.000347210627104E-12</v>
       </c>
       <c r="U3">
-        <v>-9.483133457244661E-13</v>
+        <v>-9.484003758591657E-13</v>
       </c>
       <c r="V3">
-        <v>7.265266696894096E-14</v>
+        <v>7.25498392643746E-14</v>
       </c>
       <c r="W3">
-        <v>-8.751783107123734E-13</v>
+        <v>-1.000347231598753E-12</v>
       </c>
       <c r="X3">
-        <v>9.484187313384118E-13</v>
+        <v>9.485332643025797E-13</v>
       </c>
       <c r="Y3">
-        <v>-7.254720933907335E-14</v>
+        <v>-7.250705810878926E-14</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -9969,40 +9969,40 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>1.100146561946468</v>
+        <v>1.100146561980871</v>
       </c>
       <c r="AH3">
-        <v>0.0002617041700154426</v>
+        <v>0.0002617041327635535</v>
       </c>
       <c r="AI3">
-        <v>0.0002614616043274386</v>
+        <v>0.0002614615885258088</v>
       </c>
       <c r="AJ3">
-        <v>1.100146561936159</v>
+        <v>1.100146574871856</v>
       </c>
       <c r="AK3">
-        <v>0.0002617446283086495</v>
+        <v>0.0002617445728087334</v>
       </c>
       <c r="AL3">
-        <v>0.0002614212054263953</v>
+        <v>0.0002614211766537528</v>
       </c>
       <c r="AM3">
-        <v>-0.01130067848518257</v>
+        <v>-0.01130067553898963</v>
       </c>
       <c r="AN3">
-        <v>-56.0494682669585</v>
+        <v>-56.04945884122931</v>
       </c>
       <c r="AO3">
-        <v>-56.04955374465615</v>
+        <v>-56.04954335138832</v>
       </c>
       <c r="AP3">
-        <v>-0.0113006782691833</v>
+        <v>-0.01130022160102711</v>
       </c>
       <c r="AQ3">
-        <v>-56.05456472170016</v>
+        <v>-56.05114826354445</v>
       </c>
       <c r="AR3">
-        <v>-56.05468524223646</v>
+        <v>-56.05126249984399</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -10046,40 +10046,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>5.912020438528955E-13</v>
+        <v>1.334366396966134E-12</v>
       </c>
       <c r="O4">
-        <v>-4.632861479043516E-13</v>
+        <v>-4.63119600158254E-13</v>
       </c>
       <c r="P4">
-        <v>1.052306844994674E-12</v>
+        <v>1.052253467589471E-12</v>
       </c>
       <c r="Q4">
-        <v>-5.912020438475923E-13</v>
+        <v>-1.334366400003974E-12</v>
       </c>
       <c r="R4">
-        <v>4.633797392440334E-13</v>
+        <v>4.631793064112029E-13</v>
       </c>
       <c r="S4">
-        <v>-1.052213189698017E-12</v>
+        <v>-1.05215719496576E-12</v>
       </c>
       <c r="T4">
-        <v>8.751783206572086E-13</v>
+        <v>1.333840135923061E-12</v>
       </c>
       <c r="U4">
-        <v>-9.483133565818496E-13</v>
+        <v>-9.484104778291789E-13</v>
       </c>
       <c r="V4">
-        <v>7.265267245203656E-14</v>
+        <v>7.212114737750333E-14</v>
       </c>
       <c r="W4">
-        <v>-8.751783206536257E-13</v>
+        <v>-1.333840151643789E-12</v>
       </c>
       <c r="X4">
-        <v>9.483765879528364E-13</v>
+        <v>9.484902166276184E-13</v>
       </c>
       <c r="Y4">
-        <v>-7.258939787089397E-14</v>
+        <v>-7.209550766038774E-14</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -10100,40 +10100,40 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>1.100146561946468</v>
+        <v>1.100146561980871</v>
       </c>
       <c r="AH4">
-        <v>0.0002617041700154426</v>
+        <v>0.0002617041327635535</v>
       </c>
       <c r="AI4">
-        <v>0.0002614616043274386</v>
+        <v>0.0002614615885258088</v>
       </c>
       <c r="AJ4">
-        <v>1.100146561940282</v>
+        <v>1.100146569714314</v>
       </c>
       <c r="AK4">
-        <v>0.0002617284447436158</v>
+        <v>0.0002617283955854921</v>
       </c>
       <c r="AL4">
-        <v>0.0002614373647345591</v>
+        <v>0.0002614373441949573</v>
       </c>
       <c r="AM4">
-        <v>-0.01130067848518257</v>
+        <v>-0.01130067553898963</v>
       </c>
       <c r="AN4">
-        <v>-56.0494682669585</v>
+        <v>-56.04945884122931</v>
       </c>
       <c r="AO4">
-        <v>-56.04955374465615</v>
+        <v>-56.04954335138832</v>
       </c>
       <c r="AP4">
-        <v>-0.01130067835558301</v>
+        <v>-0.01130040311335149</v>
       </c>
       <c r="AQ4">
-        <v>-56.05252632884804</v>
+        <v>-56.05047186958654</v>
       </c>
       <c r="AR4">
-        <v>-56.05263245296076</v>
+        <v>-56.05057540413078</v>
       </c>
     </row>
   </sheetData>
@@ -10321,40 +10321,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-1.701814682305212E-09</v>
+        <v>-1.701815006303854E-09</v>
       </c>
       <c r="O2">
-        <v>-9.53739656459247E-10</v>
+        <v>-9.537392466993021E-10</v>
       </c>
       <c r="P2">
-        <v>2.651096089311413E-09</v>
+        <v>2.651096332419168E-09</v>
       </c>
       <c r="Q2">
-        <v>-6.567642840658118E-16</v>
+        <v>-3.329512117437431E-16</v>
       </c>
       <c r="R2">
-        <v>2.229377202204292E-12</v>
+        <v>2.228967491257432E-12</v>
       </c>
       <c r="S2">
-        <v>2.229717879750488E-12</v>
+        <v>2.229474901435164E-12</v>
       </c>
       <c r="T2">
-        <v>-2.081891632572137E-09</v>
+        <v>-2.081891451132352E-09</v>
       </c>
       <c r="U2">
-        <v>2.516265261399469E-09</v>
+        <v>2.516265028182975E-09</v>
       </c>
       <c r="V2">
-        <v>-4.313645609339966E-10</v>
+        <v>-4.313647335117327E-10</v>
       </c>
       <c r="W2">
-        <v>-1.969571741488205E-16</v>
+        <v>-3.784455942948951E-16</v>
       </c>
       <c r="X2">
-        <v>-1.823239088447361E-12</v>
+        <v>-1.823005688745928E-12</v>
       </c>
       <c r="Y2">
-        <v>-1.824376621998415E-12</v>
+        <v>-1.824204183116636E-12</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -10384,16 +10384,16 @@
         <v>1.049806898934537</v>
       </c>
       <c r="AJ2">
-        <v>1.050000009179003</v>
+        <v>1.050000009179007</v>
       </c>
       <c r="AK2">
-        <v>1.049806885266585</v>
+        <v>1.049806885266574</v>
       </c>
       <c r="AL2">
-        <v>1.049806855745433</v>
+        <v>1.049806855745438</v>
       </c>
       <c r="AM2">
-        <v>2.43296385090606E-09</v>
+        <v>2.432964408224544E-09</v>
       </c>
       <c r="AN2">
         <v>-120.0086185415377</v>
@@ -10402,13 +10402,13 @@
         <v>119.9913814520988</v>
       </c>
       <c r="AP2">
-        <v>-9.305150854999467E-07</v>
+        <v>-9.305144203573285E-07</v>
       </c>
       <c r="AQ2">
-        <v>-120.0086153889644</v>
+        <v>-120.0086153889648</v>
       </c>
       <c r="AR2">
-        <v>119.9913792354995</v>
+        <v>119.991379235499</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -10452,40 +10452,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>2.189214621844975E-16</v>
+        <v>2.331468409958625E-16</v>
       </c>
       <c r="O3">
-        <v>-7.431257297765805E-13</v>
+        <v>-7.430219763522513E-13</v>
       </c>
       <c r="P3">
-        <v>-7.432392821871856E-13</v>
+        <v>-7.432585781823509E-13</v>
       </c>
       <c r="Q3">
-        <v>-2.189214621844971E-16</v>
+        <v>-2.331468409953368E-16</v>
       </c>
       <c r="R3">
-        <v>7.431257297846003E-13</v>
+        <v>7.43021976357367E-13</v>
       </c>
       <c r="S3">
-        <v>7.43239282195211E-13</v>
+        <v>7.432585781906019E-13</v>
       </c>
       <c r="T3">
-        <v>6.565243210779879E-17</v>
+        <v>2.331468334230013E-16</v>
       </c>
       <c r="U3">
-        <v>6.077463473301583E-13</v>
+        <v>6.075152542895653E-13</v>
       </c>
       <c r="V3">
-        <v>6.081255214978397E-13</v>
+        <v>6.082116388263866E-13</v>
       </c>
       <c r="W3">
-        <v>-6.56524321077985E-17</v>
+        <v>-2.331468334239766E-16</v>
       </c>
       <c r="X3">
-        <v>-6.077463473247399E-13</v>
+        <v>-6.075152542827344E-13</v>
       </c>
       <c r="Y3">
-        <v>-6.081255214924178E-13</v>
+        <v>-6.082116388241857E-13</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -10506,40 +10506,40 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>1.050000009179003</v>
+        <v>1.050000009179007</v>
       </c>
       <c r="AH3">
-        <v>1.049806885266585</v>
+        <v>1.049806885266574</v>
       </c>
       <c r="AI3">
-        <v>1.049806855745433</v>
+        <v>1.049806855745438</v>
       </c>
       <c r="AJ3">
-        <v>1.050000009179001</v>
+        <v>1.05000000918002</v>
       </c>
       <c r="AK3">
-        <v>1.049806885269623</v>
+        <v>1.049806885266177</v>
       </c>
       <c r="AL3">
-        <v>1.04980685574847</v>
+        <v>1.049806855750895</v>
       </c>
       <c r="AM3">
-        <v>-9.305150854999467E-07</v>
+        <v>-9.305144203573285E-07</v>
       </c>
       <c r="AN3">
-        <v>-120.0086153889644</v>
+        <v>-120.0086153889648</v>
       </c>
       <c r="AO3">
-        <v>119.9913792354995</v>
+        <v>119.991379235499</v>
       </c>
       <c r="AP3">
-        <v>-9.305151264962549E-07</v>
+        <v>-9.303299770339932E-07</v>
       </c>
       <c r="AQ3">
-        <v>-120.0086153884111</v>
+        <v>-120.0086153884558</v>
       </c>
       <c r="AR3">
-        <v>119.991379236053</v>
+        <v>119.9913792359123</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -10583,40 +10583,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>2.189214639215768E-16</v>
+        <v>1.554312248062879E-16</v>
       </c>
       <c r="O4">
-        <v>-7.431257467526669E-13</v>
+        <v>-7.430115402709891E-13</v>
       </c>
       <c r="P4">
-        <v>-7.432392957772301E-13</v>
+        <v>-7.431808971164527E-13</v>
       </c>
       <c r="Q4">
-        <v>-2.189214639215765E-16</v>
+        <v>-1.554312248063778E-16</v>
       </c>
       <c r="R4">
-        <v>7.431257467574786E-13</v>
+        <v>7.430115402740596E-13</v>
       </c>
       <c r="S4">
-        <v>7.432392957820455E-13</v>
+        <v>7.431808971214021E-13</v>
       </c>
       <c r="T4">
-        <v>6.565242805461374E-17</v>
+        <v>-2.524287081617154E-24</v>
       </c>
       <c r="U4">
-        <v>6.077463653496953E-13</v>
+        <v>6.076886860126842E-13</v>
       </c>
       <c r="V4">
-        <v>6.08125535557172E-13</v>
+        <v>6.080770445094798E-13</v>
       </c>
       <c r="W4">
-        <v>-6.565242805461355E-17</v>
+        <v>2.523986791890558E-24</v>
       </c>
       <c r="X4">
-        <v>-6.077463653464443E-13</v>
+        <v>-6.076886860085859E-13</v>
       </c>
       <c r="Y4">
-        <v>-6.081255355539188E-13</v>
+        <v>-6.08077044508159E-13</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -10637,40 +10637,40 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>1.050000009179003</v>
+        <v>1.050000009179007</v>
       </c>
       <c r="AH4">
-        <v>1.049806885266585</v>
+        <v>1.049806885266574</v>
       </c>
       <c r="AI4">
-        <v>1.049806855745433</v>
+        <v>1.049806855745438</v>
       </c>
       <c r="AJ4">
-        <v>1.050000009179002</v>
+        <v>1.050000009179614</v>
       </c>
       <c r="AK4">
-        <v>1.049806885268408</v>
+        <v>1.049806885266336</v>
       </c>
       <c r="AL4">
-        <v>1.049806855747255</v>
+        <v>1.049806855748712</v>
       </c>
       <c r="AM4">
-        <v>-9.305150854999467E-07</v>
+        <v>-9.305144203573285E-07</v>
       </c>
       <c r="AN4">
-        <v>-120.0086153889644</v>
+        <v>-120.0086153889648</v>
       </c>
       <c r="AO4">
-        <v>119.9913792354995</v>
+        <v>119.991379235499</v>
       </c>
       <c r="AP4">
-        <v>-9.305151100977329E-07</v>
+        <v>-9.304037261639954E-07</v>
       </c>
       <c r="AQ4">
-        <v>-120.0086153886324</v>
+        <v>-120.0086153886594</v>
       </c>
       <c r="AR4">
-        <v>119.9913792358316</v>
+        <v>119.991379235747</v>
       </c>
     </row>
   </sheetData>
@@ -10858,40 +10858,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-1.956657864077696E-09</v>
+        <v>-1.95665846008143E-09</v>
       </c>
       <c r="O2">
-        <v>-1.096560196436495E-09</v>
+        <v>-1.096559825000392E-09</v>
       </c>
       <c r="P2">
-        <v>3.048092208074996E-09</v>
+        <v>3.048092448689238E-09</v>
       </c>
       <c r="Q2">
-        <v>-7.551629698270654E-16</v>
+        <v>-1.593188349340453E-16</v>
       </c>
       <c r="R2">
-        <v>2.563221729021672E-12</v>
+        <v>2.562850194199798E-12</v>
       </c>
       <c r="S2">
-        <v>2.563613352966517E-12</v>
+        <v>2.563372998946609E-12</v>
       </c>
       <c r="T2">
-        <v>-2.393685547650799E-09</v>
+        <v>-2.393685767782809E-09</v>
       </c>
       <c r="U2">
-        <v>2.893070736928143E-09</v>
+        <v>2.893070669039162E-09</v>
       </c>
       <c r="V2">
-        <v>-4.959604911800325E-10</v>
+        <v>-4.959607756165919E-10</v>
       </c>
       <c r="W2">
-        <v>-2.264280618034632E-16</v>
+        <v>-6.502895611082211E-18</v>
       </c>
       <c r="X2">
-        <v>-2.096265215262696E-12</v>
+        <v>-2.096197084972154E-12</v>
       </c>
       <c r="Y2">
-        <v>-2.097573177779616E-12</v>
+        <v>-2.097288774615012E-12</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -10921,16 +10921,16 @@
         <v>1.099788147881465</v>
       </c>
       <c r="AJ2">
-        <v>1.100000086251851</v>
+        <v>1.100000086251867</v>
       </c>
       <c r="AK2">
-        <v>1.099788132876907</v>
+        <v>1.099788132876894</v>
       </c>
       <c r="AL2">
-        <v>1.099788100481589</v>
+        <v>1.09978810048159</v>
       </c>
       <c r="AM2">
-        <v>2.67013950835123E-09</v>
+        <v>2.670140400824206E-09</v>
       </c>
       <c r="AN2">
         <v>-120.0090288691279</v>
@@ -10939,13 +10939,13 @@
         <v>119.9909711238891</v>
       </c>
       <c r="AP2">
-        <v>-9.747187589925977E-07</v>
+        <v>-9.747183093687914E-07</v>
       </c>
       <c r="AQ2">
-        <v>-120.0090255664319</v>
+        <v>-120.0090255664318</v>
       </c>
       <c r="AR2">
-        <v>119.9909688017373</v>
+        <v>119.9909688017365</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -10989,40 +10989,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>2.517203166172972E-16</v>
+        <v>2.035409065778641E-16</v>
       </c>
       <c r="O3">
-        <v>-8.54407239092486E-13</v>
+        <v>-8.542946933580946E-13</v>
       </c>
       <c r="P3">
-        <v>-8.545377736424285E-13</v>
+        <v>-8.544902017504707E-13</v>
       </c>
       <c r="Q3">
-        <v>-2.517203166172967E-16</v>
+        <v>-2.035409065775205E-16</v>
       </c>
       <c r="R3">
-        <v>8.544072391021457E-13</v>
+        <v>8.542946933642587E-13</v>
       </c>
       <c r="S3">
-        <v>8.545377736520951E-13</v>
+        <v>8.544902017604085E-13</v>
       </c>
       <c r="T3">
-        <v>7.547681423507136E-17</v>
+        <v>1.628327195835506E-16</v>
       </c>
       <c r="U3">
-        <v>6.987550520419038E-13</v>
+        <v>6.987069826633464E-13</v>
       </c>
       <c r="V3">
-        <v>6.991910357856181E-13</v>
+        <v>6.992251771838918E-13</v>
       </c>
       <c r="W3">
-        <v>-7.547681423507097E-17</v>
+        <v>-1.628327195844015E-16</v>
       </c>
       <c r="X3">
-        <v>-6.987550520353775E-13</v>
+        <v>-6.987069826551185E-13</v>
       </c>
       <c r="Y3">
-        <v>-6.991910357790874E-13</v>
+        <v>-6.992251771812409E-13</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -11043,40 +11043,40 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>1.100000086251851</v>
+        <v>1.100000086251867</v>
       </c>
       <c r="AH3">
-        <v>1.099788132876907</v>
+        <v>1.099788132876894</v>
       </c>
       <c r="AI3">
-        <v>1.099788100481589</v>
+        <v>1.09978810048159</v>
       </c>
       <c r="AJ3">
-        <v>1.100000086251848</v>
+        <v>1.100000086252978</v>
       </c>
       <c r="AK3">
-        <v>1.099788132880241</v>
+        <v>1.099788132876458</v>
       </c>
       <c r="AL3">
-        <v>1.099788100484921</v>
+        <v>1.099788100487578</v>
       </c>
       <c r="AM3">
-        <v>-9.747187589925977E-07</v>
+        <v>-9.747183093687914E-07</v>
       </c>
       <c r="AN3">
-        <v>-120.0090255664319</v>
+        <v>-120.0090255664318</v>
       </c>
       <c r="AO3">
-        <v>119.9909688017373</v>
+        <v>119.9909688017365</v>
       </c>
       <c r="AP3">
-        <v>-9.747188019483638E-07</v>
+        <v>-9.745250841757035E-07</v>
       </c>
       <c r="AQ3">
-        <v>-120.0090255658522</v>
+        <v>-120.0090255658986</v>
       </c>
       <c r="AR3">
-        <v>119.9909688023173</v>
+        <v>119.9909688021696</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -11120,40 +11120,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>2.517203178304955E-16</v>
+        <v>5.540234825892299E-24</v>
       </c>
       <c r="O4">
-        <v>-8.54407245166061E-13</v>
+        <v>-8.540613589541138E-13</v>
       </c>
       <c r="P4">
-        <v>-8.545377916045984E-13</v>
+        <v>-8.538230576266527E-13</v>
       </c>
       <c r="Q4">
-        <v>-2.517203178304951E-16</v>
+        <v>-5.539575693677951E-24</v>
       </c>
       <c r="R4">
-        <v>8.544072451718568E-13</v>
+        <v>8.540613589578135E-13</v>
       </c>
       <c r="S4">
-        <v>8.545377916103983E-13</v>
+        <v>8.538230576326115E-13</v>
       </c>
       <c r="T4">
-        <v>7.547680998887719E-17</v>
+        <v>3.256654460923947E-16</v>
       </c>
       <c r="U4">
-        <v>6.987550713276754E-13</v>
+        <v>6.98948225778888E-13</v>
       </c>
       <c r="V4">
-        <v>6.991910569690182E-13</v>
+        <v>6.990463037418899E-13</v>
       </c>
       <c r="W4">
-        <v>-7.547680998887695E-17</v>
+        <v>-3.25665446092592E-16</v>
       </c>
       <c r="X4">
-        <v>-6.987550713237595E-13</v>
+        <v>-6.989482257739528E-13</v>
       </c>
       <c r="Y4">
-        <v>-6.991910569650998E-13</v>
+        <v>-6.990463037403012E-13</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -11174,40 +11174,40 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>1.100000086251851</v>
+        <v>1.100000086251867</v>
       </c>
       <c r="AH4">
-        <v>1.099788132876907</v>
+        <v>1.099788132876894</v>
       </c>
       <c r="AI4">
-        <v>1.099788100481589</v>
+        <v>1.09978810048159</v>
       </c>
       <c r="AJ4">
-        <v>1.10000008625185</v>
+        <v>1.100000086252533</v>
       </c>
       <c r="AK4">
-        <v>1.099788132878908</v>
+        <v>1.099788132876632</v>
       </c>
       <c r="AL4">
-        <v>1.099788100483588</v>
+        <v>1.099788100485182</v>
       </c>
       <c r="AM4">
-        <v>-9.747187589925977E-07</v>
+        <v>-9.747183093687914E-07</v>
       </c>
       <c r="AN4">
-        <v>-120.0090255664319</v>
+        <v>-120.0090255664318</v>
       </c>
       <c r="AO4">
-        <v>119.9909688017373</v>
+        <v>119.9909688017365</v>
       </c>
       <c r="AP4">
-        <v>-9.747187847660582E-07</v>
+        <v>-9.746023452876504E-07</v>
       </c>
       <c r="AQ4">
-        <v>-120.0090255660841</v>
+        <v>-120.0090255661119</v>
       </c>
       <c r="AR4">
-        <v>119.9909688020853</v>
+        <v>119.9909688019963</v>
       </c>
     </row>
   </sheetData>
@@ -11359,13 +11359,13 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>4.223604173205168E-05</v>
+        <v>4.223604541554004E-05</v>
       </c>
       <c r="C2">
-        <v>4.227524810876407E-05</v>
+        <v>4.227524666334303E-05</v>
       </c>
       <c r="D2">
-        <v>4.219687317699356E-05</v>
+        <v>4.21968731771389E-05</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -11377,13 +11377,13 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>9.753996170747591E-06</v>
+        <v>9.753997021412802E-06</v>
       </c>
       <c r="I2">
-        <v>9.763050495742049E-06</v>
+        <v>9.763050161936355E-06</v>
       </c>
       <c r="J2">
-        <v>9.74495058029017E-06</v>
+        <v>9.744950580323735E-06</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -11395,49 +11395,49 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>5.263054396895508E-09</v>
+        <v>5.262858613750324E-09</v>
       </c>
       <c r="O2">
-        <v>5.561607938911272E-18</v>
+        <v>5.774010912163998E-18</v>
       </c>
       <c r="P2">
-        <v>-1.843835823677933E-17</v>
+        <v>-1.858222934469635E-17</v>
       </c>
       <c r="Q2">
-        <v>-1.320104175999383E-12</v>
+        <v>-1.123792374561137E-12</v>
       </c>
       <c r="R2">
-        <v>2.598041296677462E-12</v>
+        <v>2.597966032466522E-12</v>
       </c>
       <c r="S2">
-        <v>-3.912105492113073E-12</v>
+        <v>-3.91218856248567E-12</v>
       </c>
       <c r="T2">
-        <v>-9.266298123571966E-06</v>
+        <v>-9.266298931815828E-06</v>
       </c>
       <c r="U2">
-        <v>-1.870390075196176E-17</v>
+        <v>-1.866410314206231E-17</v>
       </c>
       <c r="V2">
-        <v>4.361356250859589E-18</v>
+        <v>4.340639815996176E-18</v>
       </c>
       <c r="W2">
-        <v>-3.75899966096665E-12</v>
+        <v>-2.950751814212393E-12</v>
       </c>
       <c r="X2">
-        <v>3.018755350116535E-12</v>
+        <v>3.018585440730985E-12</v>
       </c>
       <c r="Y2">
-        <v>7.412965296814728E-13</v>
+        <v>7.415332882586744E-13</v>
       </c>
       <c r="Z2">
-        <v>89.96745515836426</v>
+        <v>89.96745637177743</v>
       </c>
       <c r="AA2">
-        <v>89.93682173753396</v>
+        <v>89.93682382195186</v>
       </c>
       <c r="AB2">
-        <v>89.93670440148045</v>
+        <v>89.93670052992074</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -11449,7 +11449,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.9500003338130747</v>
+        <v>0.9500003338131056</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -11458,16 +11458,16 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>0.9501262288408601</v>
+        <v>0.950126228851771</v>
       </c>
       <c r="AK2">
-        <v>0.0003812290955401742</v>
+        <v>0.0003812290990904399</v>
       </c>
       <c r="AL2">
-        <v>0.0003808757736725349</v>
+        <v>0.000380875783795502</v>
       </c>
       <c r="AM2">
-        <v>-2.097178818759875E-06</v>
+        <v>-2.09717856006385E-06</v>
       </c>
       <c r="AN2">
         <v>0</v>
@@ -11476,13 +11476,13 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-0.02169189043536323</v>
+        <v>-0.0216918919110005</v>
       </c>
       <c r="AQ2">
-        <v>-70.73380977207721</v>
+        <v>-70.73380901191339</v>
       </c>
       <c r="AR2">
-        <v>-70.73392136589861</v>
+        <v>-70.73392358168618</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -11526,40 +11526,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>4.400342117425012E-13</v>
+        <v>1.152506769341129E-12</v>
       </c>
       <c r="O3">
-        <v>-8.66013723894183E-13</v>
+        <v>-8.660057250295882E-13</v>
       </c>
       <c r="P3">
-        <v>1.304035122068881E-12</v>
+        <v>1.304143605209607E-12</v>
       </c>
       <c r="Q3">
-        <v>-4.400342117065266E-13</v>
+        <v>-1.15250678842863E-12</v>
       </c>
       <c r="R3">
-        <v>8.662370351944379E-13</v>
+        <v>8.661691534285883E-13</v>
       </c>
       <c r="S3">
-        <v>-1.303811517733816E-12</v>
+        <v>-1.303934598465079E-12</v>
       </c>
       <c r="T3">
-        <v>1.253000000926736E-12</v>
+        <v>8.636984998401014E-13</v>
       </c>
       <c r="U3">
-        <v>-1.006251759156729E-12</v>
+        <v>-1.006558813499763E-12</v>
       </c>
       <c r="V3">
-        <v>-2.470988246118487E-13</v>
+        <v>-2.473707419338895E-13</v>
       </c>
       <c r="W3">
-        <v>-1.253000000914077E-12</v>
+        <v>-8.636985284109113E-13</v>
       </c>
       <c r="X3">
-        <v>1.006330338139931E-12</v>
+        <v>1.006688898311093E-12</v>
       </c>
       <c r="Y3">
-        <v>2.471775067081909E-13</v>
+        <v>2.473717422614547E-13</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -11580,40 +11580,40 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>0.9501262288408601</v>
+        <v>0.950126228851771</v>
       </c>
       <c r="AH3">
-        <v>0.0003812290955401742</v>
+        <v>0.0003812290990904399</v>
       </c>
       <c r="AI3">
-        <v>0.0003808757736725349</v>
+        <v>0.000380875783795502</v>
       </c>
       <c r="AJ3">
-        <v>0.9501262288237869</v>
+        <v>0.9501262502316646</v>
       </c>
       <c r="AK3">
-        <v>0.0003812880296418253</v>
+        <v>0.0003812880131815352</v>
       </c>
       <c r="AL3">
-        <v>0.0003808169333989446</v>
+        <v>0.0003808169168244723</v>
       </c>
       <c r="AM3">
-        <v>-0.02169189043536323</v>
+        <v>-0.0216918919110005</v>
       </c>
       <c r="AN3">
-        <v>-70.73380977207721</v>
+        <v>-70.73380901191339</v>
       </c>
       <c r="AO3">
-        <v>-70.73392136589861</v>
+        <v>-70.73392358168618</v>
       </c>
       <c r="AP3">
-        <v>-0.02169188915192811</v>
+        <v>-0.0216914377370214</v>
       </c>
       <c r="AQ3">
-        <v>-70.73890156133632</v>
+        <v>-70.73549357842177</v>
       </c>
       <c r="AR3">
-        <v>-70.73905652208137</v>
+        <v>-70.73564750941759</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -11657,40 +11657,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>4.400342375095349E-13</v>
+        <v>8.64570918612256E-13</v>
       </c>
       <c r="O4">
-        <v>-8.660137620221589E-13</v>
+        <v>-8.663711676992235E-13</v>
       </c>
       <c r="P4">
-        <v>1.30403516130865E-12</v>
+        <v>1.303996504303755E-12</v>
       </c>
       <c r="Q4">
-        <v>-4.400342374879502E-13</v>
+        <v>-8.645709248051765E-13</v>
       </c>
       <c r="R4">
-        <v>8.661477488110103E-13</v>
+        <v>8.664692607674433E-13</v>
       </c>
       <c r="S4">
-        <v>-1.30390099869943E-12</v>
+        <v>-1.303871118735056E-12</v>
       </c>
       <c r="T4">
-        <v>1.253000037400716E-12</v>
+        <v>1.151852455262014E-12</v>
       </c>
       <c r="U4">
-        <v>-1.006251783692686E-12</v>
+        <v>-1.006564115682103E-12</v>
       </c>
       <c r="V4">
-        <v>-2.470988407592501E-13</v>
+        <v>-2.472998397501224E-13</v>
       </c>
       <c r="W4">
-        <v>-1.253000037393121E-12</v>
+        <v>-1.151852474926667E-12</v>
       </c>
       <c r="X4">
-        <v>1.006298931085299E-12</v>
+        <v>1.006642159866809E-12</v>
       </c>
       <c r="Y4">
-        <v>2.471460500200132E-13</v>
+        <v>2.473004439438067E-13</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -11711,40 +11711,40 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>0.9501262288408601</v>
+        <v>0.950126228851771</v>
       </c>
       <c r="AH4">
-        <v>0.0003812290955401742</v>
+        <v>0.0003812290990904399</v>
       </c>
       <c r="AI4">
-        <v>0.0003808757736725349</v>
+        <v>0.000380875783795502</v>
       </c>
       <c r="AJ4">
-        <v>0.9501262288306161</v>
+        <v>0.9501262416796955</v>
       </c>
       <c r="AK4">
-        <v>0.0003812644556411018</v>
+        <v>0.0003812644477272572</v>
       </c>
       <c r="AL4">
-        <v>0.0003808404691403564</v>
+        <v>0.0003808404645784839</v>
       </c>
       <c r="AM4">
-        <v>-0.02169189043536323</v>
+        <v>-0.0216918919110005</v>
       </c>
       <c r="AN4">
-        <v>-70.73380977207721</v>
+        <v>-70.73380901191339</v>
       </c>
       <c r="AO4">
-        <v>-70.73392136589861</v>
+        <v>-70.73392358168618</v>
       </c>
       <c r="AP4">
-        <v>-0.02169188966530214</v>
+        <v>-0.02169161932836459</v>
       </c>
       <c r="AQ4">
-        <v>-70.73686503458575</v>
+        <v>-70.73481990233215</v>
       </c>
       <c r="AR4">
-        <v>-70.73700226932468</v>
+        <v>-70.73495784903415</v>
       </c>
     </row>
   </sheetData>
@@ -12118,13 +12118,13 @@
         <v>17</v>
       </c>
       <c r="B2">
-        <v>4.00130908430465E-05</v>
+        <v>4.001309227149915E-05</v>
       </c>
       <c r="C2">
-        <v>4.005023372563329E-05</v>
+        <v>4.005023110463789E-05</v>
       </c>
       <c r="D2">
-        <v>3.997598379128892E-05</v>
+        <v>3.997598438859087E-05</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -12136,13 +12136,13 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>9.240627645432819E-06</v>
+        <v>9.240627975319832E-06</v>
       </c>
       <c r="I2">
-        <v>9.249205426864622E-06</v>
+        <v>9.249204821571654E-06</v>
       </c>
       <c r="J2">
-        <v>9.232058138776695E-06</v>
+        <v>9.232058276717676E-06</v>
       </c>
       <c r="K2">
         <v>0</v>
@@ -12154,49 +12154,49 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>4.723627259168305E-09</v>
+        <v>4.723814932457247E-09</v>
       </c>
       <c r="O2">
-        <v>8.445750168278392E-18</v>
+        <v>8.541210971909475E-18</v>
       </c>
       <c r="P2">
-        <v>2.065975261109884E-18</v>
+        <v>2.182894228690185E-18</v>
       </c>
       <c r="Q2">
-        <v>-1.184624525357772E-12</v>
+        <v>-1.372126428900454E-12</v>
       </c>
       <c r="R2">
-        <v>2.331759952998385E-12</v>
+        <v>2.331562806404917E-12</v>
       </c>
       <c r="S2">
-        <v>-3.511141600893914E-12</v>
+        <v>-3.511212951283787E-12</v>
       </c>
       <c r="T2">
-        <v>-8.316566186491665E-06</v>
+        <v>-8.316566483283621E-06</v>
       </c>
       <c r="U2">
-        <v>6.740950658752901E-18</v>
+        <v>6.774942075857585E-18</v>
       </c>
       <c r="V2">
-        <v>-1.081314811754592E-17</v>
+        <v>-1.087810416055226E-17</v>
       </c>
       <c r="W2">
-        <v>-3.373707475745143E-12</v>
+        <v>-3.076405550589519E-12</v>
       </c>
       <c r="X2">
-        <v>2.709353688754808E-12</v>
+        <v>2.709255682966113E-12</v>
       </c>
       <c r="Y2">
-        <v>6.653187076864585E-13</v>
+        <v>6.656735940844038E-13</v>
       </c>
       <c r="Z2">
-        <v>89.96745527010033</v>
+        <v>89.96745397831364</v>
       </c>
       <c r="AA2">
-        <v>89.93682184733709</v>
+        <v>89.93682230954161</v>
       </c>
       <c r="AB2">
-        <v>89.93670451152548</v>
+        <v>89.93669835092092</v>
       </c>
       <c r="AC2">
         <v>0</v>
@@ -12208,7 +12208,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.9000002864589381</v>
+        <v>0.9000002864589485</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -12217,16 +12217,16 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>0.9001195554286869</v>
+        <v>0.9001195554053522</v>
       </c>
       <c r="AK2">
-        <v>0.0003611643931572446</v>
+        <v>0.0003611643786635592</v>
       </c>
       <c r="AL2">
-        <v>0.0003608296670016657</v>
+        <v>0.000360829667038422</v>
       </c>
       <c r="AM2">
-        <v>-1.986800960446687E-06</v>
+        <v>-1.986801476760755E-06</v>
       </c>
       <c r="AN2">
         <v>0</v>
@@ -12235,13 +12235,13 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-0.02169178005741503</v>
+        <v>-0.02169178083291023</v>
       </c>
       <c r="AQ2">
-        <v>-70.73381002307775</v>
+        <v>-70.73381328390803</v>
       </c>
       <c r="AR2">
-        <v>-70.73392091061065</v>
+        <v>-70.73392747863518</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -12285,40 +12285,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>3.948768371157741E-13</v>
+        <v>6.14300367600713E-13</v>
       </c>
       <c r="O3">
-        <v>-7.772532835023283E-13</v>
+        <v>-7.772575474376066E-13</v>
       </c>
       <c r="P3">
-        <v>1.170380495906034E-12</v>
+        <v>1.170308813068623E-12</v>
       </c>
       <c r="Q3">
-        <v>-3.94876837083488E-13</v>
+        <v>-6.143003749341673E-13</v>
       </c>
       <c r="R3">
-        <v>7.774537069353966E-13</v>
+        <v>7.774042203283692E-13</v>
       </c>
       <c r="S3">
-        <v>-1.170179809472271E-12</v>
+        <v>-1.170121272835953E-12</v>
       </c>
       <c r="T3">
-        <v>1.124570404146796E-12</v>
+        <v>8.184214554454782E-13</v>
       </c>
       <c r="U3">
-        <v>-9.031178716263893E-13</v>
+        <v>-9.032035365157925E-13</v>
       </c>
       <c r="V3">
-        <v>-2.217728856889226E-13</v>
+        <v>-2.218824527176377E-13</v>
       </c>
       <c r="W3">
-        <v>-1.124570404135435E-12</v>
+        <v>-8.184214787286789E-13</v>
       </c>
       <c r="X3">
-        <v>9.031883968057675E-13</v>
+        <v>9.033202489578611E-13</v>
       </c>
       <c r="Y3">
-        <v>2.218435034135023E-13</v>
+        <v>2.218833545308619E-13</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -12339,40 +12339,40 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>0.9001195554286869</v>
+        <v>0.9001195554053522</v>
       </c>
       <c r="AH3">
-        <v>0.0003611643931572446</v>
+        <v>0.0003611643786635592</v>
       </c>
       <c r="AI3">
-        <v>0.0003608296670016657</v>
+        <v>0.000360829667038422</v>
       </c>
       <c r="AJ3">
-        <v>0.9001195554125136</v>
+        <v>0.9001195756570931</v>
       </c>
       <c r="AK3">
-        <v>0.0003612202254634719</v>
+        <v>0.0003612201894594547</v>
       </c>
       <c r="AL3">
-        <v>0.0003607739235851073</v>
+        <v>0.0003607739020138145</v>
       </c>
       <c r="AM3">
-        <v>-0.02169178005741503</v>
+        <v>-0.02169178083291023</v>
       </c>
       <c r="AN3">
-        <v>-70.73381002307775</v>
+        <v>-70.73381328390803</v>
       </c>
       <c r="AO3">
-        <v>-70.73392091061065</v>
+        <v>-70.73392747863518</v>
       </c>
       <c r="AP3">
-        <v>-0.02169177877396126</v>
+        <v>-0.02169132664722373</v>
       </c>
       <c r="AQ3">
-        <v>-70.73890181238976</v>
+        <v>-70.73549810913154</v>
       </c>
       <c r="AR3">
-        <v>-70.73905606684608</v>
+        <v>-70.73565072316602</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -12416,40 +12416,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>3.948768584753843E-13</v>
+        <v>8.190671568009506E-13</v>
       </c>
       <c r="O4">
-        <v>-7.772533117377996E-13</v>
+        <v>-7.772123876754596E-13</v>
       </c>
       <c r="P4">
-        <v>1.170380528552284E-12</v>
+        <v>1.170524365833788E-12</v>
       </c>
       <c r="Q4">
-        <v>-3.948768584560126E-13</v>
+        <v>-8.190671626679284E-13</v>
       </c>
       <c r="R4">
-        <v>7.773735658046673E-13</v>
+        <v>7.773003921872559E-13</v>
       </c>
       <c r="S4">
-        <v>-1.170260116684848E-12</v>
+        <v>-1.170411816977297E-12</v>
       </c>
       <c r="T4">
-        <v>1.124570434635948E-12</v>
+        <v>1.091228607260638E-12</v>
       </c>
       <c r="U4">
-        <v>-9.031178921146454E-13</v>
+        <v>-9.033327369348998E-13</v>
       </c>
       <c r="V4">
-        <v>-2.21772898148733E-13</v>
+        <v>-2.218360806275603E-13</v>
       </c>
       <c r="W4">
-        <v>-1.124570434629132E-12</v>
+        <v>-1.091228625890309E-12</v>
       </c>
       <c r="X4">
-        <v>9.031602072248363E-13</v>
+        <v>9.034027824490395E-13</v>
       </c>
       <c r="Y4">
-        <v>2.218152687860071E-13</v>
+        <v>2.218366369977509E-13</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -12470,40 +12470,40 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>0.9001195554286869</v>
+        <v>0.9001195554053522</v>
       </c>
       <c r="AH4">
-        <v>0.0003611643931572446</v>
+        <v>0.0003611643786635592</v>
       </c>
       <c r="AI4">
-        <v>0.0003608296670016657</v>
+        <v>0.000360829667038422</v>
       </c>
       <c r="AJ4">
-        <v>0.9001195554189829</v>
+        <v>0.9001195675581231</v>
       </c>
       <c r="AK4">
-        <v>0.0003611978921998335</v>
+        <v>0.0003611978668456565</v>
       </c>
       <c r="AL4">
-        <v>0.0003607962206030118</v>
+        <v>0.0003607962067283275</v>
       </c>
       <c r="AM4">
-        <v>-0.02169178005741503</v>
+        <v>-0.02169178083291023</v>
       </c>
       <c r="AN4">
-        <v>-70.73381002307775</v>
+        <v>-70.73381328390803</v>
       </c>
       <c r="AO4">
-        <v>-70.73392091061065</v>
+        <v>-70.73392747863518</v>
       </c>
       <c r="AP4">
-        <v>-0.02169177928734275</v>
+        <v>-0.02169150825026314</v>
       </c>
       <c r="AQ4">
-        <v>-70.73686528561373</v>
+        <v>-70.73482417402057</v>
       </c>
       <c r="AR4">
-        <v>-70.7370018140615</v>
+        <v>-70.73496174646925</v>
       </c>
     </row>
   </sheetData>
@@ -12691,40 +12691,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-1.574923508548382E-09</v>
+        <v>-1.574923577117689E-09</v>
       </c>
       <c r="O2">
-        <v>-8.835537262057283E-10</v>
+        <v>-8.835537124051814E-10</v>
       </c>
       <c r="P2">
-        <v>2.45435023153024E-09</v>
+        <v>2.454350130431908E-09</v>
       </c>
       <c r="Q2">
-        <v>-9.135150860527591E-16</v>
+        <v>-8.449911078598466E-16</v>
       </c>
       <c r="R2">
-        <v>2.063665916269664E-12</v>
+        <v>2.063652202938913E-12</v>
       </c>
       <c r="S2">
-        <v>2.064630465383226E-12</v>
+        <v>2.064731525832086E-12</v>
       </c>
       <c r="T2">
-        <v>-1.927808497530656E-09</v>
+        <v>-1.927808417665502E-09</v>
       </c>
       <c r="U2">
-        <v>2.329182445024226E-09</v>
+        <v>2.329182369968423E-09</v>
       </c>
       <c r="V2">
-        <v>-3.986657478074489E-10</v>
+        <v>-3.986656455351969E-10</v>
       </c>
       <c r="W2">
-        <v>-5.574266016519804E-16</v>
+        <v>-6.372217600362772E-16</v>
       </c>
       <c r="X2">
-        <v>-1.68740475407041E-12</v>
+        <v>-1.687329696310622E-12</v>
       </c>
       <c r="Y2">
-        <v>-1.688986995169712E-12</v>
+        <v>-1.689089341289751E-12</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -12754,16 +12754,16 @@
         <v>0.9498024507880762</v>
       </c>
       <c r="AJ2">
-        <v>0.9500000754967397</v>
+        <v>0.9500000754967369</v>
       </c>
       <c r="AK2">
         <v>0.9498024532803541</v>
       </c>
       <c r="AL2">
-        <v>0.9498023609145367</v>
+        <v>0.9498023609145418</v>
       </c>
       <c r="AM2">
-        <v>3.110444667927112E-09</v>
+        <v>3.110444840212894E-09</v>
       </c>
       <c r="AN2">
         <v>-120.0097469250981</v>
@@ -12772,13 +12772,13 @@
         <v>119.9902530667639</v>
       </c>
       <c r="AP2">
-        <v>-3.217144193350149E-06</v>
+        <v>-3.217143930572254E-06</v>
       </c>
       <c r="AQ2">
-        <v>-120.0097407489747</v>
+        <v>-120.009740748975</v>
       </c>
       <c r="AR2">
-        <v>119.9902501163165</v>
+        <v>119.9902501163167</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -12822,40 +12822,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>3.045048828706839E-16</v>
+        <v>3.86727723566623E-16</v>
       </c>
       <c r="O3">
-        <v>-6.878886200626896E-13</v>
+        <v>-6.879630901705409E-13</v>
       </c>
       <c r="P3">
-        <v>-6.882101387926326E-13</v>
+        <v>-6.881559928514509E-13</v>
       </c>
       <c r="Q3">
-        <v>-3.045048828706813E-16</v>
+        <v>-3.867277235673343E-16</v>
       </c>
       <c r="R3">
-        <v>6.87888620078806E-13</v>
+        <v>6.879630901823359E-13</v>
       </c>
       <c r="S3">
-        <v>6.8821013880877E-13</v>
+        <v>6.881559928665328E-13</v>
       </c>
       <c r="T3">
-        <v>1.8580891576365E-16</v>
+        <v>1.05471174006545E-16</v>
       </c>
       <c r="U3">
-        <v>5.624682225977548E-13</v>
+        <v>5.624775413847807E-13</v>
       </c>
       <c r="V3">
-        <v>5.629956410442148E-13</v>
+        <v>5.630940059484315E-13</v>
       </c>
       <c r="W3">
-        <v>-1.85808915763649E-16</v>
+        <v>-1.054711740090138E-16</v>
       </c>
       <c r="X3">
-        <v>-5.624682225920839E-13</v>
+        <v>-5.624775413753946E-13</v>
       </c>
       <c r="Y3">
-        <v>-5.629956410385364E-13</v>
+        <v>-5.630940059483594E-13</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -12876,40 +12876,40 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>0.9500000754967397</v>
+        <v>0.9500000754967369</v>
       </c>
       <c r="AH3">
         <v>0.9498024532803541</v>
       </c>
       <c r="AI3">
-        <v>0.9498023609145367</v>
+        <v>0.9498023609145418</v>
       </c>
       <c r="AJ3">
-        <v>0.9500000754967326</v>
+        <v>0.9500000754999026</v>
       </c>
       <c r="AK3">
-        <v>0.9498024532898531</v>
+        <v>0.9498024532837641</v>
       </c>
       <c r="AL3">
-        <v>0.9498023609240385</v>
+        <v>0.949802360926961</v>
       </c>
       <c r="AM3">
-        <v>-3.217144193350149E-06</v>
+        <v>-3.217143930572254E-06</v>
       </c>
       <c r="AN3">
-        <v>-120.0097407489747</v>
+        <v>-120.009740748975</v>
       </c>
       <c r="AO3">
-        <v>119.9902501163165</v>
+        <v>119.9902501163167</v>
       </c>
       <c r="AP3">
-        <v>-3.217144101395338E-06</v>
+        <v>-3.216830245752654E-06</v>
       </c>
       <c r="AQ3">
-        <v>-120.0097407480338</v>
+        <v>-120.0097407480252</v>
       </c>
       <c r="AR3">
-        <v>119.9902501172581</v>
+        <v>119.9902501169358</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -12953,40 +12953,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>3.045048949199494E-16</v>
+        <v>3.515706681965221E-16</v>
       </c>
       <c r="O4">
-        <v>-6.878886383121029E-13</v>
+        <v>-6.879725351943282E-13</v>
       </c>
       <c r="P4">
-        <v>-6.882101539120678E-13</v>
+        <v>-6.883515281141081E-13</v>
       </c>
       <c r="Q4">
-        <v>-3.045048949199478E-16</v>
+        <v>-3.515706681963012E-16</v>
       </c>
       <c r="R4">
-        <v>6.878886383217727E-13</v>
+        <v>6.879725352014037E-13</v>
       </c>
       <c r="S4">
-        <v>6.882101539217505E-13</v>
+        <v>6.883515281231574E-13</v>
       </c>
       <c r="T4">
-        <v>1.85808919954698E-16</v>
+        <v>2.812565021826244E-16</v>
       </c>
       <c r="U4">
-        <v>5.624682467644664E-13</v>
+        <v>5.623206309246884E-13</v>
       </c>
       <c r="V4">
-        <v>5.629956608041305E-13</v>
+        <v>5.62940574525821E-13</v>
       </c>
       <c r="W4">
-        <v>-1.858089199546975E-16</v>
+        <v>-2.812565021843422E-16</v>
       </c>
       <c r="X4">
-        <v>-5.624682467610639E-13</v>
+        <v>-5.623206309190574E-13</v>
       </c>
       <c r="Y4">
-        <v>-5.629956608007235E-13</v>
+        <v>-5.629405745257745E-13</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -13007,40 +13007,40 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>0.9500000754967397</v>
+        <v>0.9500000754967369</v>
       </c>
       <c r="AH4">
         <v>0.9498024532803541</v>
       </c>
       <c r="AI4">
-        <v>0.9498023609145367</v>
+        <v>0.9498023609145418</v>
       </c>
       <c r="AJ4">
-        <v>0.9500000754967355</v>
+        <v>0.9500000754986373</v>
       </c>
       <c r="AK4">
-        <v>0.9498024532860535</v>
+        <v>0.9498024532824008</v>
       </c>
       <c r="AL4">
-        <v>0.9498023609202377</v>
+        <v>0.9498023609219927</v>
       </c>
       <c r="AM4">
-        <v>-3.217144193350149E-06</v>
+        <v>-3.217143930572254E-06</v>
       </c>
       <c r="AN4">
-        <v>-120.0097407489747</v>
+        <v>-120.009740748975</v>
       </c>
       <c r="AO4">
-        <v>119.9902501163165</v>
+        <v>119.9902501163167</v>
       </c>
       <c r="AP4">
-        <v>-3.217144138177262E-06</v>
+        <v>-3.216955667905308E-06</v>
       </c>
       <c r="AQ4">
-        <v>-120.0097407484101</v>
+        <v>-120.0097407484052</v>
       </c>
       <c r="AR4">
-        <v>119.9902501168814</v>
+        <v>119.9902501166882</v>
       </c>
     </row>
   </sheetData>
@@ -13228,40 +13228,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>-1.339138993327805E-09</v>
+        <v>-1.339139020543481E-09</v>
       </c>
       <c r="O2">
-        <v>-7.512753473600394E-10</v>
+        <v>-7.512753066316285E-10</v>
       </c>
       <c r="P2">
-        <v>2.08690518110145E-09</v>
+        <v>2.086905220791652E-09</v>
       </c>
       <c r="Q2">
-        <v>-7.76709803221207E-16</v>
+        <v>-7.494908292054936E-16</v>
       </c>
       <c r="R2">
-        <v>1.754710954606336E-12</v>
+        <v>1.754670312534387E-12</v>
       </c>
       <c r="S2">
-        <v>1.755531157399338E-12</v>
+        <v>1.755491381913804E-12</v>
       </c>
       <c r="T2">
-        <v>-1.639162993665593E-09</v>
+        <v>-1.639162845447367E-09</v>
       </c>
       <c r="U2">
-        <v>1.980476488507743E-09</v>
+        <v>1.980476391360479E-09</v>
       </c>
       <c r="V2">
-        <v>-3.389808163672247E-10</v>
+        <v>-3.389805667449464E-10</v>
       </c>
       <c r="W2">
-        <v>-4.73984801650588E-16</v>
+        <v>-6.221047012434584E-16</v>
       </c>
       <c r="X2">
-        <v>-1.434780563044211E-12</v>
+        <v>-1.4346834694704E-12</v>
       </c>
       <c r="Y2">
-        <v>-1.436125852071583E-12</v>
+        <v>-1.436375517674645E-12</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -13291,16 +13291,16 @@
         <v>0.8998226837825006</v>
       </c>
       <c r="AJ2">
-        <v>0.9000000546137114</v>
+        <v>0.9000000546137056</v>
       </c>
       <c r="AK2">
-        <v>0.8998226860235774</v>
+        <v>0.8998226860235802</v>
       </c>
       <c r="AL2">
-        <v>0.8998226031194996</v>
+        <v>0.8998226031194994</v>
       </c>
       <c r="AM2">
-        <v>2.791713753470196E-09</v>
+        <v>2.791713853329513E-09</v>
       </c>
       <c r="AN2">
         <v>-120.0092340302239</v>
@@ -13309,13 +13309,13 @@
         <v>119.9907659624712</v>
       </c>
       <c r="AP2">
-        <v>-3.047964365618454E-06</v>
+        <v>-3.047964171733972E-06</v>
       </c>
       <c r="AQ2">
-        <v>-120.0092281791599</v>
+        <v>-120.0092281791603</v>
       </c>
       <c r="AR2">
-        <v>119.9907631673106</v>
+        <v>119.9907631673112</v>
       </c>
     </row>
     <row r="3" spans="1:44">
@@ -13359,40 +13359,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>2.589033775900048E-16</v>
+        <v>2.997602436978923E-16</v>
       </c>
       <c r="O3">
-        <v>-5.849036373223066E-13</v>
+        <v>-5.849320757271921E-13</v>
       </c>
       <c r="P3">
-        <v>-5.851770388532911E-13</v>
+        <v>-5.850743034775369E-13</v>
       </c>
       <c r="Q3">
-        <v>-2.589033775900027E-16</v>
+        <v>-2.997602436979746E-16</v>
       </c>
       <c r="R3">
-        <v>5.84903637335289E-13</v>
+        <v>5.849320757366931E-13</v>
       </c>
       <c r="S3">
-        <v>5.851770388662906E-13</v>
+        <v>5.850743034896837E-13</v>
       </c>
       <c r="T3">
-        <v>1.579951315797019E-16</v>
+        <v>1.665334478529905E-16</v>
       </c>
       <c r="U3">
-        <v>4.782601628469417E-13</v>
+        <v>4.782749011745446E-13</v>
       </c>
       <c r="V3">
-        <v>4.787085978358296E-13</v>
+        <v>4.787397931863478E-13</v>
       </c>
       <c r="W3">
-        <v>-1.579951315797011E-16</v>
+        <v>-1.665334478550711E-16</v>
       </c>
       <c r="X3">
-        <v>-4.782601628423734E-13</v>
+        <v>-4.782749011669849E-13</v>
       </c>
       <c r="Y3">
-        <v>-4.787085978312553E-13</v>
+        <v>-4.787397931862893E-13</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -13413,40 +13413,40 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>0.9000000546137114</v>
+        <v>0.9000000546137056</v>
       </c>
       <c r="AH3">
-        <v>0.8998226860235774</v>
+        <v>0.8998226860235802</v>
       </c>
       <c r="AI3">
-        <v>0.8998226031194996</v>
+        <v>0.8998226031194994</v>
       </c>
       <c r="AJ3">
-        <v>0.9000000546137049</v>
+        <v>0.9000000546165466</v>
       </c>
       <c r="AK3">
-        <v>0.899822686032103</v>
+        <v>0.8998226860266408</v>
       </c>
       <c r="AL3">
-        <v>0.8998226031280274</v>
+        <v>0.8998226031306448</v>
       </c>
       <c r="AM3">
-        <v>-3.047964365618454E-06</v>
+        <v>-3.047964171733972E-06</v>
       </c>
       <c r="AN3">
-        <v>-120.0092281791599</v>
+        <v>-120.0092281791603</v>
       </c>
       <c r="AO3">
-        <v>119.9907631673106</v>
+        <v>119.9907631673112</v>
       </c>
       <c r="AP3">
-        <v>-3.047964278490057E-06</v>
+        <v>-3.047666960828988E-06</v>
       </c>
       <c r="AQ3">
-        <v>-120.0092281782685</v>
+        <v>-120.0092281782605</v>
       </c>
       <c r="AR3">
-        <v>119.9907631682027</v>
+        <v>119.9907631678976</v>
       </c>
     </row>
     <row r="4" spans="1:44">
@@ -13490,40 +13490,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>2.589033860272477E-16</v>
+        <v>1.998401778210043E-16</v>
       </c>
       <c r="O4">
-        <v>-5.849036517269161E-13</v>
+        <v>-5.847590592746451E-13</v>
       </c>
       <c r="P4">
-        <v>-5.851770517891424E-13</v>
+        <v>-5.853094843751586E-13</v>
       </c>
       <c r="Q4">
-        <v>-2.589033860272465E-16</v>
+        <v>-1.998401778201389E-16</v>
       </c>
       <c r="R4">
-        <v>5.849036517347055E-13</v>
+        <v>5.847590592803444E-13</v>
       </c>
       <c r="S4">
-        <v>5.851770517969421E-13</v>
+        <v>5.853094843824484E-13</v>
       </c>
       <c r="T4">
-        <v>1.579951340612434E-16</v>
+        <v>3.996803024875143E-16</v>
       </c>
       <c r="U4">
-        <v>4.782601826087622E-13</v>
+        <v>4.781749729204432E-13</v>
       </c>
       <c r="V4">
-        <v>4.787086161836332E-13</v>
+        <v>4.78680958169433E-13</v>
       </c>
       <c r="W4">
-        <v>-1.57995134061243E-16</v>
+        <v>-3.996803024888937E-16</v>
       </c>
       <c r="X4">
-        <v>-4.782601826060213E-13</v>
+        <v>-4.781749729159094E-13</v>
       </c>
       <c r="Y4">
-        <v>-4.787086161808885E-13</v>
+        <v>-4.786809581693957E-13</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -13544,40 +13544,40 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>0.9000000546137114</v>
+        <v>0.9000000546137056</v>
       </c>
       <c r="AH4">
-        <v>0.8998226860235774</v>
+        <v>0.8998226860235802</v>
       </c>
       <c r="AI4">
-        <v>0.8998226031194996</v>
+        <v>0.8998226031194994</v>
       </c>
       <c r="AJ4">
-        <v>0.9000000546137076</v>
+        <v>0.9000000546154112</v>
       </c>
       <c r="AK4">
-        <v>0.8998226860286929</v>
+        <v>0.899822686025417</v>
       </c>
       <c r="AL4">
-        <v>0.8998226031246163</v>
+        <v>0.8998226031261867</v>
       </c>
       <c r="AM4">
-        <v>-3.047964365618454E-06</v>
+        <v>-3.047964171733972E-06</v>
       </c>
       <c r="AN4">
-        <v>-120.0092281791599</v>
+        <v>-120.0092281791603</v>
       </c>
       <c r="AO4">
-        <v>119.9907631673106</v>
+        <v>119.9907631673112</v>
       </c>
       <c r="AP4">
-        <v>-3.047964313341416E-06</v>
+        <v>-3.047785814703789E-06</v>
       </c>
       <c r="AQ4">
-        <v>-120.0092281786251</v>
+        <v>-120.0092281786205</v>
       </c>
       <c r="AR4">
-        <v>119.9907631678459</v>
+        <v>119.9907631676631</v>
       </c>
     </row>
   </sheetData>
@@ -14872,40 +14872,40 @@
         <v>0</v>
       </c>
       <c r="N2">
-        <v>2.899362709301044E-32</v>
+        <v>-1.799966344178518E-13</v>
       </c>
       <c r="O2">
-        <v>-4.359417221757416E-16</v>
+        <v>-8.28072005758487E-14</v>
       </c>
       <c r="P2">
-        <v>4.225722585540734E-16</v>
+        <v>-2.910207294775528E-14</v>
       </c>
       <c r="Q2">
-        <v>-2.958804065529305E-32</v>
+        <v>1.799504907802913E-13</v>
       </c>
       <c r="R2">
-        <v>1.395501411721234E-15</v>
+        <v>8.379454098628914E-14</v>
       </c>
       <c r="S2">
-        <v>5.345588329073687E-16</v>
+        <v>3.008817696400831E-14</v>
       </c>
       <c r="T2">
-        <v>-2.428612756093138E-18</v>
+        <v>6.37165985463069E-13</v>
       </c>
       <c r="U2">
-        <v>5.251360417084603E-09</v>
+        <v>5.251015381641699E-09</v>
       </c>
       <c r="V2">
-        <v>-5.251360442573949E-09</v>
+        <v>-5.250833229602337E-09</v>
       </c>
       <c r="W2">
-        <v>2.428612756093137E-18</v>
+        <v>-6.371222704292374E-13</v>
       </c>
       <c r="X2">
-        <v>-5.251359776081031E-09</v>
+        <v>-5.251014758958749E-09</v>
       </c>
       <c r="Y2">
-        <v>5.251361090863373E-09</v>
+        <v>5.250833848639078E-09</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -14926,40 +14926,40 @@
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.049999952323356</v>
+        <v>1.049999952323337</v>
       </c>
       <c r="AG2">
-        <v>0.5249999761622322</v>
+        <v>0.5249999761622289</v>
       </c>
       <c r="AH2">
-        <v>0.5249999761611237</v>
+        <v>0.5249999761611168</v>
       </c>
       <c r="AI2">
-        <v>1.049999952323355</v>
+        <v>1.049999952318965</v>
       </c>
       <c r="AJ2">
-        <v>0.5249999113501055</v>
+        <v>0.5249999113579495</v>
       </c>
       <c r="AK2">
-        <v>0.5250000409732692</v>
+        <v>0.5250000409693789</v>
       </c>
       <c r="AL2">
-        <v>6.840170220788716E-13</v>
+        <v>1.08101060599428E-12</v>
       </c>
       <c r="AM2">
-        <v>-179.9999999999302</v>
+        <v>-179.9999999999301</v>
       </c>
       <c r="AN2">
-        <v>179.9999999999233</v>
+        <v>179.9999999999241</v>
       </c>
       <c r="AO2">
-        <v>6.980404139591467E-13</v>
+        <v>5.005959726037086E-10</v>
       </c>
       <c r="AP2">
-        <v>-179.999989530504</v>
+        <v>-179.9999895313235</v>
       </c>
       <c r="AQ2">
-        <v>179.9999895304996</v>
+        <v>179.9999895313486</v>
       </c>
     </row>
     <row r="3" spans="1:43">
@@ -15003,40 +15003,40 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>2.722412804757337E-20</v>
+        <v>3.183231311680899E-13</v>
       </c>
       <c r="O3">
-        <v>-4.850007999382701E-16</v>
+        <v>-3.198601935560318E-16</v>
       </c>
       <c r="P3">
-        <v>-1.595669049568566E-16</v>
+        <v>3.180033691173211E-13</v>
       </c>
       <c r="Q3">
-        <v>-2.722412804757337E-20</v>
+        <v>-3.18323131167561E-13</v>
       </c>
       <c r="R3">
-        <v>5.916185400130231E-16</v>
+        <v>4.264861270589288E-16</v>
       </c>
       <c r="S3">
-        <v>2.661846455273342E-16</v>
+        <v>-3.178967735148762E-13</v>
       </c>
       <c r="T3">
-        <v>-4.924954585559059E-23</v>
+        <v>-3.183231311625275E-13</v>
       </c>
       <c r="U3">
-        <v>1.75045322752648E-09</v>
+        <v>1.750617843762178E-09</v>
       </c>
       <c r="V3">
-        <v>-1.750453664572954E-09</v>
+        <v>-1.750299952840581E-09</v>
       </c>
       <c r="W3">
-        <v>4.92495458555906E-23</v>
+        <v>3.183231311623904E-13</v>
       </c>
       <c r="X3">
-        <v>-1.750453155494326E-09</v>
+        <v>-1.750617771729728E-09</v>
       </c>
       <c r="Y3">
-        <v>1.750453736605109E-09</v>
+        <v>1.75030002487566E-09</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -15057,40 +15057,40 @@
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.049999952323355</v>
+        <v>1.049999952318965</v>
       </c>
       <c r="AG3">
-        <v>0.5249999113501055</v>
+        <v>0.5249999113579495</v>
       </c>
       <c r="AH3">
-        <v>0.5250000409732692</v>
+        <v>0.5250000409693789</v>
       </c>
       <c r="AI3">
-        <v>1.049999952323355</v>
+        <v>1.049999952317867</v>
       </c>
       <c r="AJ3">
-        <v>0.5249998897460679</v>
+        <v>0.5249998897558518</v>
       </c>
       <c r="AK3">
-        <v>0.5250000625773207</v>
+        <v>0.5250000625703921</v>
       </c>
       <c r="AL3">
-        <v>6.980404139591467E-13</v>
+        <v>5.005959726037086E-10</v>
       </c>
       <c r="AM3">
-        <v>-179.999989530504</v>
+        <v>-179.9999895313235</v>
       </c>
       <c r="AN3">
-        <v>179.9999895304996</v>
+        <v>179.9999895313486</v>
       </c>
       <c r="AO3">
-        <v>6.980312221028967E-13</v>
+        <v>4.65325469723474E-10</v>
       </c>
       <c r="AP3">
-        <v>-179.9999860406947</v>
+        <v>-179.9999860415744</v>
       </c>
       <c r="AQ3">
-        <v>179.9999860406923</v>
+        <v>179.999986041531</v>
       </c>
     </row>
     <row r="4" spans="1:43">
@@ -15134,40 +15134,40 @@
         <v>0</v>
       </c>
       <c r="N4">
-        <v>2.722412818893724E-20</v>
+        <v>1.273292524669578E-12</v>
       </c>
       <c r="O4">
-        <v>-4.704291331885115E-16</v>
+        <v>-6.369661021036479E-13</v>
       </c>
       <c r="P4">
-        <v>-1.595669138323263E-16</v>
+        <v>-4.778044116324633E-13</v>
       </c>
       <c r="Q4">
-        <v>-2.722412818893724E-20</v>
+        <v>-1.273292524668427E-12</v>
       </c>
       <c r="R4">
-        <v>5.343997801531593E-16</v>
+        <v>6.370300677692029E-13</v>
       </c>
       <c r="S4">
-        <v>2.23537561652478E-16</v>
+        <v>4.778683466855712E-13</v>
       </c>
       <c r="T4">
-        <v>-4.924989926526009E-23</v>
+        <v>-9.549693934848013E-13</v>
       </c>
       <c r="U4">
-        <v>1.750453271241507E-09</v>
+        <v>1.750936166737729E-09</v>
       </c>
       <c r="V4">
-        <v>-1.750453713145215E-09</v>
+        <v>-1.749504144769024E-09</v>
       </c>
       <c r="W4">
-        <v>4.92498992652601E-23</v>
+        <v>9.549693934806566E-13</v>
       </c>
       <c r="X4">
-        <v>-1.750453228022212E-09</v>
+        <v>-1.750936123487597E-09</v>
       </c>
       <c r="Y4">
-        <v>1.75045375636451E-09</v>
+        <v>1.749504187935591E-09</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -15188,40 +15188,40 @@
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.049999952323355</v>
+        <v>1.049999952318965</v>
       </c>
       <c r="AG4">
-        <v>0.5249999113501055</v>
+        <v>0.5249999113579495</v>
       </c>
       <c r="AH4">
-        <v>0.5250000409732692</v>
+        <v>0.5250000409693789</v>
       </c>
       <c r="AI4">
-        <v>1.049999952323355</v>
+        <v>1.049999952316717</v>
       </c>
       <c r="AJ4">
-        <v>0.5249998983876822</v>
+        <v>0.5249998983968288</v>
       </c>
       <c r="AK4">
-        <v>0.5250000539357004</v>
+        <v>0.5250000539282597</v>
       </c>
       <c r="AL4">
-        <v>6.980404139591467E-13</v>
+        <v>5.005959726037086E-10</v>
       </c>
       <c r="AM4">
-        <v>-179.999989530504</v>
+        <v>-179.9999895313235</v>
       </c>
       <c r="AN4">
-        <v>179.9999895304996</v>
+        <v>179.9999895313486</v>
       </c>
       <c r="AO4">
-        <v>6.980348988452555E-13</v>
+        <v>5.950980962266128E-10</v>
       </c>
       <c r="AP4">
-        <v>-179.9999874366184</v>
+        <v>-179.9999874376642</v>
       </c>
       <c r="AQ4">
-        <v>179.9999874366152</v>
+        <v>179.9999874378795</v>
       </c>
     </row>
   </sheetData>
